--- a/research/traditional_assets/database/data/greece/greece_recreation.xlsx
+++ b/research/traditional_assets/database/data/greece/greece_recreation.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="atse_asco" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,121 +590,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.01065</v>
+        <v>0.015805</v>
       </c>
       <c r="E2">
-        <v>0.133</v>
+        <v>-0.00208</v>
       </c>
       <c r="G2">
-        <v>-0.002998065764023207</v>
+        <v>0.06838365896980461</v>
       </c>
       <c r="H2">
-        <v>-0.007930367504835584</v>
+        <v>0.0649911190053286</v>
       </c>
       <c r="I2">
-        <v>0.009090909090909094</v>
+        <v>0.06936056838365898</v>
       </c>
       <c r="J2">
-        <v>0.008124389051808409</v>
+        <v>0.06211096377040805</v>
       </c>
       <c r="K2">
-        <v>-0.08999999999999986</v>
+        <v>1.63</v>
       </c>
       <c r="L2">
-        <v>-0.001740812379110249</v>
+        <v>0.02895204262877443</v>
       </c>
       <c r="M2">
-        <v>1.31</v>
+        <v>2.661</v>
       </c>
       <c r="N2">
-        <v>0.03096926713947991</v>
+        <v>0.06991592222806095</v>
       </c>
       <c r="O2">
-        <v>-14.55555555555558</v>
+        <v>1.632515337423313</v>
       </c>
       <c r="P2">
-        <v>1.31</v>
+        <v>2.61</v>
       </c>
       <c r="Q2">
-        <v>0.03096926713947991</v>
+        <v>0.06857593273778244</v>
       </c>
       <c r="R2">
-        <v>-14.55555555555558</v>
+        <v>1.601226993865031</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>0.05100000000000016</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>0.01916572717023681</v>
       </c>
       <c r="U2">
-        <v>10.35</v>
+        <v>8.620000000000001</v>
       </c>
       <c r="V2">
-        <v>0.2446808510638298</v>
+        <v>0.2264844981607987</v>
       </c>
       <c r="W2">
-        <v>-0.04737203506213866</v>
+        <v>-0.003513513513513505</v>
       </c>
       <c r="X2">
-        <v>0.1339427321273028</v>
+        <v>0.2215528831657406</v>
       </c>
       <c r="Y2">
-        <v>-0.1813147671894415</v>
+        <v>-0.2250663966792541</v>
       </c>
       <c r="Z2">
-        <v>0.9250147608738439</v>
+        <v>0.9827709602527622</v>
       </c>
       <c r="AA2">
-        <v>-0.001680619980682543</v>
+        <v>0.04794383270872352</v>
       </c>
       <c r="AB2">
-        <v>0.09471180665963076</v>
+        <v>0.1622103710858177</v>
       </c>
       <c r="AC2">
-        <v>-0.09639242664031331</v>
+        <v>-0.1142665383770941</v>
       </c>
       <c r="AD2">
-        <v>15.837</v>
+        <v>11.102</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>15.837</v>
+        <v>11.102</v>
       </c>
       <c r="AG2">
-        <v>5.487</v>
+        <v>2.481999999999999</v>
       </c>
       <c r="AH2">
-        <v>0.2724082770008772</v>
+        <v>0.2258248240510964</v>
       </c>
       <c r="AI2">
-        <v>0.2341469905525082</v>
+        <v>0.1944240131694161</v>
       </c>
       <c r="AJ2">
-        <v>0.1148220227258459</v>
+        <v>0.06122046273000837</v>
       </c>
       <c r="AK2">
-        <v>0.09578089269816888</v>
+        <v>0.05119425766263767</v>
       </c>
       <c r="AL2">
-        <v>0.465</v>
+        <v>1.785</v>
       </c>
       <c r="AM2">
-        <v>-0.8659999999999999</v>
+        <v>1.738</v>
       </c>
       <c r="AN2">
-        <v>6.309561752988048</v>
+        <v>1.934820494945974</v>
       </c>
       <c r="AO2">
-        <v>1.010752688172043</v>
+        <v>2.187675070028011</v>
       </c>
       <c r="AP2">
-        <v>2.18605577689243</v>
+        <v>0.4325548971767165</v>
       </c>
       <c r="AQ2">
-        <v>-0.542725173210162</v>
+        <v>2.246835443037975</v>
       </c>
     </row>
     <row r="3">
@@ -722,118 +724,121 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.0251</v>
+        <v>0.00191</v>
       </c>
       <c r="E3">
-        <v>0.133</v>
+        <v>-0.00208</v>
       </c>
       <c r="G3">
-        <v>0.1723451327433628</v>
+        <v>0.1552797202797203</v>
       </c>
       <c r="H3">
-        <v>0.1610619469026549</v>
+        <v>0.1486013986013986</v>
       </c>
       <c r="I3">
-        <v>0.1345132743362832</v>
+        <v>0.163986013986014</v>
       </c>
       <c r="J3">
-        <v>0.1059111237986488</v>
+        <v>0.1297061979116774</v>
       </c>
       <c r="K3">
-        <v>2.93</v>
+        <v>2.89</v>
       </c>
       <c r="L3">
-        <v>0.129646017699115</v>
+        <v>0.101048951048951</v>
       </c>
       <c r="M3">
-        <v>1.31</v>
+        <v>2.661</v>
       </c>
       <c r="N3">
-        <v>0.04198717948717949</v>
+        <v>0.08899665551839465</v>
       </c>
       <c r="O3">
-        <v>0.447098976109215</v>
+        <v>0.9207612456747405</v>
       </c>
       <c r="P3">
-        <v>1.31</v>
+        <v>2.61</v>
       </c>
       <c r="Q3">
-        <v>0.04198717948717949</v>
+        <v>0.08729096989966555</v>
       </c>
       <c r="R3">
-        <v>0.447098976109215</v>
+        <v>0.903114186851211</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>0.05100000000000016</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>0.01916572717023681</v>
       </c>
       <c r="U3">
-        <v>7.53</v>
+        <v>6.17</v>
       </c>
       <c r="V3">
-        <v>0.2413461538461538</v>
+        <v>0.2063545150501672</v>
       </c>
       <c r="W3">
-        <v>0.0839541547277937</v>
+        <v>0.07810810810810812</v>
       </c>
       <c r="X3">
-        <v>0.09317100240141284</v>
+        <v>0.1593808854223156</v>
       </c>
       <c r="Y3">
-        <v>-0.009216847673619133</v>
+        <v>-0.08127277731420748</v>
       </c>
       <c r="Z3">
-        <v>0.822386376041629</v>
+        <v>0.9595061562720166</v>
       </c>
       <c r="AA3">
-        <v>0.08709986528326709</v>
+        <v>0.124453895402891</v>
       </c>
       <c r="AB3">
-        <v>0.0926137257477144</v>
+        <v>0.1587892663994007</v>
       </c>
       <c r="AC3">
-        <v>-0.005513860464447309</v>
+        <v>-0.03433537099650968</v>
       </c>
       <c r="AD3">
-        <v>0.337</v>
+        <v>0.202</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.337</v>
+        <v>0.202</v>
       </c>
       <c r="AG3">
-        <v>-7.193000000000001</v>
+        <v>-5.968</v>
       </c>
       <c r="AH3">
-        <v>0.01068586105209754</v>
+        <v>0.006710517573583151</v>
       </c>
       <c r="AI3">
-        <v>0.009025899242038728</v>
+        <v>0.005888869453676171</v>
       </c>
       <c r="AJ3">
-        <v>-0.2996209438913651</v>
+        <v>-0.2493732241350493</v>
       </c>
       <c r="AK3">
-        <v>-0.2413191532190425</v>
+        <v>-0.2121427555808332</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AM3">
-        <v>-1.29</v>
+        <v>1.234</v>
       </c>
       <c r="AN3">
-        <v>0.09492957746478874</v>
+        <v>0.03937621832358675</v>
+      </c>
+      <c r="AO3">
+        <v>3.6640625</v>
       </c>
       <c r="AP3">
-        <v>-2.026197183098592</v>
+        <v>-1.163352826510721</v>
       </c>
       <c r="AQ3">
-        <v>-2.356589147286821</v>
+        <v>3.80064829821718</v>
       </c>
     </row>
     <row r="4">
@@ -853,25 +858,25 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0464</v>
+        <v>0.0297</v>
       </c>
       <c r="G4">
-        <v>-0.1391752577319587</v>
+        <v>-0.02133574007220217</v>
       </c>
       <c r="H4">
-        <v>-0.1391752577319587</v>
+        <v>-0.02133574007220217</v>
       </c>
       <c r="I4">
-        <v>-0.08831615120274913</v>
+        <v>-0.02833935018050542</v>
       </c>
       <c r="J4">
-        <v>-0.08831615120274913</v>
+        <v>-0.02833935018050542</v>
       </c>
       <c r="K4">
-        <v>-3.02</v>
+        <v>-1.26</v>
       </c>
       <c r="L4">
-        <v>-0.1037800687285223</v>
+        <v>-0.04548736462093863</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -895,73 +900,8785 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>2.82</v>
+        <v>2.45</v>
       </c>
       <c r="V4">
-        <v>0.2540540540540541</v>
+        <v>0.3002450980392157</v>
       </c>
       <c r="W4">
-        <v>-0.178698224852071</v>
+        <v>-0.08513513513513513</v>
       </c>
       <c r="X4">
-        <v>0.1747144618531928</v>
+        <v>0.2837248809091656</v>
       </c>
       <c r="Y4">
-        <v>-0.3534126867052638</v>
+        <v>-0.3688600160443007</v>
       </c>
       <c r="Z4">
-        <v>1.02428722280887</v>
+        <v>1.008005822416303</v>
       </c>
       <c r="AA4">
-        <v>-0.09046110524463218</v>
+        <v>-0.02856622998544396</v>
       </c>
       <c r="AB4">
-        <v>0.09680988757154713</v>
+        <v>0.1656314757722346</v>
       </c>
       <c r="AC4">
-        <v>-0.1872709928161793</v>
+        <v>-0.1941977057576786</v>
       </c>
       <c r="AD4">
-        <v>15.5</v>
+        <v>10.9</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>15.5</v>
+        <v>10.9</v>
       </c>
       <c r="AG4">
-        <v>12.68</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="AH4">
-        <v>0.5827067669172932</v>
+        <v>0.5718782791185729</v>
       </c>
       <c r="AI4">
-        <v>0.5115511551155115</v>
+        <v>0.4780701754385965</v>
       </c>
       <c r="AJ4">
-        <v>0.5332211942809083</v>
+        <v>0.5087296809151114</v>
       </c>
       <c r="AK4">
-        <v>0.4614264919941776</v>
+        <v>0.4152334152334152</v>
       </c>
       <c r="AL4">
-        <v>0.465</v>
+        <v>0.505</v>
       </c>
       <c r="AM4">
-        <v>0.424</v>
+        <v>0.504</v>
       </c>
       <c r="AN4">
-        <v>-14.90384615384615</v>
+        <v>17.92763157894737</v>
       </c>
       <c r="AO4">
-        <v>-5.526881720430107</v>
+        <v>-1.554455445544555</v>
       </c>
       <c r="AP4">
-        <v>-12.19230769230769</v>
+        <v>13.89802631578947</v>
       </c>
       <c r="AQ4">
-        <v>-6.06132075471698</v>
+        <v>-1.557539682539683</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AQ2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_capital</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>actual_equity_value</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>actual_enterprise_value</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_capital</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_rating</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>actual_beta</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>As Commercial Industrial Company of Computers and Toys S.A. (ATSE:ASCO)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ATSE:ASCO</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Recreation</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>0.00671051757358315</v>
+      </c>
+      <c r="F2">
+        <v>0.62</v>
+      </c>
+      <c r="G2">
+        <v>29.9</v>
+      </c>
+      <c r="H2">
+        <v>14.0701906654609</v>
+      </c>
+      <c r="I2">
+        <v>23.932</v>
+      </c>
+      <c r="J2">
+        <v>26.5634306654609</v>
+      </c>
+      <c r="K2">
+        <v>0.202</v>
+      </c>
+      <c r="L2">
+        <v>18.66324</v>
+      </c>
+      <c r="M2">
+        <v>0.158789266399401</v>
+      </c>
+      <c r="N2">
+        <v>0.144929790035395</v>
+      </c>
+      <c r="O2">
+        <v>0.0712179357798165</v>
+      </c>
+      <c r="P2">
+        <v>0.0429</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="S2">
+        <v>0.159380885422316</v>
+      </c>
+      <c r="T2">
+        <v>0.311399447461565</v>
+      </c>
+      <c r="U2">
+        <v>0.994752238840203</v>
+      </c>
+      <c r="V2">
+        <v>2.24885486384735</v>
+      </c>
+      <c r="W2">
+        <v>4.569020559813155</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0.0388</v>
+      </c>
+      <c r="AA2">
+        <v>29.9</v>
+      </c>
+      <c r="AB2">
+        <v>0.1212170033041622</v>
+      </c>
+      <c r="AC2">
+        <v>0.09130504587155963</v>
+      </c>
+      <c r="AD2">
+        <v>0.22</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>1</v>
+      </c>
+      <c r="AG2">
+        <v>5.13</v>
+      </c>
+      <c r="AH2">
+        <v>0.4399999999999995</v>
+      </c>
+      <c r="AI2">
+        <v>0.8119999999999994</v>
+      </c>
+      <c r="AJ2">
+        <v>0.202</v>
+      </c>
+      <c r="AK2">
+        <v>0.202</v>
+      </c>
+      <c r="AL2">
+        <v>1.28</v>
+      </c>
+      <c r="AM2">
+        <v>0.202</v>
+      </c>
+      <c r="AN2">
+        <v>6.17</v>
+      </c>
+      <c r="AO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ2">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.1587488073591881</v>
+      </c>
+      <c r="C2">
+        <v>30.10892278949363</v>
+      </c>
+      <c r="D2">
+        <v>23.93892278949362</v>
+      </c>
+      <c r="E2">
+        <v>-0.202</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>6.17</v>
+      </c>
+      <c r="H2">
+        <v>29.9</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>5.13</v>
+      </c>
+      <c r="K2">
+        <v>0.4399999999999995</v>
+      </c>
+      <c r="L2">
+        <v>4.69</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>4.69</v>
+      </c>
+      <c r="O2">
+        <v>1.0318</v>
+      </c>
+      <c r="P2">
+        <v>3.6582</v>
+      </c>
+      <c r="Q2">
+        <v>4.0982</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.1587488073591881</v>
+      </c>
+      <c r="T2">
+        <v>0.9895378048425111</v>
+      </c>
+      <c r="U2">
+        <v>0.0457</v>
+      </c>
+      <c r="V2">
+        <v>0.22</v>
+      </c>
+      <c r="W2">
+        <v>0.035646</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.1584533799829978</v>
+      </c>
+      <c r="C3">
+        <v>29.85857387274369</v>
+      </c>
+      <c r="D3">
+        <v>23.98959387274369</v>
+      </c>
+      <c r="E3">
+        <v>0.09902</v>
+      </c>
+      <c r="F3">
+        <v>0.30102</v>
+      </c>
+      <c r="G3">
+        <v>6.17</v>
+      </c>
+      <c r="H3">
+        <v>29.9</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>5.13</v>
+      </c>
+      <c r="K3">
+        <v>0.4399999999999995</v>
+      </c>
+      <c r="L3">
+        <v>4.69</v>
+      </c>
+      <c r="M3">
+        <v>0.013756614</v>
+      </c>
+      <c r="N3">
+        <v>4.676243386</v>
+      </c>
+      <c r="O3">
+        <v>1.02877354492</v>
+      </c>
+      <c r="P3">
+        <v>3.64746984108</v>
+      </c>
+      <c r="Q3">
+        <v>4.08746984108</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.1596938585686847</v>
+      </c>
+      <c r="T3">
+        <v>0.9973341633049065</v>
+      </c>
+      <c r="U3">
+        <v>0.0457</v>
+      </c>
+      <c r="V3">
+        <v>0.22</v>
+      </c>
+      <c r="W3">
+        <v>0.035646</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>340.9269170451391</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.1581579526068076</v>
+      </c>
+      <c r="C4">
+        <v>29.60843992012837</v>
+      </c>
+      <c r="D4">
+        <v>24.04047992012837</v>
+      </c>
+      <c r="E4">
+        <v>0.40004</v>
+      </c>
+      <c r="F4">
+        <v>0.60204</v>
+      </c>
+      <c r="G4">
+        <v>6.17</v>
+      </c>
+      <c r="H4">
+        <v>29.9</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>5.13</v>
+      </c>
+      <c r="K4">
+        <v>0.4399999999999995</v>
+      </c>
+      <c r="L4">
+        <v>4.69</v>
+      </c>
+      <c r="M4">
+        <v>0.027513228</v>
+      </c>
+      <c r="N4">
+        <v>4.662486772</v>
+      </c>
+      <c r="O4">
+        <v>1.02574708984</v>
+      </c>
+      <c r="P4">
+        <v>3.63673968216</v>
+      </c>
+      <c r="Q4">
+        <v>4.076739682159999</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.1606581965375588</v>
+      </c>
+      <c r="T4">
+        <v>1.005289631123678</v>
+      </c>
+      <c r="U4">
+        <v>0.0457</v>
+      </c>
+      <c r="V4">
+        <v>0.22</v>
+      </c>
+      <c r="W4">
+        <v>0.035646</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>170.4634585225696</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.1578625252306174</v>
+      </c>
+      <c r="C5">
+        <v>29.35852230248294</v>
+      </c>
+      <c r="D5">
+        <v>24.09158230248294</v>
+      </c>
+      <c r="E5">
+        <v>0.70106</v>
+      </c>
+      <c r="F5">
+        <v>0.90306</v>
+      </c>
+      <c r="G5">
+        <v>6.17</v>
+      </c>
+      <c r="H5">
+        <v>29.9</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>5.13</v>
+      </c>
+      <c r="K5">
+        <v>0.4399999999999995</v>
+      </c>
+      <c r="L5">
+        <v>4.69</v>
+      </c>
+      <c r="M5">
+        <v>0.041269842</v>
+      </c>
+      <c r="N5">
+        <v>4.648730158</v>
+      </c>
+      <c r="O5">
+        <v>1.02272063476</v>
+      </c>
+      <c r="P5">
+        <v>3.62600952324</v>
+      </c>
+      <c r="Q5">
+        <v>4.06600952324</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.1616424177635231</v>
+      </c>
+      <c r="T5">
+        <v>1.013409129206753</v>
+      </c>
+      <c r="U5">
+        <v>0.0457</v>
+      </c>
+      <c r="V5">
+        <v>0.22</v>
+      </c>
+      <c r="W5">
+        <v>0.035646</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>113.6423056817131</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.1575670978544272</v>
+      </c>
+      <c r="C6">
+        <v>29.10882240232337</v>
+      </c>
+      <c r="D6">
+        <v>24.14290240232337</v>
+      </c>
+      <c r="E6">
+        <v>1.00208</v>
+      </c>
+      <c r="F6">
+        <v>1.20408</v>
+      </c>
+      <c r="G6">
+        <v>6.17</v>
+      </c>
+      <c r="H6">
+        <v>29.9</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>5.13</v>
+      </c>
+      <c r="K6">
+        <v>0.4399999999999995</v>
+      </c>
+      <c r="L6">
+        <v>4.69</v>
+      </c>
+      <c r="M6">
+        <v>0.05502645600000001</v>
+      </c>
+      <c r="N6">
+        <v>4.634973544</v>
+      </c>
+      <c r="O6">
+        <v>1.01969417968</v>
+      </c>
+      <c r="P6">
+        <v>3.61527936432</v>
+      </c>
+      <c r="Q6">
+        <v>4.05527936432</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.1626471435983617</v>
+      </c>
+      <c r="T6">
+        <v>1.021697783499893</v>
+      </c>
+      <c r="U6">
+        <v>0.0457</v>
+      </c>
+      <c r="V6">
+        <v>0.22</v>
+      </c>
+      <c r="W6">
+        <v>0.035646</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>85.23172926128478</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.157271670478237</v>
+      </c>
+      <c r="C7">
+        <v>28.85934161397093</v>
+      </c>
+      <c r="D7">
+        <v>24.19444161397093</v>
+      </c>
+      <c r="E7">
+        <v>1.3031</v>
+      </c>
+      <c r="F7">
+        <v>1.5051</v>
+      </c>
+      <c r="G7">
+        <v>6.17</v>
+      </c>
+      <c r="H7">
+        <v>29.9</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>5.13</v>
+      </c>
+      <c r="K7">
+        <v>0.4399999999999995</v>
+      </c>
+      <c r="L7">
+        <v>4.69</v>
+      </c>
+      <c r="M7">
+        <v>0.06878307000000002</v>
+      </c>
+      <c r="N7">
+        <v>4.62121693</v>
+      </c>
+      <c r="O7">
+        <v>1.0166677246</v>
+      </c>
+      <c r="P7">
+        <v>3.6045492054</v>
+      </c>
+      <c r="Q7">
+        <v>4.044549205399999</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.163673021556039</v>
+      </c>
+      <c r="T7">
+        <v>1.030160935778151</v>
+      </c>
+      <c r="U7">
+        <v>0.0457</v>
+      </c>
+      <c r="V7">
+        <v>0.22</v>
+      </c>
+      <c r="W7">
+        <v>0.035646</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>68.18538340902782</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.1569762431020468</v>
+      </c>
+      <c r="C8">
+        <v>28.61008134367853</v>
+      </c>
+      <c r="D8">
+        <v>24.24620134367853</v>
+      </c>
+      <c r="E8">
+        <v>1.60412</v>
+      </c>
+      <c r="F8">
+        <v>1.80612</v>
+      </c>
+      <c r="G8">
+        <v>6.17</v>
+      </c>
+      <c r="H8">
+        <v>29.9</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>5.13</v>
+      </c>
+      <c r="K8">
+        <v>0.4399999999999995</v>
+      </c>
+      <c r="L8">
+        <v>4.69</v>
+      </c>
+      <c r="M8">
+        <v>0.082539684</v>
+      </c>
+      <c r="N8">
+        <v>4.607460316</v>
+      </c>
+      <c r="O8">
+        <v>1.01364126952</v>
+      </c>
+      <c r="P8">
+        <v>3.59381904648</v>
+      </c>
+      <c r="Q8">
+        <v>4.03381904648</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.1647207267043051</v>
+      </c>
+      <c r="T8">
+        <v>1.03880415512616</v>
+      </c>
+      <c r="U8">
+        <v>0.0457</v>
+      </c>
+      <c r="V8">
+        <v>0.22</v>
+      </c>
+      <c r="W8">
+        <v>0.035646</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>56.82115284085653</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.1566808157258565</v>
+      </c>
+      <c r="C9">
+        <v>28.36104300975859</v>
+      </c>
+      <c r="D9">
+        <v>24.29818300975859</v>
+      </c>
+      <c r="E9">
+        <v>1.90514</v>
+      </c>
+      <c r="F9">
+        <v>2.10714</v>
+      </c>
+      <c r="G9">
+        <v>6.17</v>
+      </c>
+      <c r="H9">
+        <v>29.9</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>5.13</v>
+      </c>
+      <c r="K9">
+        <v>0.4399999999999995</v>
+      </c>
+      <c r="L9">
+        <v>4.69</v>
+      </c>
+      <c r="M9">
+        <v>0.09629629800000002</v>
+      </c>
+      <c r="N9">
+        <v>4.593703702</v>
+      </c>
+      <c r="O9">
+        <v>1.01061481444</v>
+      </c>
+      <c r="P9">
+        <v>3.58308888756</v>
+      </c>
+      <c r="Q9">
+        <v>4.02308888756</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.1657909631460823</v>
+      </c>
+      <c r="T9">
+        <v>1.047633250159071</v>
+      </c>
+      <c r="U9">
+        <v>0.0457</v>
+      </c>
+      <c r="V9">
+        <v>0.22</v>
+      </c>
+      <c r="W9">
+        <v>0.035646</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>48.70384529216273</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.1563853883496663</v>
+      </c>
+      <c r="C10">
+        <v>28.1122280427126</v>
+      </c>
+      <c r="D10">
+        <v>24.3503880427126</v>
+      </c>
+      <c r="E10">
+        <v>2.20616</v>
+      </c>
+      <c r="F10">
+        <v>2.40816</v>
+      </c>
+      <c r="G10">
+        <v>6.17</v>
+      </c>
+      <c r="H10">
+        <v>29.9</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>5.13</v>
+      </c>
+      <c r="K10">
+        <v>0.4399999999999995</v>
+      </c>
+      <c r="L10">
+        <v>4.69</v>
+      </c>
+      <c r="M10">
+        <v>0.110052912</v>
+      </c>
+      <c r="N10">
+        <v>4.579947088</v>
+      </c>
+      <c r="O10">
+        <v>1.00758835936</v>
+      </c>
+      <c r="P10">
+        <v>3.57235872864</v>
+      </c>
+      <c r="Q10">
+        <v>4.01235872864</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.1668844655974634</v>
+      </c>
+      <c r="T10">
+        <v>1.056654282040525</v>
+      </c>
+      <c r="U10">
+        <v>0.0457</v>
+      </c>
+      <c r="V10">
+        <v>0.22</v>
+      </c>
+      <c r="W10">
+        <v>0.035646</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>42.61586463064238</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.1560899609734762</v>
+      </c>
+      <c r="C11">
+        <v>27.86363788536232</v>
+      </c>
+      <c r="D11">
+        <v>24.40281788536232</v>
+      </c>
+      <c r="E11">
+        <v>2.50718</v>
+      </c>
+      <c r="F11">
+        <v>2.70918</v>
+      </c>
+      <c r="G11">
+        <v>6.17</v>
+      </c>
+      <c r="H11">
+        <v>29.9</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>5.13</v>
+      </c>
+      <c r="K11">
+        <v>0.4399999999999995</v>
+      </c>
+      <c r="L11">
+        <v>4.69</v>
+      </c>
+      <c r="M11">
+        <v>0.123809526</v>
+      </c>
+      <c r="N11">
+        <v>4.566190474000001</v>
+      </c>
+      <c r="O11">
+        <v>1.00456190428</v>
+      </c>
+      <c r="P11">
+        <v>3.561628569720001</v>
+      </c>
+      <c r="Q11">
+        <v>4.00162856972</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.168002001069754</v>
+      </c>
+      <c r="T11">
+        <v>1.065873578358933</v>
+      </c>
+      <c r="U11">
+        <v>0.0457</v>
+      </c>
+      <c r="V11">
+        <v>0.22</v>
+      </c>
+      <c r="W11">
+        <v>0.035646</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>37.88076856057102</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.1557945335972859</v>
+      </c>
+      <c r="C12">
+        <v>27.61527399298276</v>
+      </c>
+      <c r="D12">
+        <v>24.45547399298276</v>
+      </c>
+      <c r="E12">
+        <v>2.8082</v>
+      </c>
+      <c r="F12">
+        <v>3.0102</v>
+      </c>
+      <c r="G12">
+        <v>6.17</v>
+      </c>
+      <c r="H12">
+        <v>29.9</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>5.13</v>
+      </c>
+      <c r="K12">
+        <v>0.4399999999999995</v>
+      </c>
+      <c r="L12">
+        <v>4.69</v>
+      </c>
+      <c r="M12">
+        <v>0.13756614</v>
+      </c>
+      <c r="N12">
+        <v>4.552433860000001</v>
+      </c>
+      <c r="O12">
+        <v>1.0015354492</v>
+      </c>
+      <c r="P12">
+        <v>3.550898410800001</v>
+      </c>
+      <c r="Q12">
+        <v>3.9908984108</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.169144370663651</v>
+      </c>
+      <c r="T12">
+        <v>1.075297747928862</v>
+      </c>
+      <c r="U12">
+        <v>0.0457</v>
+      </c>
+      <c r="V12">
+        <v>0.22</v>
+      </c>
+      <c r="W12">
+        <v>0.035646</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>34.09269170451391</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.1554991062210957</v>
+      </c>
+      <c r="C13">
+        <v>27.36713783343677</v>
+      </c>
+      <c r="D13">
+        <v>24.50835783343677</v>
+      </c>
+      <c r="E13">
+        <v>3.10922</v>
+      </c>
+      <c r="F13">
+        <v>3.31122</v>
+      </c>
+      <c r="G13">
+        <v>6.17</v>
+      </c>
+      <c r="H13">
+        <v>29.9</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>5.13</v>
+      </c>
+      <c r="K13">
+        <v>0.4399999999999995</v>
+      </c>
+      <c r="L13">
+        <v>4.69</v>
+      </c>
+      <c r="M13">
+        <v>0.151322754</v>
+      </c>
+      <c r="N13">
+        <v>4.538677246000001</v>
+      </c>
+      <c r="O13">
+        <v>0.99850899412</v>
+      </c>
+      <c r="P13">
+        <v>3.540168251880001</v>
+      </c>
+      <c r="Q13">
+        <v>3.98016825188</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.1703124114843772</v>
+      </c>
+      <c r="T13">
+        <v>1.08493369659025</v>
+      </c>
+      <c r="U13">
+        <v>0.0457</v>
+      </c>
+      <c r="V13">
+        <v>0.22</v>
+      </c>
+      <c r="W13">
+        <v>0.035646</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>30.99335609501265</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.1552036788449055</v>
+      </c>
+      <c r="C14">
+        <v>27.11923088731147</v>
+      </c>
+      <c r="D14">
+        <v>24.56147088731147</v>
+      </c>
+      <c r="E14">
+        <v>3.41024</v>
+      </c>
+      <c r="F14">
+        <v>3.61224</v>
+      </c>
+      <c r="G14">
+        <v>6.17</v>
+      </c>
+      <c r="H14">
+        <v>29.9</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>5.13</v>
+      </c>
+      <c r="K14">
+        <v>0.4399999999999995</v>
+      </c>
+      <c r="L14">
+        <v>4.69</v>
+      </c>
+      <c r="M14">
+        <v>0.165079368</v>
+      </c>
+      <c r="N14">
+        <v>4.524920632000001</v>
+      </c>
+      <c r="O14">
+        <v>0.9954825390400001</v>
+      </c>
+      <c r="P14">
+        <v>3.52943809296</v>
+      </c>
+      <c r="Q14">
+        <v>3.96943809296</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.1715069986873926</v>
+      </c>
+      <c r="T14">
+        <v>1.094788644084851</v>
+      </c>
+      <c r="U14">
+        <v>0.0457</v>
+      </c>
+      <c r="V14">
+        <v>0.22</v>
+      </c>
+      <c r="W14">
+        <v>0.035646</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>28.41057642042827</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.1549082514687153</v>
+      </c>
+      <c r="C15">
+        <v>26.87155464805639</v>
+      </c>
+      <c r="D15">
+        <v>24.61481464805639</v>
+      </c>
+      <c r="E15">
+        <v>3.71126</v>
+      </c>
+      <c r="F15">
+        <v>3.91326</v>
+      </c>
+      <c r="G15">
+        <v>6.17</v>
+      </c>
+      <c r="H15">
+        <v>29.9</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>5.13</v>
+      </c>
+      <c r="K15">
+        <v>0.4399999999999995</v>
+      </c>
+      <c r="L15">
+        <v>4.69</v>
+      </c>
+      <c r="M15">
+        <v>0.178835982</v>
+      </c>
+      <c r="N15">
+        <v>4.511164018000001</v>
+      </c>
+      <c r="O15">
+        <v>0.99245608396</v>
+      </c>
+      <c r="P15">
+        <v>3.51870793404</v>
+      </c>
+      <c r="Q15">
+        <v>3.95870793404</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.17272904766519</v>
+      </c>
+      <c r="T15">
+        <v>1.104870142096569</v>
+      </c>
+      <c r="U15">
+        <v>0.0457</v>
+      </c>
+      <c r="V15">
+        <v>0.22</v>
+      </c>
+      <c r="W15">
+        <v>0.035646</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>26.2251474650107</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.1546128240925251</v>
+      </c>
+      <c r="C16">
+        <v>26.6241106221235</v>
+      </c>
+      <c r="D16">
+        <v>24.6683906221235</v>
+      </c>
+      <c r="E16">
+        <v>4.012280000000001</v>
+      </c>
+      <c r="F16">
+        <v>4.21428</v>
+      </c>
+      <c r="G16">
+        <v>6.17</v>
+      </c>
+      <c r="H16">
+        <v>29.9</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>5.13</v>
+      </c>
+      <c r="K16">
+        <v>0.4399999999999995</v>
+      </c>
+      <c r="L16">
+        <v>4.69</v>
+      </c>
+      <c r="M16">
+        <v>0.192592596</v>
+      </c>
+      <c r="N16">
+        <v>4.497407404</v>
+      </c>
+      <c r="O16">
+        <v>0.98942962888</v>
+      </c>
+      <c r="P16">
+        <v>3.507977775120001</v>
+      </c>
+      <c r="Q16">
+        <v>3.94797777512</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.1739795163866571</v>
+      </c>
+      <c r="T16">
+        <v>1.115186093550421</v>
+      </c>
+      <c r="U16">
+        <v>0.0457</v>
+      </c>
+      <c r="V16">
+        <v>0.22</v>
+      </c>
+      <c r="W16">
+        <v>0.035646</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>24.35192264608137</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.1543173967163348</v>
+      </c>
+      <c r="C17">
+        <v>26.376900329109</v>
+      </c>
+      <c r="D17">
+        <v>24.722200329109</v>
+      </c>
+      <c r="E17">
+        <v>4.3133</v>
+      </c>
+      <c r="F17">
+        <v>4.5153</v>
+      </c>
+      <c r="G17">
+        <v>6.17</v>
+      </c>
+      <c r="H17">
+        <v>29.9</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>5.13</v>
+      </c>
+      <c r="K17">
+        <v>0.4399999999999995</v>
+      </c>
+      <c r="L17">
+        <v>4.69</v>
+      </c>
+      <c r="M17">
+        <v>0.20634921</v>
+      </c>
+      <c r="N17">
+        <v>4.48365079</v>
+      </c>
+      <c r="O17">
+        <v>0.9864031738</v>
+      </c>
+      <c r="P17">
+        <v>3.497247616200001</v>
+      </c>
+      <c r="Q17">
+        <v>3.9372476162</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.1752594079015704</v>
+      </c>
+      <c r="T17">
+        <v>1.125744773273774</v>
+      </c>
+      <c r="U17">
+        <v>0.0457</v>
+      </c>
+      <c r="V17">
+        <v>0.22</v>
+      </c>
+      <c r="W17">
+        <v>0.035646</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>22.72846113634261</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.1540219693401446</v>
+      </c>
+      <c r="C18">
+        <v>26.12992530189699</v>
+      </c>
+      <c r="D18">
+        <v>24.77624530189699</v>
+      </c>
+      <c r="E18">
+        <v>4.61432</v>
+      </c>
+      <c r="F18">
+        <v>4.81632</v>
+      </c>
+      <c r="G18">
+        <v>6.17</v>
+      </c>
+      <c r="H18">
+        <v>29.9</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>5.13</v>
+      </c>
+      <c r="K18">
+        <v>0.4399999999999995</v>
+      </c>
+      <c r="L18">
+        <v>4.69</v>
+      </c>
+      <c r="M18">
+        <v>0.220105824</v>
+      </c>
+      <c r="N18">
+        <v>4.469894176</v>
+      </c>
+      <c r="O18">
+        <v>0.98337671872</v>
+      </c>
+      <c r="P18">
+        <v>3.486517457280001</v>
+      </c>
+      <c r="Q18">
+        <v>3.92651745728</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.1765697730239817</v>
+      </c>
+      <c r="T18">
+        <v>1.136554850133398</v>
+      </c>
+      <c r="U18">
+        <v>0.0457</v>
+      </c>
+      <c r="V18">
+        <v>0.22</v>
+      </c>
+      <c r="W18">
+        <v>0.035646</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>21.3079323153212</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.1537265419639544</v>
+      </c>
+      <c r="C19">
+        <v>25.88318708680501</v>
+      </c>
+      <c r="D19">
+        <v>24.83052708680501</v>
+      </c>
+      <c r="E19">
+        <v>4.91534</v>
+      </c>
+      <c r="F19">
+        <v>5.11734</v>
+      </c>
+      <c r="G19">
+        <v>6.17</v>
+      </c>
+      <c r="H19">
+        <v>29.9</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>5.13</v>
+      </c>
+      <c r="K19">
+        <v>0.4399999999999995</v>
+      </c>
+      <c r="L19">
+        <v>4.69</v>
+      </c>
+      <c r="M19">
+        <v>0.233862438</v>
+      </c>
+      <c r="N19">
+        <v>4.456137562</v>
+      </c>
+      <c r="O19">
+        <v>0.98035026364</v>
+      </c>
+      <c r="P19">
+        <v>3.47578729836</v>
+      </c>
+      <c r="Q19">
+        <v>3.91578729836</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.1779117132095837</v>
+      </c>
+      <c r="T19">
+        <v>1.147625410772773</v>
+      </c>
+      <c r="U19">
+        <v>0.0457</v>
+      </c>
+      <c r="V19">
+        <v>0.22</v>
+      </c>
+      <c r="W19">
+        <v>0.035646</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>20.05452453206701</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.1534311145877642</v>
+      </c>
+      <c r="C20">
+        <v>25.63668724373155</v>
+      </c>
+      <c r="D20">
+        <v>24.88504724373155</v>
+      </c>
+      <c r="E20">
+        <v>5.21636</v>
+      </c>
+      <c r="F20">
+        <v>5.41836</v>
+      </c>
+      <c r="G20">
+        <v>6.17</v>
+      </c>
+      <c r="H20">
+        <v>29.9</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>5.13</v>
+      </c>
+      <c r="K20">
+        <v>0.4399999999999995</v>
+      </c>
+      <c r="L20">
+        <v>4.69</v>
+      </c>
+      <c r="M20">
+        <v>0.247619052</v>
+      </c>
+      <c r="N20">
+        <v>4.442380948</v>
+      </c>
+      <c r="O20">
+        <v>0.9773238085599999</v>
+      </c>
+      <c r="P20">
+        <v>3.46505713944</v>
+      </c>
+      <c r="Q20">
+        <v>3.90505713944</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.1792863836436149</v>
+      </c>
+      <c r="T20">
+        <v>1.158965985086277</v>
+      </c>
+      <c r="U20">
+        <v>0.0457</v>
+      </c>
+      <c r="V20">
+        <v>0.22</v>
+      </c>
+      <c r="W20">
+        <v>0.035646</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>18.94038428028551</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.153135687211574</v>
+      </c>
+      <c r="C21">
+        <v>25.39042734630549</v>
+      </c>
+      <c r="D21">
+        <v>24.93980734630549</v>
+      </c>
+      <c r="E21">
+        <v>5.51738</v>
+      </c>
+      <c r="F21">
+        <v>5.71938</v>
+      </c>
+      <c r="G21">
+        <v>6.17</v>
+      </c>
+      <c r="H21">
+        <v>29.9</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>5.13</v>
+      </c>
+      <c r="K21">
+        <v>0.4399999999999995</v>
+      </c>
+      <c r="L21">
+        <v>4.69</v>
+      </c>
+      <c r="M21">
+        <v>0.261375666</v>
+      </c>
+      <c r="N21">
+        <v>4.428624334</v>
+      </c>
+      <c r="O21">
+        <v>0.9742973534799999</v>
+      </c>
+      <c r="P21">
+        <v>3.45432698052</v>
+      </c>
+      <c r="Q21">
+        <v>3.89432698052</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.1806949965574988</v>
+      </c>
+      <c r="T21">
+        <v>1.170586573580363</v>
+      </c>
+      <c r="U21">
+        <v>0.0457</v>
+      </c>
+      <c r="V21">
+        <v>0.22</v>
+      </c>
+      <c r="W21">
+        <v>0.035646</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>17.94352194974417</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.1528402598353838</v>
+      </c>
+      <c r="C22">
+        <v>25.14440898203745</v>
+      </c>
+      <c r="D22">
+        <v>24.99480898203745</v>
+      </c>
+      <c r="E22">
+        <v>5.8184</v>
+      </c>
+      <c r="F22">
+        <v>6.0204</v>
+      </c>
+      <c r="G22">
+        <v>6.17</v>
+      </c>
+      <c r="H22">
+        <v>29.9</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>5.13</v>
+      </c>
+      <c r="K22">
+        <v>0.4399999999999995</v>
+      </c>
+      <c r="L22">
+        <v>4.69</v>
+      </c>
+      <c r="M22">
+        <v>0.2751322800000001</v>
+      </c>
+      <c r="N22">
+        <v>4.41486772</v>
+      </c>
+      <c r="O22">
+        <v>0.9712708983999999</v>
+      </c>
+      <c r="P22">
+        <v>3.4435968216</v>
+      </c>
+      <c r="Q22">
+        <v>3.8835968216</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.1821388247942297</v>
+      </c>
+      <c r="T22">
+        <v>1.182497676786801</v>
+      </c>
+      <c r="U22">
+        <v>0.0457</v>
+      </c>
+      <c r="V22">
+        <v>0.22</v>
+      </c>
+      <c r="W22">
+        <v>0.035646</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>17.04634585225696</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.1525448324591936</v>
+      </c>
+      <c r="C23">
+        <v>24.89863375247326</v>
+      </c>
+      <c r="D23">
+        <v>25.05005375247326</v>
+      </c>
+      <c r="E23">
+        <v>6.11942</v>
+      </c>
+      <c r="F23">
+        <v>6.32142</v>
+      </c>
+      <c r="G23">
+        <v>6.17</v>
+      </c>
+      <c r="H23">
+        <v>29.9</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>5.13</v>
+      </c>
+      <c r="K23">
+        <v>0.4399999999999995</v>
+      </c>
+      <c r="L23">
+        <v>4.69</v>
+      </c>
+      <c r="M23">
+        <v>0.288888894</v>
+      </c>
+      <c r="N23">
+        <v>4.401111106</v>
+      </c>
+      <c r="O23">
+        <v>0.9682444433199999</v>
+      </c>
+      <c r="P23">
+        <v>3.43286666268</v>
+      </c>
+      <c r="Q23">
+        <v>3.87286666268</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.1836192056445488</v>
+      </c>
+      <c r="T23">
+        <v>1.194710326909857</v>
+      </c>
+      <c r="U23">
+        <v>0.0457</v>
+      </c>
+      <c r="V23">
+        <v>0.22</v>
+      </c>
+      <c r="W23">
+        <v>0.035646</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>16.23461509738758</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.1522494050830034</v>
+      </c>
+      <c r="C24">
+        <v>24.65310327334932</v>
+      </c>
+      <c r="D24">
+        <v>25.10554327334932</v>
+      </c>
+      <c r="E24">
+        <v>6.42044</v>
+      </c>
+      <c r="F24">
+        <v>6.62244</v>
+      </c>
+      <c r="G24">
+        <v>6.17</v>
+      </c>
+      <c r="H24">
+        <v>29.9</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>5.13</v>
+      </c>
+      <c r="K24">
+        <v>0.4399999999999995</v>
+      </c>
+      <c r="L24">
+        <v>4.69</v>
+      </c>
+      <c r="M24">
+        <v>0.302645508</v>
+      </c>
+      <c r="N24">
+        <v>4.387354492</v>
+      </c>
+      <c r="O24">
+        <v>0.9652179882399999</v>
+      </c>
+      <c r="P24">
+        <v>3.42213650376</v>
+      </c>
+      <c r="Q24">
+        <v>3.86213650376</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.1851375449782094</v>
+      </c>
+      <c r="T24">
+        <v>1.207236121907864</v>
+      </c>
+      <c r="U24">
+        <v>0.0457</v>
+      </c>
+      <c r="V24">
+        <v>0.22</v>
+      </c>
+      <c r="W24">
+        <v>0.035646</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>15.49667804750633</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.1519539777068132</v>
+      </c>
+      <c r="C25">
+        <v>24.40781917475026</v>
+      </c>
+      <c r="D25">
+        <v>25.16127917475026</v>
+      </c>
+      <c r="E25">
+        <v>6.72146</v>
+      </c>
+      <c r="F25">
+        <v>6.92346</v>
+      </c>
+      <c r="G25">
+        <v>6.17</v>
+      </c>
+      <c r="H25">
+        <v>29.9</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>5.13</v>
+      </c>
+      <c r="K25">
+        <v>0.4399999999999995</v>
+      </c>
+      <c r="L25">
+        <v>4.69</v>
+      </c>
+      <c r="M25">
+        <v>0.3164021220000001</v>
+      </c>
+      <c r="N25">
+        <v>4.373597878</v>
+      </c>
+      <c r="O25">
+        <v>0.9621915331599998</v>
+      </c>
+      <c r="P25">
+        <v>3.41140634484</v>
+      </c>
+      <c r="Q25">
+        <v>3.85140634484</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.1866953216971599</v>
+      </c>
+      <c r="T25">
+        <v>1.220087262230494</v>
+      </c>
+      <c r="U25">
+        <v>0.0457</v>
+      </c>
+      <c r="V25">
+        <v>0.22</v>
+      </c>
+      <c r="W25">
+        <v>0.035646</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>14.82290943674518</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.1516585503306229</v>
+      </c>
+      <c r="C26">
+        <v>24.16278310126842</v>
+      </c>
+      <c r="D26">
+        <v>25.21726310126842</v>
+      </c>
+      <c r="E26">
+        <v>7.02248</v>
+      </c>
+      <c r="F26">
+        <v>7.22448</v>
+      </c>
+      <c r="G26">
+        <v>6.17</v>
+      </c>
+      <c r="H26">
+        <v>29.9</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>5.13</v>
+      </c>
+      <c r="K26">
+        <v>0.4399999999999995</v>
+      </c>
+      <c r="L26">
+        <v>4.69</v>
+      </c>
+      <c r="M26">
+        <v>0.330158736</v>
+      </c>
+      <c r="N26">
+        <v>4.359841264</v>
+      </c>
+      <c r="O26">
+        <v>0.9591650780799998</v>
+      </c>
+      <c r="P26">
+        <v>3.40067618592</v>
+      </c>
+      <c r="Q26">
+        <v>3.84067618592</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.1882940925402933</v>
+      </c>
+      <c r="T26">
+        <v>1.233276590456351</v>
+      </c>
+      <c r="U26">
+        <v>0.0457</v>
+      </c>
+      <c r="V26">
+        <v>0.22</v>
+      </c>
+      <c r="W26">
+        <v>0.035646</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>14.20528821021413</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.1513631229544327</v>
+      </c>
+      <c r="C27">
+        <v>23.9179967121657</v>
+      </c>
+      <c r="D27">
+        <v>25.27349671216571</v>
+      </c>
+      <c r="E27">
+        <v>7.3235</v>
+      </c>
+      <c r="F27">
+        <v>7.5255</v>
+      </c>
+      <c r="G27">
+        <v>6.17</v>
+      </c>
+      <c r="H27">
+        <v>29.9</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>5.13</v>
+      </c>
+      <c r="K27">
+        <v>0.4399999999999995</v>
+      </c>
+      <c r="L27">
+        <v>4.69</v>
+      </c>
+      <c r="M27">
+        <v>0.3439153500000001</v>
+      </c>
+      <c r="N27">
+        <v>4.34608465</v>
+      </c>
+      <c r="O27">
+        <v>0.9561386229999999</v>
+      </c>
+      <c r="P27">
+        <v>3.389946027</v>
+      </c>
+      <c r="Q27">
+        <v>3.829946027</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.189935497272577</v>
+      </c>
+      <c r="T27">
+        <v>1.246817634101564</v>
+      </c>
+      <c r="U27">
+        <v>0.0457</v>
+      </c>
+      <c r="V27">
+        <v>0.22</v>
+      </c>
+      <c r="W27">
+        <v>0.035646</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>13.63707668180556</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.1510676955782425</v>
+      </c>
+      <c r="C28">
+        <v>23.67346168153747</v>
+      </c>
+      <c r="D28">
+        <v>25.32998168153747</v>
+      </c>
+      <c r="E28">
+        <v>7.62452</v>
+      </c>
+      <c r="F28">
+        <v>7.82652</v>
+      </c>
+      <c r="G28">
+        <v>6.17</v>
+      </c>
+      <c r="H28">
+        <v>29.9</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>5.13</v>
+      </c>
+      <c r="K28">
+        <v>0.4399999999999995</v>
+      </c>
+      <c r="L28">
+        <v>4.69</v>
+      </c>
+      <c r="M28">
+        <v>0.3576719640000001</v>
+      </c>
+      <c r="N28">
+        <v>4.332328036000001</v>
+      </c>
+      <c r="O28">
+        <v>0.9531121679200001</v>
+      </c>
+      <c r="P28">
+        <v>3.379215868080001</v>
+      </c>
+      <c r="Q28">
+        <v>3.81921586808</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.1916212642949223</v>
+      </c>
+      <c r="T28">
+        <v>1.260724651899351</v>
+      </c>
+      <c r="U28">
+        <v>0.0457</v>
+      </c>
+      <c r="V28">
+        <v>0.22</v>
+      </c>
+      <c r="W28">
+        <v>0.035646</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>13.11257373250535</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.1511092282020523</v>
+      </c>
+      <c r="C29">
+        <v>23.36448550084864</v>
+      </c>
+      <c r="D29">
+        <v>25.32202550084864</v>
+      </c>
+      <c r="E29">
+        <v>7.92554</v>
+      </c>
+      <c r="F29">
+        <v>8.12754</v>
+      </c>
+      <c r="G29">
+        <v>6.17</v>
+      </c>
+      <c r="H29">
+        <v>29.9</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>5.13</v>
+      </c>
+      <c r="K29">
+        <v>0.4399999999999995</v>
+      </c>
+      <c r="L29">
+        <v>4.69</v>
+      </c>
+      <c r="M29">
+        <v>0.384432642</v>
+      </c>
+      <c r="N29">
+        <v>4.305567358</v>
+      </c>
+      <c r="O29">
+        <v>0.94722481876</v>
+      </c>
+      <c r="P29">
+        <v>3.35834253924</v>
+      </c>
+      <c r="Q29">
+        <v>3.79834253924</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.1933532167151401</v>
+      </c>
+      <c r="T29">
+        <v>1.275012683883378</v>
+      </c>
+      <c r="U29">
+        <v>0.0473</v>
+      </c>
+      <c r="V29">
+        <v>0.22</v>
+      </c>
+      <c r="W29">
+        <v>0.036894</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>12.19979649907044</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.1508262808258621</v>
+      </c>
+      <c r="C30">
+        <v>23.1177673767605</v>
+      </c>
+      <c r="D30">
+        <v>25.3763273767605</v>
+      </c>
+      <c r="E30">
+        <v>8.226560000000001</v>
+      </c>
+      <c r="F30">
+        <v>8.428560000000001</v>
+      </c>
+      <c r="G30">
+        <v>6.17</v>
+      </c>
+      <c r="H30">
+        <v>29.9</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>5.13</v>
+      </c>
+      <c r="K30">
+        <v>0.4399999999999995</v>
+      </c>
+      <c r="L30">
+        <v>4.69</v>
+      </c>
+      <c r="M30">
+        <v>0.3986708880000001</v>
+      </c>
+      <c r="N30">
+        <v>4.291329112000001</v>
+      </c>
+      <c r="O30">
+        <v>0.94409240464</v>
+      </c>
+      <c r="P30">
+        <v>3.34723670736</v>
+      </c>
+      <c r="Q30">
+        <v>3.78723670736</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.1951332789248084</v>
+      </c>
+      <c r="T30">
+        <v>1.28969760564474</v>
+      </c>
+      <c r="U30">
+        <v>0.0473</v>
+      </c>
+      <c r="V30">
+        <v>0.22</v>
+      </c>
+      <c r="W30">
+        <v>0.036894</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>11.7640894812465</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.1505433334496719</v>
+      </c>
+      <c r="C31">
+        <v>22.87128264874488</v>
+      </c>
+      <c r="D31">
+        <v>25.43086264874488</v>
+      </c>
+      <c r="E31">
+        <v>8.52758</v>
+      </c>
+      <c r="F31">
+        <v>8.72958</v>
+      </c>
+      <c r="G31">
+        <v>6.17</v>
+      </c>
+      <c r="H31">
+        <v>29.9</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>5.13</v>
+      </c>
+      <c r="K31">
+        <v>0.4399999999999995</v>
+      </c>
+      <c r="L31">
+        <v>4.69</v>
+      </c>
+      <c r="M31">
+        <v>0.412909134</v>
+      </c>
+      <c r="N31">
+        <v>4.277090866</v>
+      </c>
+      <c r="O31">
+        <v>0.9409599905199999</v>
+      </c>
+      <c r="P31">
+        <v>3.33613087548</v>
+      </c>
+      <c r="Q31">
+        <v>3.77613087548</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.1969634837319322</v>
+      </c>
+      <c r="T31">
+        <v>1.304796187174027</v>
+      </c>
+      <c r="U31">
+        <v>0.0473</v>
+      </c>
+      <c r="V31">
+        <v>0.22</v>
+      </c>
+      <c r="W31">
+        <v>0.036894</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>11.35843122327248</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.1502603860734816</v>
+      </c>
+      <c r="C32">
+        <v>22.62503282478959</v>
+      </c>
+      <c r="D32">
+        <v>25.48563282478959</v>
+      </c>
+      <c r="E32">
+        <v>8.8286</v>
+      </c>
+      <c r="F32">
+        <v>9.0306</v>
+      </c>
+      <c r="G32">
+        <v>6.17</v>
+      </c>
+      <c r="H32">
+        <v>29.9</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>5.13</v>
+      </c>
+      <c r="K32">
+        <v>0.4399999999999995</v>
+      </c>
+      <c r="L32">
+        <v>4.69</v>
+      </c>
+      <c r="M32">
+        <v>0.42714738</v>
+      </c>
+      <c r="N32">
+        <v>4.26285262</v>
+      </c>
+      <c r="O32">
+        <v>0.9378275763999999</v>
+      </c>
+      <c r="P32">
+        <v>3.3250250436</v>
+      </c>
+      <c r="Q32">
+        <v>3.7650250436</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.1988459801049738</v>
+      </c>
+      <c r="T32">
+        <v>1.320326156747008</v>
+      </c>
+      <c r="U32">
+        <v>0.0473</v>
+      </c>
+      <c r="V32">
+        <v>0.22</v>
+      </c>
+      <c r="W32">
+        <v>0.036894</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>10.9798168491634</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.1499774386972914</v>
+      </c>
+      <c r="C33">
+        <v>22.37901942590151</v>
+      </c>
+      <c r="D33">
+        <v>25.54063942590151</v>
+      </c>
+      <c r="E33">
+        <v>9.129620000000001</v>
+      </c>
+      <c r="F33">
+        <v>9.331620000000001</v>
+      </c>
+      <c r="G33">
+        <v>6.17</v>
+      </c>
+      <c r="H33">
+        <v>29.9</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>5.13</v>
+      </c>
+      <c r="K33">
+        <v>0.4399999999999995</v>
+      </c>
+      <c r="L33">
+        <v>4.69</v>
+      </c>
+      <c r="M33">
+        <v>0.4413856260000001</v>
+      </c>
+      <c r="N33">
+        <v>4.248614374000001</v>
+      </c>
+      <c r="O33">
+        <v>0.93469516228</v>
+      </c>
+      <c r="P33">
+        <v>3.31391921172</v>
+      </c>
+      <c r="Q33">
+        <v>3.75391921172</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.2007830415902774</v>
+      </c>
+      <c r="T33">
+        <v>1.336306270365582</v>
+      </c>
+      <c r="U33">
+        <v>0.0473</v>
+      </c>
+      <c r="V33">
+        <v>0.22</v>
+      </c>
+      <c r="W33">
+        <v>0.036894</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>10.6256292088678</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.1496944913211012</v>
+      </c>
+      <c r="C34">
+        <v>22.13324398624724</v>
+      </c>
+      <c r="D34">
+        <v>25.59588398624725</v>
+      </c>
+      <c r="E34">
+        <v>9.43064</v>
+      </c>
+      <c r="F34">
+        <v>9.63264</v>
+      </c>
+      <c r="G34">
+        <v>6.17</v>
+      </c>
+      <c r="H34">
+        <v>29.9</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>5.13</v>
+      </c>
+      <c r="K34">
+        <v>0.4399999999999995</v>
+      </c>
+      <c r="L34">
+        <v>4.69</v>
+      </c>
+      <c r="M34">
+        <v>0.455623872</v>
+      </c>
+      <c r="N34">
+        <v>4.234376128</v>
+      </c>
+      <c r="O34">
+        <v>0.93156274816</v>
+      </c>
+      <c r="P34">
+        <v>3.30281337984</v>
+      </c>
+      <c r="Q34">
+        <v>3.742813379839999</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.2027770754722077</v>
+      </c>
+      <c r="T34">
+        <v>1.35275638732588</v>
+      </c>
+      <c r="U34">
+        <v>0.0473</v>
+      </c>
+      <c r="V34">
+        <v>0.22</v>
+      </c>
+      <c r="W34">
+        <v>0.036894</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>10.29357829609068</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.150389663944911</v>
+      </c>
+      <c r="C35">
+        <v>21.69691924169639</v>
+      </c>
+      <c r="D35">
+        <v>25.46057924169639</v>
+      </c>
+      <c r="E35">
+        <v>9.73166</v>
+      </c>
+      <c r="F35">
+        <v>9.93366</v>
+      </c>
+      <c r="G35">
+        <v>6.17</v>
+      </c>
+      <c r="H35">
+        <v>29.9</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>5.13</v>
+      </c>
+      <c r="K35">
+        <v>0.4399999999999995</v>
+      </c>
+      <c r="L35">
+        <v>4.69</v>
+      </c>
+      <c r="M35">
+        <v>0.5076100259999999</v>
+      </c>
+      <c r="N35">
+        <v>4.182389974</v>
+      </c>
+      <c r="O35">
+        <v>0.92012579428</v>
+      </c>
+      <c r="P35">
+        <v>3.26226417972</v>
+      </c>
+      <c r="Q35">
+        <v>3.70226417972</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.2048306327535985</v>
+      </c>
+      <c r="T35">
+        <v>1.369697552553649</v>
+      </c>
+      <c r="U35">
+        <v>0.0511</v>
+      </c>
+      <c r="V35">
+        <v>0.22</v>
+      </c>
+      <c r="W35">
+        <v>0.039858</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>9.239376213581725</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.1501363565687208</v>
+      </c>
+      <c r="C36">
+        <v>21.44503568148288</v>
+      </c>
+      <c r="D36">
+        <v>25.50971568148288</v>
+      </c>
+      <c r="E36">
+        <v>10.03268</v>
+      </c>
+      <c r="F36">
+        <v>10.23468</v>
+      </c>
+      <c r="G36">
+        <v>6.17</v>
+      </c>
+      <c r="H36">
+        <v>29.9</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>5.13</v>
+      </c>
+      <c r="K36">
+        <v>0.4399999999999995</v>
+      </c>
+      <c r="L36">
+        <v>4.69</v>
+      </c>
+      <c r="M36">
+        <v>0.522992148</v>
+      </c>
+      <c r="N36">
+        <v>4.167007852</v>
+      </c>
+      <c r="O36">
+        <v>0.9167417274399999</v>
+      </c>
+      <c r="P36">
+        <v>3.25026612456</v>
+      </c>
+      <c r="Q36">
+        <v>3.69026612456</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.2069464190435164</v>
+      </c>
+      <c r="T36">
+        <v>1.387152086424684</v>
+      </c>
+      <c r="U36">
+        <v>0.0511</v>
+      </c>
+      <c r="V36">
+        <v>0.22</v>
+      </c>
+      <c r="W36">
+        <v>0.039858</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>8.96762985435873</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.1498830491925306</v>
+      </c>
+      <c r="C37">
+        <v>21.19334214508927</v>
+      </c>
+      <c r="D37">
+        <v>25.55904214508926</v>
+      </c>
+      <c r="E37">
+        <v>10.3337</v>
+      </c>
+      <c r="F37">
+        <v>10.5357</v>
+      </c>
+      <c r="G37">
+        <v>6.17</v>
+      </c>
+      <c r="H37">
+        <v>29.9</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>5.13</v>
+      </c>
+      <c r="K37">
+        <v>0.4399999999999995</v>
+      </c>
+      <c r="L37">
+        <v>4.69</v>
+      </c>
+      <c r="M37">
+        <v>0.53837427</v>
+      </c>
+      <c r="N37">
+        <v>4.15162573</v>
+      </c>
+      <c r="O37">
+        <v>0.9133576605999999</v>
+      </c>
+      <c r="P37">
+        <v>3.2382680694</v>
+      </c>
+      <c r="Q37">
+        <v>3.6782680694</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.2091273064500471</v>
+      </c>
+      <c r="T37">
+        <v>1.405143682876366</v>
+      </c>
+      <c r="U37">
+        <v>0.0511</v>
+      </c>
+      <c r="V37">
+        <v>0.22</v>
+      </c>
+      <c r="W37">
+        <v>0.039858</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>8.711411858519909</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.1496297418163404</v>
+      </c>
+      <c r="C38">
+        <v>20.94183973696088</v>
+      </c>
+      <c r="D38">
+        <v>25.60855973696088</v>
+      </c>
+      <c r="E38">
+        <v>10.63472</v>
+      </c>
+      <c r="F38">
+        <v>10.83672</v>
+      </c>
+      <c r="G38">
+        <v>6.17</v>
+      </c>
+      <c r="H38">
+        <v>29.9</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>5.13</v>
+      </c>
+      <c r="K38">
+        <v>0.4399999999999995</v>
+      </c>
+      <c r="L38">
+        <v>4.69</v>
+      </c>
+      <c r="M38">
+        <v>0.5537563919999999</v>
+      </c>
+      <c r="N38">
+        <v>4.136243608000001</v>
+      </c>
+      <c r="O38">
+        <v>0.9099735937600001</v>
+      </c>
+      <c r="P38">
+        <v>3.226270014240001</v>
+      </c>
+      <c r="Q38">
+        <v>3.66627001424</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.2113763465880318</v>
+      </c>
+      <c r="T38">
+        <v>1.423697516717163</v>
+      </c>
+      <c r="U38">
+        <v>0.0511</v>
+      </c>
+      <c r="V38">
+        <v>0.22</v>
+      </c>
+      <c r="W38">
+        <v>0.039858</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>8.469428195783248</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.1493764344401501</v>
+      </c>
+      <c r="C39">
+        <v>20.69052957011868</v>
+      </c>
+      <c r="D39">
+        <v>25.65826957011868</v>
+      </c>
+      <c r="E39">
+        <v>10.93574</v>
+      </c>
+      <c r="F39">
+        <v>11.13774</v>
+      </c>
+      <c r="G39">
+        <v>6.17</v>
+      </c>
+      <c r="H39">
+        <v>29.9</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>5.13</v>
+      </c>
+      <c r="K39">
+        <v>0.4399999999999995</v>
+      </c>
+      <c r="L39">
+        <v>4.69</v>
+      </c>
+      <c r="M39">
+        <v>0.569138514</v>
+      </c>
+      <c r="N39">
+        <v>4.120861486000001</v>
+      </c>
+      <c r="O39">
+        <v>0.9065895269200001</v>
+      </c>
+      <c r="P39">
+        <v>3.214271959080001</v>
+      </c>
+      <c r="Q39">
+        <v>3.65427195908</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.2136967848256352</v>
+      </c>
+      <c r="T39">
+        <v>1.44284036115608</v>
+      </c>
+      <c r="U39">
+        <v>0.0511</v>
+      </c>
+      <c r="V39">
+        <v>0.22</v>
+      </c>
+      <c r="W39">
+        <v>0.039858</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>8.240524731032348</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.1491231270639599</v>
+      </c>
+      <c r="C40">
+        <v>20.43941276624247</v>
+      </c>
+      <c r="D40">
+        <v>25.70817276624247</v>
+      </c>
+      <c r="E40">
+        <v>11.23676</v>
+      </c>
+      <c r="F40">
+        <v>11.43876</v>
+      </c>
+      <c r="G40">
+        <v>6.17</v>
+      </c>
+      <c r="H40">
+        <v>29.9</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>5.13</v>
+      </c>
+      <c r="K40">
+        <v>0.4399999999999995</v>
+      </c>
+      <c r="L40">
+        <v>4.69</v>
+      </c>
+      <c r="M40">
+        <v>0.584520636</v>
+      </c>
+      <c r="N40">
+        <v>4.105479364000001</v>
+      </c>
+      <c r="O40">
+        <v>0.90320546008</v>
+      </c>
+      <c r="P40">
+        <v>3.202273903920001</v>
+      </c>
+      <c r="Q40">
+        <v>3.64227390392</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.2160920759096128</v>
+      </c>
+      <c r="T40">
+        <v>1.462600716705931</v>
+      </c>
+      <c r="U40">
+        <v>0.0511</v>
+      </c>
+      <c r="V40">
+        <v>0.22</v>
+      </c>
+      <c r="W40">
+        <v>0.039858</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>8.023668817057814</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.1488698196877697</v>
+      </c>
+      <c r="C41">
+        <v>20.18849045575542</v>
+      </c>
+      <c r="D41">
+        <v>25.75827045575542</v>
+      </c>
+      <c r="E41">
+        <v>11.53778</v>
+      </c>
+      <c r="F41">
+        <v>11.73978</v>
+      </c>
+      <c r="G41">
+        <v>6.17</v>
+      </c>
+      <c r="H41">
+        <v>29.9</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>5.13</v>
+      </c>
+      <c r="K41">
+        <v>0.4399999999999995</v>
+      </c>
+      <c r="L41">
+        <v>4.69</v>
+      </c>
+      <c r="M41">
+        <v>0.5999027579999999</v>
+      </c>
+      <c r="N41">
+        <v>4.090097242000001</v>
+      </c>
+      <c r="O41">
+        <v>0.89982139324</v>
+      </c>
+      <c r="P41">
+        <v>3.190275848760001</v>
+      </c>
+      <c r="Q41">
+        <v>3.63027584876</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.2185659011274914</v>
+      </c>
+      <c r="T41">
+        <v>1.483008952765613</v>
+      </c>
+      <c r="U41">
+        <v>0.0511</v>
+      </c>
+      <c r="V41">
+        <v>0.22</v>
+      </c>
+      <c r="W41">
+        <v>0.039858</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>7.817933719184537</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.1492093123115795</v>
+      </c>
+      <c r="C42">
+        <v>19.82037194069263</v>
+      </c>
+      <c r="D42">
+        <v>25.69117194069264</v>
+      </c>
+      <c r="E42">
+        <v>11.8388</v>
+      </c>
+      <c r="F42">
+        <v>12.0408</v>
+      </c>
+      <c r="G42">
+        <v>6.17</v>
+      </c>
+      <c r="H42">
+        <v>29.9</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>5.13</v>
+      </c>
+      <c r="K42">
+        <v>0.4399999999999995</v>
+      </c>
+      <c r="L42">
+        <v>4.69</v>
+      </c>
+      <c r="M42">
+        <v>0.6381624000000001</v>
+      </c>
+      <c r="N42">
+        <v>4.051837600000001</v>
+      </c>
+      <c r="O42">
+        <v>0.8914042720000001</v>
+      </c>
+      <c r="P42">
+        <v>3.160433328000001</v>
+      </c>
+      <c r="Q42">
+        <v>3.600433328</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.2211221871859659</v>
+      </c>
+      <c r="T42">
+        <v>1.504097463360617</v>
+      </c>
+      <c r="U42">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V42">
+        <v>0.22</v>
+      </c>
+      <c r="W42">
+        <v>0.04134000000000001</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>7.349226466491915</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.1489708249353893</v>
+      </c>
+      <c r="C43">
+        <v>19.56645082605694</v>
+      </c>
+      <c r="D43">
+        <v>25.73827082605694</v>
+      </c>
+      <c r="E43">
+        <v>12.13982</v>
+      </c>
+      <c r="F43">
+        <v>12.34182</v>
+      </c>
+      <c r="G43">
+        <v>6.17</v>
+      </c>
+      <c r="H43">
+        <v>29.9</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>5.13</v>
+      </c>
+      <c r="K43">
+        <v>0.4399999999999995</v>
+      </c>
+      <c r="L43">
+        <v>4.69</v>
+      </c>
+      <c r="M43">
+        <v>0.6541164600000001</v>
+      </c>
+      <c r="N43">
+        <v>4.03588354</v>
+      </c>
+      <c r="O43">
+        <v>0.8878943788</v>
+      </c>
+      <c r="P43">
+        <v>3.1479891612</v>
+      </c>
+      <c r="Q43">
+        <v>3.5879891612</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.2237651270091344</v>
+      </c>
+      <c r="T43">
+        <v>1.525900838721554</v>
+      </c>
+      <c r="U43">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V43">
+        <v>0.22</v>
+      </c>
+      <c r="W43">
+        <v>0.04134000000000001</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>7.169977040479917</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.1487323375591991</v>
+      </c>
+      <c r="C44">
+        <v>19.31270271864966</v>
+      </c>
+      <c r="D44">
+        <v>25.78554271864966</v>
+      </c>
+      <c r="E44">
+        <v>12.44084</v>
+      </c>
+      <c r="F44">
+        <v>12.64284</v>
+      </c>
+      <c r="G44">
+        <v>6.17</v>
+      </c>
+      <c r="H44">
+        <v>29.9</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>5.13</v>
+      </c>
+      <c r="K44">
+        <v>0.4399999999999995</v>
+      </c>
+      <c r="L44">
+        <v>4.69</v>
+      </c>
+      <c r="M44">
+        <v>0.67007052</v>
+      </c>
+      <c r="N44">
+        <v>4.01992948</v>
+      </c>
+      <c r="O44">
+        <v>0.8843844855999999</v>
+      </c>
+      <c r="P44">
+        <v>3.1355449944</v>
+      </c>
+      <c r="Q44">
+        <v>3.5755449944</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.2264992026882743</v>
+      </c>
+      <c r="T44">
+        <v>1.548456054612178</v>
+      </c>
+      <c r="U44">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V44">
+        <v>0.22</v>
+      </c>
+      <c r="W44">
+        <v>0.04134000000000001</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>6.999263301420871</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.1484938501830089</v>
+      </c>
+      <c r="C45">
+        <v>19.05912857347992</v>
+      </c>
+      <c r="D45">
+        <v>25.83298857347992</v>
+      </c>
+      <c r="E45">
+        <v>12.74186</v>
+      </c>
+      <c r="F45">
+        <v>12.94386</v>
+      </c>
+      <c r="G45">
+        <v>6.17</v>
+      </c>
+      <c r="H45">
+        <v>29.9</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>5.13</v>
+      </c>
+      <c r="K45">
+        <v>0.4399999999999995</v>
+      </c>
+      <c r="L45">
+        <v>4.69</v>
+      </c>
+      <c r="M45">
+        <v>0.6860245800000001</v>
+      </c>
+      <c r="N45">
+        <v>4.003975420000001</v>
+      </c>
+      <c r="O45">
+        <v>0.8808745924</v>
+      </c>
+      <c r="P45">
+        <v>3.123100827600001</v>
+      </c>
+      <c r="Q45">
+        <v>3.5631008276</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.229329210847384</v>
+      </c>
+      <c r="T45">
+        <v>1.571802681586683</v>
+      </c>
+      <c r="U45">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V45">
+        <v>0.22</v>
+      </c>
+      <c r="W45">
+        <v>0.04134000000000001</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>6.836489736271549</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.1482553628068187</v>
+      </c>
+      <c r="C46">
+        <v>18.80572935259868</v>
+      </c>
+      <c r="D46">
+        <v>25.88060935259868</v>
+      </c>
+      <c r="E46">
+        <v>13.04288</v>
+      </c>
+      <c r="F46">
+        <v>13.24488</v>
+      </c>
+      <c r="G46">
+        <v>6.17</v>
+      </c>
+      <c r="H46">
+        <v>29.9</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>5.13</v>
+      </c>
+      <c r="K46">
+        <v>0.4399999999999995</v>
+      </c>
+      <c r="L46">
+        <v>4.69</v>
+      </c>
+      <c r="M46">
+        <v>0.7019786400000001</v>
+      </c>
+      <c r="N46">
+        <v>3.98802136</v>
+      </c>
+      <c r="O46">
+        <v>0.8773646991999999</v>
+      </c>
+      <c r="P46">
+        <v>3.1106566608</v>
+      </c>
+      <c r="Q46">
+        <v>3.5506566608</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.2322602907264619</v>
+      </c>
+      <c r="T46">
+        <v>1.595983116667422</v>
+      </c>
+      <c r="U46">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V46">
+        <v>0.22</v>
+      </c>
+      <c r="W46">
+        <v>0.04134000000000001</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>6.681114969538104</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.1480168754306285</v>
+      </c>
+      <c r="C47">
+        <v>18.55250602516382</v>
+      </c>
+      <c r="D47">
+        <v>25.92840602516382</v>
+      </c>
+      <c r="E47">
+        <v>13.3439</v>
+      </c>
+      <c r="F47">
+        <v>13.5459</v>
+      </c>
+      <c r="G47">
+        <v>6.17</v>
+      </c>
+      <c r="H47">
+        <v>29.9</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>5.13</v>
+      </c>
+      <c r="K47">
+        <v>0.4399999999999995</v>
+      </c>
+      <c r="L47">
+        <v>4.69</v>
+      </c>
+      <c r="M47">
+        <v>0.7179327000000001</v>
+      </c>
+      <c r="N47">
+        <v>3.9720673</v>
+      </c>
+      <c r="O47">
+        <v>0.873854806</v>
+      </c>
+      <c r="P47">
+        <v>3.098212494</v>
+      </c>
+      <c r="Q47">
+        <v>3.538212494</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.2352979553284154</v>
+      </c>
+      <c r="T47">
+        <v>1.62104284029655</v>
+      </c>
+      <c r="U47">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V47">
+        <v>0.22</v>
+      </c>
+      <c r="W47">
+        <v>0.04134000000000001</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>6.532645747992813</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.1477783880544382</v>
+      </c>
+      <c r="C48">
+        <v>18.29945956750591</v>
+      </c>
+      <c r="D48">
+        <v>25.97637956750591</v>
+      </c>
+      <c r="E48">
+        <v>13.64492</v>
+      </c>
+      <c r="F48">
+        <v>13.84692</v>
+      </c>
+      <c r="G48">
+        <v>6.17</v>
+      </c>
+      <c r="H48">
+        <v>29.9</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>5.13</v>
+      </c>
+      <c r="K48">
+        <v>0.4399999999999995</v>
+      </c>
+      <c r="L48">
+        <v>4.69</v>
+      </c>
+      <c r="M48">
+        <v>0.7338867600000001</v>
+      </c>
+      <c r="N48">
+        <v>3.956113240000001</v>
+      </c>
+      <c r="O48">
+        <v>0.8703449128</v>
+      </c>
+      <c r="P48">
+        <v>3.0857683272</v>
+      </c>
+      <c r="Q48">
+        <v>3.5257683272</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.2384481260267375</v>
+      </c>
+      <c r="T48">
+        <v>1.647030701837868</v>
+      </c>
+      <c r="U48">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V48">
+        <v>0.22</v>
+      </c>
+      <c r="W48">
+        <v>0.04134000000000001</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>6.390631709992969</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.147539900678248</v>
+      </c>
+      <c r="C49">
+        <v>18.04659096319465</v>
+      </c>
+      <c r="D49">
+        <v>26.02453096319464</v>
+      </c>
+      <c r="E49">
+        <v>13.94594</v>
+      </c>
+      <c r="F49">
+        <v>14.14794</v>
+      </c>
+      <c r="G49">
+        <v>6.17</v>
+      </c>
+      <c r="H49">
+        <v>29.9</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>5.13</v>
+      </c>
+      <c r="K49">
+        <v>0.4399999999999995</v>
+      </c>
+      <c r="L49">
+        <v>4.69</v>
+      </c>
+      <c r="M49">
+        <v>0.7498408200000001</v>
+      </c>
+      <c r="N49">
+        <v>3.94015918</v>
+      </c>
+      <c r="O49">
+        <v>0.8668350196</v>
+      </c>
+      <c r="P49">
+        <v>3.0733241604</v>
+      </c>
+      <c r="Q49">
+        <v>3.5133241604</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.241717171091034</v>
+      </c>
+      <c r="T49">
+        <v>1.673999237399614</v>
+      </c>
+      <c r="U49">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V49">
+        <v>0.22</v>
+      </c>
+      <c r="W49">
+        <v>0.04134000000000001</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>6.254660822546311</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.1480502133020578</v>
+      </c>
+      <c r="C50">
+        <v>17.64275397246757</v>
+      </c>
+      <c r="D50">
+        <v>25.92171397246758</v>
+      </c>
+      <c r="E50">
+        <v>14.24696</v>
+      </c>
+      <c r="F50">
+        <v>14.44896</v>
+      </c>
+      <c r="G50">
+        <v>6.17</v>
+      </c>
+      <c r="H50">
+        <v>29.9</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>5.13</v>
+      </c>
+      <c r="K50">
+        <v>0.4399999999999995</v>
+      </c>
+      <c r="L50">
+        <v>4.69</v>
+      </c>
+      <c r="M50">
+        <v>0.7946928</v>
+      </c>
+      <c r="N50">
+        <v>3.8953072</v>
+      </c>
+      <c r="O50">
+        <v>0.8569675839999999</v>
+      </c>
+      <c r="P50">
+        <v>3.038339616</v>
+      </c>
+      <c r="Q50">
+        <v>3.478339616</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.2451119486578034</v>
+      </c>
+      <c r="T50">
+        <v>1.702005024329119</v>
+      </c>
+      <c r="U50">
+        <v>0.055</v>
+      </c>
+      <c r="V50">
+        <v>0.22</v>
+      </c>
+      <c r="W50">
+        <v>0.0429</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>5.901651556425326</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.1478273259258676</v>
+      </c>
+      <c r="C51">
+        <v>17.38654087290406</v>
+      </c>
+      <c r="D51">
+        <v>25.96652087290406</v>
+      </c>
+      <c r="E51">
+        <v>14.54798</v>
+      </c>
+      <c r="F51">
+        <v>14.74998</v>
+      </c>
+      <c r="G51">
+        <v>6.17</v>
+      </c>
+      <c r="H51">
+        <v>29.9</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>5.13</v>
+      </c>
+      <c r="K51">
+        <v>0.4399999999999995</v>
+      </c>
+      <c r="L51">
+        <v>4.69</v>
+      </c>
+      <c r="M51">
+        <v>0.8112489000000001</v>
+      </c>
+      <c r="N51">
+        <v>3.878751100000001</v>
+      </c>
+      <c r="O51">
+        <v>0.853325242</v>
+      </c>
+      <c r="P51">
+        <v>3.025425858000001</v>
+      </c>
+      <c r="Q51">
+        <v>3.465425858</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.2486398547566031</v>
+      </c>
+      <c r="T51">
+        <v>1.731109077412722</v>
+      </c>
+      <c r="U51">
+        <v>0.055</v>
+      </c>
+      <c r="V51">
+        <v>0.22</v>
+      </c>
+      <c r="W51">
+        <v>0.0429</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>5.78120968792685</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.1476044385496774</v>
+      </c>
+      <c r="C52">
+        <v>17.13048294322395</v>
+      </c>
+      <c r="D52">
+        <v>26.01148294322395</v>
+      </c>
+      <c r="E52">
+        <v>14.849</v>
+      </c>
+      <c r="F52">
+        <v>15.051</v>
+      </c>
+      <c r="G52">
+        <v>6.17</v>
+      </c>
+      <c r="H52">
+        <v>29.9</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>5.13</v>
+      </c>
+      <c r="K52">
+        <v>0.4399999999999995</v>
+      </c>
+      <c r="L52">
+        <v>4.69</v>
+      </c>
+      <c r="M52">
+        <v>0.827805</v>
+      </c>
+      <c r="N52">
+        <v>3.862195</v>
+      </c>
+      <c r="O52">
+        <v>0.8496828999999999</v>
+      </c>
+      <c r="P52">
+        <v>3.0125121</v>
+      </c>
+      <c r="Q52">
+        <v>3.4525121</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.2523088770993548</v>
+      </c>
+      <c r="T52">
+        <v>1.76137729261967</v>
+      </c>
+      <c r="U52">
+        <v>0.055</v>
+      </c>
+      <c r="V52">
+        <v>0.22</v>
+      </c>
+      <c r="W52">
+        <v>0.0429</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>5.665585494168313</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.1473815511734872</v>
+      </c>
+      <c r="C53">
+        <v>16.87458099087398</v>
+      </c>
+      <c r="D53">
+        <v>26.05660099087398</v>
+      </c>
+      <c r="E53">
+        <v>15.15002</v>
+      </c>
+      <c r="F53">
+        <v>15.35202</v>
+      </c>
+      <c r="G53">
+        <v>6.17</v>
+      </c>
+      <c r="H53">
+        <v>29.9</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>5.13</v>
+      </c>
+      <c r="K53">
+        <v>0.4399999999999995</v>
+      </c>
+      <c r="L53">
+        <v>4.69</v>
+      </c>
+      <c r="M53">
+        <v>0.8443611</v>
+      </c>
+      <c r="N53">
+        <v>3.8456389</v>
+      </c>
+      <c r="O53">
+        <v>0.846040558</v>
+      </c>
+      <c r="P53">
+        <v>2.999598342000001</v>
+      </c>
+      <c r="Q53">
+        <v>3.439598342</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.2561276554560963</v>
+      </c>
+      <c r="T53">
+        <v>1.792880945182003</v>
+      </c>
+      <c r="U53">
+        <v>0.055</v>
+      </c>
+      <c r="V53">
+        <v>0.22</v>
+      </c>
+      <c r="W53">
+        <v>0.0429</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>5.554495582517954</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.1471586637972969</v>
+      </c>
+      <c r="C54">
+        <v>16.6188358289128</v>
+      </c>
+      <c r="D54">
+        <v>26.1018758289128</v>
+      </c>
+      <c r="E54">
+        <v>15.45104</v>
+      </c>
+      <c r="F54">
+        <v>15.65304</v>
+      </c>
+      <c r="G54">
+        <v>6.17</v>
+      </c>
+      <c r="H54">
+        <v>29.9</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>5.13</v>
+      </c>
+      <c r="K54">
+        <v>0.4399999999999995</v>
+      </c>
+      <c r="L54">
+        <v>4.69</v>
+      </c>
+      <c r="M54">
+        <v>0.8609172</v>
+      </c>
+      <c r="N54">
+        <v>3.8290828</v>
+      </c>
+      <c r="O54">
+        <v>0.842398216</v>
+      </c>
+      <c r="P54">
+        <v>2.986684584</v>
+      </c>
+      <c r="Q54">
+        <v>3.426684584</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.260105549577702</v>
+      </c>
+      <c r="T54">
+        <v>1.825697249934433</v>
+      </c>
+      <c r="U54">
+        <v>0.055</v>
+      </c>
+      <c r="V54">
+        <v>0.22</v>
+      </c>
+      <c r="W54">
+        <v>0.0429</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>5.447678359777224</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.1469357764211067</v>
+      </c>
+      <c r="C55">
+        <v>16.36324827605986</v>
+      </c>
+      <c r="D55">
+        <v>26.14730827605986</v>
+      </c>
+      <c r="E55">
+        <v>15.75206</v>
+      </c>
+      <c r="F55">
+        <v>15.95406</v>
+      </c>
+      <c r="G55">
+        <v>6.17</v>
+      </c>
+      <c r="H55">
+        <v>29.9</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>5.13</v>
+      </c>
+      <c r="K55">
+        <v>0.4399999999999995</v>
+      </c>
+      <c r="L55">
+        <v>4.69</v>
+      </c>
+      <c r="M55">
+        <v>0.8774733</v>
+      </c>
+      <c r="N55">
+        <v>3.8125267</v>
+      </c>
+      <c r="O55">
+        <v>0.838755874</v>
+      </c>
+      <c r="P55">
+        <v>2.973770826</v>
+      </c>
+      <c r="Q55">
+        <v>3.413770826</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.2642527157895888</v>
+      </c>
+      <c r="T55">
+        <v>1.859909993186967</v>
+      </c>
+      <c r="U55">
+        <v>0.055</v>
+      </c>
+      <c r="V55">
+        <v>0.22</v>
+      </c>
+      <c r="W55">
+        <v>0.0429</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>5.344891975630484</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.1467128890449165</v>
+      </c>
+      <c r="C56">
+        <v>16.10781915674472</v>
+      </c>
+      <c r="D56">
+        <v>26.19289915674472</v>
+      </c>
+      <c r="E56">
+        <v>16.05308</v>
+      </c>
+      <c r="F56">
+        <v>16.25508</v>
+      </c>
+      <c r="G56">
+        <v>6.17</v>
+      </c>
+      <c r="H56">
+        <v>29.9</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>5.13</v>
+      </c>
+      <c r="K56">
+        <v>0.4399999999999995</v>
+      </c>
+      <c r="L56">
+        <v>4.69</v>
+      </c>
+      <c r="M56">
+        <v>0.8940294</v>
+      </c>
+      <c r="N56">
+        <v>3.7959706</v>
+      </c>
+      <c r="O56">
+        <v>0.8351135319999999</v>
+      </c>
+      <c r="P56">
+        <v>2.960857068000001</v>
+      </c>
+      <c r="Q56">
+        <v>3.400857068</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.2685801935759055</v>
+      </c>
+      <c r="T56">
+        <v>1.895610247015697</v>
+      </c>
+      <c r="U56">
+        <v>0.055</v>
+      </c>
+      <c r="V56">
+        <v>0.22</v>
+      </c>
+      <c r="W56">
+        <v>0.0429</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>5.24591249460029</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.1464900016687263</v>
+      </c>
+      <c r="C57">
+        <v>15.85254930115694</v>
+      </c>
+      <c r="D57">
+        <v>26.23864930115694</v>
+      </c>
+      <c r="E57">
+        <v>16.3541</v>
+      </c>
+      <c r="F57">
+        <v>16.5561</v>
+      </c>
+      <c r="G57">
+        <v>6.17</v>
+      </c>
+      <c r="H57">
+        <v>29.9</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>5.13</v>
+      </c>
+      <c r="K57">
+        <v>0.4399999999999995</v>
+      </c>
+      <c r="L57">
+        <v>4.69</v>
+      </c>
+      <c r="M57">
+        <v>0.9105855</v>
+      </c>
+      <c r="N57">
+        <v>3.779414500000001</v>
+      </c>
+      <c r="O57">
+        <v>0.83147119</v>
+      </c>
+      <c r="P57">
+        <v>2.94794331</v>
+      </c>
+      <c r="Q57">
+        <v>3.38794331</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.2731000037082807</v>
+      </c>
+      <c r="T57">
+        <v>1.932897178792372</v>
+      </c>
+      <c r="U57">
+        <v>0.055</v>
+      </c>
+      <c r="V57">
+        <v>0.22</v>
+      </c>
+      <c r="W57">
+        <v>0.0429</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>5.150532267425739</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.1462671142925361</v>
+      </c>
+      <c r="C58">
+        <v>15.5974395452965</v>
+      </c>
+      <c r="D58">
+        <v>26.28455954529651</v>
+      </c>
+      <c r="E58">
+        <v>16.65512</v>
+      </c>
+      <c r="F58">
+        <v>16.85712</v>
+      </c>
+      <c r="G58">
+        <v>6.17</v>
+      </c>
+      <c r="H58">
+        <v>29.9</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>5.13</v>
+      </c>
+      <c r="K58">
+        <v>0.4399999999999995</v>
+      </c>
+      <c r="L58">
+        <v>4.69</v>
+      </c>
+      <c r="M58">
+        <v>0.9271416000000001</v>
+      </c>
+      <c r="N58">
+        <v>3.7628584</v>
+      </c>
+      <c r="O58">
+        <v>0.827828848</v>
+      </c>
+      <c r="P58">
+        <v>2.935029552</v>
+      </c>
+      <c r="Q58">
+        <v>3.375029552</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.2778252597557639</v>
+      </c>
+      <c r="T58">
+        <v>1.97187897110435</v>
+      </c>
+      <c r="U58">
+        <v>0.055</v>
+      </c>
+      <c r="V58">
+        <v>0.22</v>
+      </c>
+      <c r="W58">
+        <v>0.0429</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>5.058558476935993</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.1460442269163459</v>
+      </c>
+      <c r="C59">
+        <v>15.34249073102468</v>
+      </c>
+      <c r="D59">
+        <v>26.33063073102468</v>
+      </c>
+      <c r="E59">
+        <v>16.95614</v>
+      </c>
+      <c r="F59">
+        <v>17.15814</v>
+      </c>
+      <c r="G59">
+        <v>6.17</v>
+      </c>
+      <c r="H59">
+        <v>29.9</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>5.13</v>
+      </c>
+      <c r="K59">
+        <v>0.4399999999999995</v>
+      </c>
+      <c r="L59">
+        <v>4.69</v>
+      </c>
+      <c r="M59">
+        <v>0.9436977000000002</v>
+      </c>
+      <c r="N59">
+        <v>3.7463023</v>
+      </c>
+      <c r="O59">
+        <v>0.8241865059999999</v>
+      </c>
+      <c r="P59">
+        <v>2.922115794</v>
+      </c>
+      <c r="Q59">
+        <v>3.362115794</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.2827702951542928</v>
+      </c>
+      <c r="T59">
+        <v>2.012673870035489</v>
+      </c>
+      <c r="U59">
+        <v>0.055</v>
+      </c>
+      <c r="V59">
+        <v>0.22</v>
+      </c>
+      <c r="W59">
+        <v>0.0429</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>4.969811836989747</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.1458213395401557</v>
+      </c>
+      <c r="C60">
+        <v>15.08770370611552</v>
+      </c>
+      <c r="D60">
+        <v>26.37686370611552</v>
+      </c>
+      <c r="E60">
+        <v>17.25716</v>
+      </c>
+      <c r="F60">
+        <v>17.45916</v>
+      </c>
+      <c r="G60">
+        <v>6.17</v>
+      </c>
+      <c r="H60">
+        <v>29.9</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>5.13</v>
+      </c>
+      <c r="K60">
+        <v>0.4399999999999995</v>
+      </c>
+      <c r="L60">
+        <v>4.69</v>
+      </c>
+      <c r="M60">
+        <v>0.9602538</v>
+      </c>
+      <c r="N60">
+        <v>3.7297462</v>
+      </c>
+      <c r="O60">
+        <v>0.820544164</v>
+      </c>
+      <c r="P60">
+        <v>2.909202036</v>
+      </c>
+      <c r="Q60">
+        <v>3.349202035999999</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.2879508084289421</v>
+      </c>
+      <c r="T60">
+        <v>2.055411383201444</v>
+      </c>
+      <c r="U60">
+        <v>0.055</v>
+      </c>
+      <c r="V60">
+        <v>0.22</v>
+      </c>
+      <c r="W60">
+        <v>0.0429</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>4.884125426007166</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.1455984521639654</v>
+      </c>
+      <c r="C61">
+        <v>14.83307932430783</v>
+      </c>
+      <c r="D61">
+        <v>26.42325932430783</v>
+      </c>
+      <c r="E61">
+        <v>17.55818</v>
+      </c>
+      <c r="F61">
+        <v>17.76018</v>
+      </c>
+      <c r="G61">
+        <v>6.17</v>
+      </c>
+      <c r="H61">
+        <v>29.9</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>5.13</v>
+      </c>
+      <c r="K61">
+        <v>0.4399999999999995</v>
+      </c>
+      <c r="L61">
+        <v>4.69</v>
+      </c>
+      <c r="M61">
+        <v>0.9768098999999999</v>
+      </c>
+      <c r="N61">
+        <v>3.7131901</v>
+      </c>
+      <c r="O61">
+        <v>0.8169018219999999</v>
+      </c>
+      <c r="P61">
+        <v>2.896288278</v>
+      </c>
+      <c r="Q61">
+        <v>3.336288278</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.2933840296682084</v>
+      </c>
+      <c r="T61">
+        <v>2.100233653107202</v>
+      </c>
+      <c r="U61">
+        <v>0.055</v>
+      </c>
+      <c r="V61">
+        <v>0.22</v>
+      </c>
+      <c r="W61">
+        <v>0.0429</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>4.801343639125689</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.1453755647877752</v>
+      </c>
+      <c r="C62">
+        <v>14.57861844535775</v>
+      </c>
+      <c r="D62">
+        <v>26.46981844535776</v>
+      </c>
+      <c r="E62">
+        <v>17.8592</v>
+      </c>
+      <c r="F62">
+        <v>18.0612</v>
+      </c>
+      <c r="G62">
+        <v>6.17</v>
+      </c>
+      <c r="H62">
+        <v>29.9</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>5.13</v>
+      </c>
+      <c r="K62">
+        <v>0.4399999999999995</v>
+      </c>
+      <c r="L62">
+        <v>4.69</v>
+      </c>
+      <c r="M62">
+        <v>0.993366</v>
+      </c>
+      <c r="N62">
+        <v>3.696634</v>
+      </c>
+      <c r="O62">
+        <v>0.81325948</v>
+      </c>
+      <c r="P62">
+        <v>2.88337452</v>
+      </c>
+      <c r="Q62">
+        <v>3.32337452</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.2990889119694381</v>
+      </c>
+      <c r="T62">
+        <v>2.147297036508249</v>
+      </c>
+      <c r="U62">
+        <v>0.055</v>
+      </c>
+      <c r="V62">
+        <v>0.22</v>
+      </c>
+      <c r="W62">
+        <v>0.0429</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>4.721321245140262</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.145152677411585</v>
+      </c>
+      <c r="C63">
+        <v>14.32432193509189</v>
+      </c>
+      <c r="D63">
+        <v>26.51654193509189</v>
+      </c>
+      <c r="E63">
+        <v>18.16022</v>
+      </c>
+      <c r="F63">
+        <v>18.36222</v>
+      </c>
+      <c r="G63">
+        <v>6.17</v>
+      </c>
+      <c r="H63">
+        <v>29.9</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>5.13</v>
+      </c>
+      <c r="K63">
+        <v>0.4399999999999995</v>
+      </c>
+      <c r="L63">
+        <v>4.69</v>
+      </c>
+      <c r="M63">
+        <v>1.0099221</v>
+      </c>
+      <c r="N63">
+        <v>3.680077900000001</v>
+      </c>
+      <c r="O63">
+        <v>0.809617138</v>
+      </c>
+      <c r="P63">
+        <v>2.870460762</v>
+      </c>
+      <c r="Q63">
+        <v>3.310460762</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.3050863523373975</v>
+      </c>
+      <c r="T63">
+        <v>2.196773926750375</v>
+      </c>
+      <c r="U63">
+        <v>0.055</v>
+      </c>
+      <c r="V63">
+        <v>0.22</v>
+      </c>
+      <c r="W63">
+        <v>0.0429</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>4.643922536203535</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.1449297900353948</v>
+      </c>
+      <c r="C64">
+        <v>14.0701906654609</v>
+      </c>
+      <c r="D64">
+        <v>26.5634306654609</v>
+      </c>
+      <c r="E64">
+        <v>18.46124</v>
+      </c>
+      <c r="F64">
+        <v>18.66324</v>
+      </c>
+      <c r="G64">
+        <v>6.17</v>
+      </c>
+      <c r="H64">
+        <v>29.9</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>5.13</v>
+      </c>
+      <c r="K64">
+        <v>0.4399999999999995</v>
+      </c>
+      <c r="L64">
+        <v>4.69</v>
+      </c>
+      <c r="M64">
+        <v>1.0264782</v>
+      </c>
+      <c r="N64">
+        <v>3.6635218</v>
+      </c>
+      <c r="O64">
+        <v>0.805974796</v>
+      </c>
+      <c r="P64">
+        <v>2.857547004</v>
+      </c>
+      <c r="Q64">
+        <v>3.297547004</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.3113994474615653</v>
+      </c>
+      <c r="T64">
+        <v>2.248854863847349</v>
+      </c>
+      <c r="U64">
+        <v>0.055</v>
+      </c>
+      <c r="V64">
+        <v>0.22</v>
+      </c>
+      <c r="W64">
+        <v>0.0429</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>4.569020559813155</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.1465742226592046</v>
+      </c>
+      <c r="C65">
+        <v>13.42708322117888</v>
+      </c>
+      <c r="D65">
+        <v>26.22134322117888</v>
+      </c>
+      <c r="E65">
+        <v>18.76226</v>
+      </c>
+      <c r="F65">
+        <v>18.96426</v>
+      </c>
+      <c r="G65">
+        <v>6.17</v>
+      </c>
+      <c r="H65">
+        <v>29.9</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>5.13</v>
+      </c>
+      <c r="K65">
+        <v>0.4399999999999995</v>
+      </c>
+      <c r="L65">
+        <v>4.69</v>
+      </c>
+      <c r="M65">
+        <v>1.115098488</v>
+      </c>
+      <c r="N65">
+        <v>3.574901512</v>
+      </c>
+      <c r="O65">
+        <v>0.78647833264</v>
+      </c>
+      <c r="P65">
+        <v>2.788423179360001</v>
+      </c>
+      <c r="Q65">
+        <v>3.22842317936</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.3180537909708233</v>
+      </c>
+      <c r="T65">
+        <v>2.303750986733349</v>
+      </c>
+      <c r="U65">
+        <v>0.05880000000000001</v>
+      </c>
+      <c r="V65">
+        <v>0.22</v>
+      </c>
+      <c r="W65">
+        <v>0.04586400000000001</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>4.205906518994401</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.1463809752830144</v>
+      </c>
+      <c r="C66">
+        <v>13.16580645321677</v>
+      </c>
+      <c r="D66">
+        <v>26.26108645321677</v>
+      </c>
+      <c r="E66">
+        <v>19.06328</v>
+      </c>
+      <c r="F66">
+        <v>19.26528</v>
+      </c>
+      <c r="G66">
+        <v>6.17</v>
+      </c>
+      <c r="H66">
+        <v>29.9</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>5.13</v>
+      </c>
+      <c r="K66">
+        <v>0.4399999999999995</v>
+      </c>
+      <c r="L66">
+        <v>4.69</v>
+      </c>
+      <c r="M66">
+        <v>1.132798464</v>
+      </c>
+      <c r="N66">
+        <v>3.557201536</v>
+      </c>
+      <c r="O66">
+        <v>0.7825843379199999</v>
+      </c>
+      <c r="P66">
+        <v>2.77461719808</v>
+      </c>
+      <c r="Q66">
+        <v>3.21461719808</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.3250778202305955</v>
+      </c>
+      <c r="T66">
+        <v>2.361696894224127</v>
+      </c>
+      <c r="U66">
+        <v>0.05880000000000001</v>
+      </c>
+      <c r="V66">
+        <v>0.22</v>
+      </c>
+      <c r="W66">
+        <v>0.04586400000000001</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>4.140189229635113</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.1461877279068242</v>
+      </c>
+      <c r="C67">
+        <v>12.90465034438117</v>
+      </c>
+      <c r="D67">
+        <v>26.30095034438117</v>
+      </c>
+      <c r="E67">
+        <v>19.3643</v>
+      </c>
+      <c r="F67">
+        <v>19.5663</v>
+      </c>
+      <c r="G67">
+        <v>6.17</v>
+      </c>
+      <c r="H67">
+        <v>29.9</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>5.13</v>
+      </c>
+      <c r="K67">
+        <v>0.4399999999999995</v>
+      </c>
+      <c r="L67">
+        <v>4.69</v>
+      </c>
+      <c r="M67">
+        <v>1.15049844</v>
+      </c>
+      <c r="N67">
+        <v>3.53950156</v>
+      </c>
+      <c r="O67">
+        <v>0.7786903432</v>
+      </c>
+      <c r="P67">
+        <v>2.7608112168</v>
+      </c>
+      <c r="Q67">
+        <v>3.2008112168</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.3325032225909262</v>
+      </c>
+      <c r="T67">
+        <v>2.422953996428663</v>
+      </c>
+      <c r="U67">
+        <v>0.05880000000000001</v>
+      </c>
+      <c r="V67">
+        <v>0.22</v>
+      </c>
+      <c r="W67">
+        <v>0.04586400000000001</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>4.076494010717649</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.145994480530634</v>
+      </c>
+      <c r="C68">
+        <v>12.64361544498309</v>
+      </c>
+      <c r="D68">
+        <v>26.34093544498309</v>
+      </c>
+      <c r="E68">
+        <v>19.66532</v>
+      </c>
+      <c r="F68">
+        <v>19.86732</v>
+      </c>
+      <c r="G68">
+        <v>6.17</v>
+      </c>
+      <c r="H68">
+        <v>29.9</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>5.13</v>
+      </c>
+      <c r="K68">
+        <v>0.4399999999999995</v>
+      </c>
+      <c r="L68">
+        <v>4.69</v>
+      </c>
+      <c r="M68">
+        <v>1.168198416</v>
+      </c>
+      <c r="N68">
+        <v>3.521801584</v>
+      </c>
+      <c r="O68">
+        <v>0.77479634848</v>
+      </c>
+      <c r="P68">
+        <v>2.747005235520001</v>
+      </c>
+      <c r="Q68">
+        <v>3.18700523552</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.3403654133253941</v>
+      </c>
+      <c r="T68">
+        <v>2.487814457586408</v>
+      </c>
+      <c r="U68">
+        <v>0.05880000000000001</v>
+      </c>
+      <c r="V68">
+        <v>0.22</v>
+      </c>
+      <c r="W68">
+        <v>0.04586400000000001</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>4.014728949949202</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.1479961531544438</v>
+      </c>
+      <c r="C69">
+        <v>11.93422743744175</v>
+      </c>
+      <c r="D69">
+        <v>25.93256743744175</v>
+      </c>
+      <c r="E69">
+        <v>19.96634</v>
+      </c>
+      <c r="F69">
+        <v>20.16834</v>
+      </c>
+      <c r="G69">
+        <v>6.17</v>
+      </c>
+      <c r="H69">
+        <v>29.9</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>5.13</v>
+      </c>
+      <c r="K69">
+        <v>0.4399999999999995</v>
+      </c>
+      <c r="L69">
+        <v>4.69</v>
+      </c>
+      <c r="M69">
+        <v>1.27060542</v>
+      </c>
+      <c r="N69">
+        <v>3.419394580000001</v>
+      </c>
+      <c r="O69">
+        <v>0.7522668076</v>
+      </c>
+      <c r="P69">
+        <v>2.667127772400001</v>
+      </c>
+      <c r="Q69">
+        <v>3.1071277724</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.3487041004680114</v>
+      </c>
+      <c r="T69">
+        <v>2.556605855784015</v>
+      </c>
+      <c r="U69">
+        <v>0.063</v>
+      </c>
+      <c r="V69">
+        <v>0.22</v>
+      </c>
+      <c r="W69">
+        <v>0.04914</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>3.691153780848818</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.1478356657782535</v>
+      </c>
+      <c r="C70">
+        <v>11.66548152855858</v>
+      </c>
+      <c r="D70">
+        <v>25.96484152855858</v>
+      </c>
+      <c r="E70">
+        <v>20.26736</v>
+      </c>
+      <c r="F70">
+        <v>20.46936</v>
+      </c>
+      <c r="G70">
+        <v>6.17</v>
+      </c>
+      <c r="H70">
+        <v>29.9</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>5.13</v>
+      </c>
+      <c r="K70">
+        <v>0.4399999999999995</v>
+      </c>
+      <c r="L70">
+        <v>4.69</v>
+      </c>
+      <c r="M70">
+        <v>1.28956968</v>
+      </c>
+      <c r="N70">
+        <v>3.40043032</v>
+      </c>
+      <c r="O70">
+        <v>0.7480946704</v>
+      </c>
+      <c r="P70">
+        <v>2.6523356496</v>
+      </c>
+      <c r="Q70">
+        <v>3.0923356496</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.3575639555570423</v>
+      </c>
+      <c r="T70">
+        <v>2.629696716368974</v>
+      </c>
+      <c r="U70">
+        <v>0.063</v>
+      </c>
+      <c r="V70">
+        <v>0.22</v>
+      </c>
+      <c r="W70">
+        <v>0.04914</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>3.636872107601041</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.1476751784020633</v>
+      </c>
+      <c r="C71">
+        <v>11.3968160525063</v>
+      </c>
+      <c r="D71">
+        <v>25.9971960525063</v>
+      </c>
+      <c r="E71">
+        <v>20.56838</v>
+      </c>
+      <c r="F71">
+        <v>20.77038</v>
+      </c>
+      <c r="G71">
+        <v>6.17</v>
+      </c>
+      <c r="H71">
+        <v>29.9</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>5.13</v>
+      </c>
+      <c r="K71">
+        <v>0.4399999999999995</v>
+      </c>
+      <c r="L71">
+        <v>4.69</v>
+      </c>
+      <c r="M71">
+        <v>1.30853394</v>
+      </c>
+      <c r="N71">
+        <v>3.38146606</v>
+      </c>
+      <c r="O71">
+        <v>0.7439225331999999</v>
+      </c>
+      <c r="P71">
+        <v>2.6375435268</v>
+      </c>
+      <c r="Q71">
+        <v>3.0775435268</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.3669954142002043</v>
+      </c>
+      <c r="T71">
+        <v>2.70750311634651</v>
+      </c>
+      <c r="U71">
+        <v>0.063</v>
+      </c>
+      <c r="V71">
+        <v>0.22</v>
+      </c>
+      <c r="W71">
+        <v>0.04914</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>3.584163816186533</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.1475146910258731</v>
+      </c>
+      <c r="C72">
+        <v>11.12823131033964</v>
+      </c>
+      <c r="D72">
+        <v>26.02963131033964</v>
+      </c>
+      <c r="E72">
+        <v>20.8694</v>
+      </c>
+      <c r="F72">
+        <v>21.0714</v>
+      </c>
+      <c r="G72">
+        <v>6.17</v>
+      </c>
+      <c r="H72">
+        <v>29.9</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>5.13</v>
+      </c>
+      <c r="K72">
+        <v>0.4399999999999995</v>
+      </c>
+      <c r="L72">
+        <v>4.69</v>
+      </c>
+      <c r="M72">
+        <v>1.3274982</v>
+      </c>
+      <c r="N72">
+        <v>3.3625018</v>
+      </c>
+      <c r="O72">
+        <v>0.739750396</v>
+      </c>
+      <c r="P72">
+        <v>2.622751404000001</v>
+      </c>
+      <c r="Q72">
+        <v>3.062751404</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.3770556367529104</v>
+      </c>
+      <c r="T72">
+        <v>2.790496609655881</v>
+      </c>
+      <c r="U72">
+        <v>0.063</v>
+      </c>
+      <c r="V72">
+        <v>0.22</v>
+      </c>
+      <c r="W72">
+        <v>0.04914</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>3.532961475955297</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.1512861836496829</v>
+      </c>
+      <c r="C73">
+        <v>10.08576303830662</v>
+      </c>
+      <c r="D73">
+        <v>25.28818303830662</v>
+      </c>
+      <c r="E73">
+        <v>21.17042</v>
+      </c>
+      <c r="F73">
+        <v>21.37242</v>
+      </c>
+      <c r="G73">
+        <v>6.17</v>
+      </c>
+      <c r="H73">
+        <v>29.9</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>5.13</v>
+      </c>
+      <c r="K73">
+        <v>0.4399999999999995</v>
+      </c>
+      <c r="L73">
+        <v>4.69</v>
+      </c>
+      <c r="M73">
+        <v>1.498206642</v>
+      </c>
+      <c r="N73">
+        <v>3.191793358000001</v>
+      </c>
+      <c r="O73">
+        <v>0.7021945387600002</v>
+      </c>
+      <c r="P73">
+        <v>2.489598819240001</v>
+      </c>
+      <c r="Q73">
+        <v>2.92959881924</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.3878096677575272</v>
+      </c>
+      <c r="T73">
+        <v>2.879213792159003</v>
+      </c>
+      <c r="U73">
+        <v>0.0701</v>
+      </c>
+      <c r="V73">
+        <v>0.22</v>
+      </c>
+      <c r="W73">
+        <v>0.054678</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>3.130409296369947</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.1511810762734927</v>
+      </c>
+      <c r="C74">
+        <v>9.804833748834106</v>
+      </c>
+      <c r="D74">
+        <v>25.30827374883411</v>
+      </c>
+      <c r="E74">
+        <v>21.47144</v>
+      </c>
+      <c r="F74">
+        <v>21.67344</v>
+      </c>
+      <c r="G74">
+        <v>6.17</v>
+      </c>
+      <c r="H74">
+        <v>29.9</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>5.13</v>
+      </c>
+      <c r="K74">
+        <v>0.4399999999999995</v>
+      </c>
+      <c r="L74">
+        <v>4.69</v>
+      </c>
+      <c r="M74">
+        <v>1.519308144</v>
+      </c>
+      <c r="N74">
+        <v>3.170691856</v>
+      </c>
+      <c r="O74">
+        <v>0.69755220832</v>
+      </c>
+      <c r="P74">
+        <v>2.47313964768</v>
+      </c>
+      <c r="Q74">
+        <v>2.91313964768</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.3993318438339024</v>
+      </c>
+      <c r="T74">
+        <v>2.974267916269491</v>
+      </c>
+      <c r="U74">
+        <v>0.0701</v>
+      </c>
+      <c r="V74">
+        <v>0.22</v>
+      </c>
+      <c r="W74">
+        <v>0.054678</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>3.08693138947592</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.1510759688973025</v>
+      </c>
+      <c r="C75">
+        <v>9.523936407689511</v>
+      </c>
+      <c r="D75">
+        <v>25.32839640768951</v>
+      </c>
+      <c r="E75">
+        <v>21.77246</v>
+      </c>
+      <c r="F75">
+        <v>21.97446</v>
+      </c>
+      <c r="G75">
+        <v>6.17</v>
+      </c>
+      <c r="H75">
+        <v>29.9</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>5.13</v>
+      </c>
+      <c r="K75">
+        <v>0.4399999999999995</v>
+      </c>
+      <c r="L75">
+        <v>4.69</v>
+      </c>
+      <c r="M75">
+        <v>1.540409646</v>
+      </c>
+      <c r="N75">
+        <v>3.149590354000001</v>
+      </c>
+      <c r="O75">
+        <v>0.6929098778800001</v>
+      </c>
+      <c r="P75">
+        <v>2.456680476120001</v>
+      </c>
+      <c r="Q75">
+        <v>2.89668047612</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.4117075144344535</v>
+      </c>
+      <c r="T75">
+        <v>3.076363086610384</v>
+      </c>
+      <c r="U75">
+        <v>0.0701</v>
+      </c>
+      <c r="V75">
+        <v>0.22</v>
+      </c>
+      <c r="W75">
+        <v>0.054678</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>3.044644658113236</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.1509708615211122</v>
+      </c>
+      <c r="C76">
+        <v>9.243071091139981</v>
+      </c>
+      <c r="D76">
+        <v>25.34855109113998</v>
+      </c>
+      <c r="E76">
+        <v>22.07348</v>
+      </c>
+      <c r="F76">
+        <v>22.27548</v>
+      </c>
+      <c r="G76">
+        <v>6.17</v>
+      </c>
+      <c r="H76">
+        <v>29.9</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>5.13</v>
+      </c>
+      <c r="K76">
+        <v>0.4399999999999995</v>
+      </c>
+      <c r="L76">
+        <v>4.69</v>
+      </c>
+      <c r="M76">
+        <v>1.561511148</v>
+      </c>
+      <c r="N76">
+        <v>3.128488852</v>
+      </c>
+      <c r="O76">
+        <v>0.68826754744</v>
+      </c>
+      <c r="P76">
+        <v>2.440221304560001</v>
+      </c>
+      <c r="Q76">
+        <v>2.88022130456</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.4250351596965855</v>
+      </c>
+      <c r="T76">
+        <v>3.186311731592885</v>
+      </c>
+      <c r="U76">
+        <v>0.0701</v>
+      </c>
+      <c r="V76">
+        <v>0.22</v>
+      </c>
+      <c r="W76">
+        <v>0.054678</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>3.003500811381976</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.163326254144922</v>
+      </c>
+      <c r="C77">
+        <v>6.773794879713893</v>
+      </c>
+      <c r="D77">
+        <v>23.18029487971389</v>
+      </c>
+      <c r="E77">
+        <v>22.3745</v>
+      </c>
+      <c r="F77">
+        <v>22.5765</v>
+      </c>
+      <c r="G77">
+        <v>6.17</v>
+      </c>
+      <c r="H77">
+        <v>29.9</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>5.13</v>
+      </c>
+      <c r="K77">
+        <v>0.4399999999999995</v>
+      </c>
+      <c r="L77">
+        <v>4.69</v>
+      </c>
+      <c r="M77">
+        <v>2.0634921</v>
+      </c>
+      <c r="N77">
+        <v>2.6265079</v>
+      </c>
+      <c r="O77">
+        <v>0.577831738</v>
+      </c>
+      <c r="P77">
+        <v>2.048676162</v>
+      </c>
+      <c r="Q77">
+        <v>2.488676162</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.4394290165796881</v>
+      </c>
+      <c r="T77">
+        <v>3.305056268173987</v>
+      </c>
+      <c r="U77">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V77">
+        <v>0.22</v>
+      </c>
+      <c r="W77">
+        <v>0.07129200000000001</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>2.272846113634261</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.1633872867687318</v>
+      </c>
+      <c r="C78">
+        <v>6.462984524722732</v>
+      </c>
+      <c r="D78">
+        <v>23.17050452472273</v>
+      </c>
+      <c r="E78">
+        <v>22.67552</v>
+      </c>
+      <c r="F78">
+        <v>22.87752</v>
+      </c>
+      <c r="G78">
+        <v>6.17</v>
+      </c>
+      <c r="H78">
+        <v>29.9</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>5.13</v>
+      </c>
+      <c r="K78">
+        <v>0.4399999999999995</v>
+      </c>
+      <c r="L78">
+        <v>4.69</v>
+      </c>
+      <c r="M78">
+        <v>2.091005328</v>
+      </c>
+      <c r="N78">
+        <v>2.598994672</v>
+      </c>
+      <c r="O78">
+        <v>0.57177882784</v>
+      </c>
+      <c r="P78">
+        <v>2.027215844160001</v>
+      </c>
+      <c r="Q78">
+        <v>2.46721584416</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.4550223615363826</v>
+      </c>
+      <c r="T78">
+        <v>3.433696182803514</v>
+      </c>
+      <c r="U78">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V78">
+        <v>0.22</v>
+      </c>
+      <c r="W78">
+        <v>0.07129200000000001</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>2.242940243718021</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.1634483193925416</v>
+      </c>
+      <c r="C79">
+        <v>6.152182436285994</v>
+      </c>
+      <c r="D79">
+        <v>23.160722436286</v>
+      </c>
+      <c r="E79">
+        <v>22.97654</v>
+      </c>
+      <c r="F79">
+        <v>23.17854</v>
+      </c>
+      <c r="G79">
+        <v>6.17</v>
+      </c>
+      <c r="H79">
+        <v>29.9</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>5.13</v>
+      </c>
+      <c r="K79">
+        <v>0.4399999999999995</v>
+      </c>
+      <c r="L79">
+        <v>4.69</v>
+      </c>
+      <c r="M79">
+        <v>2.118518556</v>
+      </c>
+      <c r="N79">
+        <v>2.571481444</v>
+      </c>
+      <c r="O79">
+        <v>0.56572591768</v>
+      </c>
+      <c r="P79">
+        <v>2.00575552632</v>
+      </c>
+      <c r="Q79">
+        <v>2.44575552632</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.4719716495327896</v>
+      </c>
+      <c r="T79">
+        <v>3.573522176966042</v>
+      </c>
+      <c r="U79">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V79">
+        <v>0.22</v>
+      </c>
+      <c r="W79">
+        <v>0.07129200000000001</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>2.213811149643761</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.1635093520163514</v>
+      </c>
+      <c r="C80">
+        <v>5.841388603938213</v>
+      </c>
+      <c r="D80">
+        <v>23.15094860393821</v>
+      </c>
+      <c r="E80">
+        <v>23.27756</v>
+      </c>
+      <c r="F80">
+        <v>23.47956</v>
+      </c>
+      <c r="G80">
+        <v>6.17</v>
+      </c>
+      <c r="H80">
+        <v>29.9</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>5.13</v>
+      </c>
+      <c r="K80">
+        <v>0.4399999999999995</v>
+      </c>
+      <c r="L80">
+        <v>4.69</v>
+      </c>
+      <c r="M80">
+        <v>2.146031784</v>
+      </c>
+      <c r="N80">
+        <v>2.543968216</v>
+      </c>
+      <c r="O80">
+        <v>0.5596730075199999</v>
+      </c>
+      <c r="P80">
+        <v>1.98429520848</v>
+      </c>
+      <c r="Q80">
+        <v>2.42429520848</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.4904617818925064</v>
+      </c>
+      <c r="T80">
+        <v>3.726059625143347</v>
+      </c>
+      <c r="U80">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V80">
+        <v>0.22</v>
+      </c>
+      <c r="W80">
+        <v>0.07129200000000001</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>2.185428955417558</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.1635703846401612</v>
+      </c>
+      <c r="C81">
+        <v>5.530603017231591</v>
+      </c>
+      <c r="D81">
+        <v>23.14118301723159</v>
+      </c>
+      <c r="E81">
+        <v>23.57858</v>
+      </c>
+      <c r="F81">
+        <v>23.78058</v>
+      </c>
+      <c r="G81">
+        <v>6.17</v>
+      </c>
+      <c r="H81">
+        <v>29.9</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>5.13</v>
+      </c>
+      <c r="K81">
+        <v>0.4399999999999995</v>
+      </c>
+      <c r="L81">
+        <v>4.69</v>
+      </c>
+      <c r="M81">
+        <v>2.173545012</v>
+      </c>
+      <c r="N81">
+        <v>2.516454988</v>
+      </c>
+      <c r="O81">
+        <v>0.55362009736</v>
+      </c>
+      <c r="P81">
+        <v>1.96283489064</v>
+      </c>
+      <c r="Q81">
+        <v>2.402834890639999</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.5107128792388629</v>
+      </c>
+      <c r="T81">
+        <v>3.893124449337537</v>
+      </c>
+      <c r="U81">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V81">
+        <v>0.22</v>
+      </c>
+      <c r="W81">
+        <v>0.07129200000000001</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>2.157765297754045</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.163631417263971</v>
+      </c>
+      <c r="C82">
+        <v>5.219825665735932</v>
+      </c>
+      <c r="D82">
+        <v>23.13142566573593</v>
+      </c>
+      <c r="E82">
+        <v>23.8796</v>
+      </c>
+      <c r="F82">
+        <v>24.0816</v>
+      </c>
+      <c r="G82">
+        <v>6.17</v>
+      </c>
+      <c r="H82">
+        <v>29.9</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>5.13</v>
+      </c>
+      <c r="K82">
+        <v>0.4399999999999995</v>
+      </c>
+      <c r="L82">
+        <v>4.69</v>
+      </c>
+      <c r="M82">
+        <v>2.20105824</v>
+      </c>
+      <c r="N82">
+        <v>2.48894176</v>
+      </c>
+      <c r="O82">
+        <v>0.5475671871999999</v>
+      </c>
+      <c r="P82">
+        <v>1.9413745728</v>
+      </c>
+      <c r="Q82">
+        <v>2.3813745728</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.532989086319855</v>
+      </c>
+      <c r="T82">
+        <v>4.076895755951147</v>
+      </c>
+      <c r="U82">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V82">
+        <v>0.22</v>
+      </c>
+      <c r="W82">
+        <v>0.07129200000000001</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>2.130793231532119</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.1636924498877808</v>
+      </c>
+      <c r="C83">
+        <v>4.90905653903863</v>
+      </c>
+      <c r="D83">
+        <v>23.12167653903863</v>
+      </c>
+      <c r="E83">
+        <v>24.18062</v>
+      </c>
+      <c r="F83">
+        <v>24.38262</v>
+      </c>
+      <c r="G83">
+        <v>6.17</v>
+      </c>
+      <c r="H83">
+        <v>29.9</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>5.13</v>
+      </c>
+      <c r="K83">
+        <v>0.4399999999999995</v>
+      </c>
+      <c r="L83">
+        <v>4.69</v>
+      </c>
+      <c r="M83">
+        <v>2.228571468000001</v>
+      </c>
+      <c r="N83">
+        <v>2.461428532</v>
+      </c>
+      <c r="O83">
+        <v>0.5415142770399999</v>
+      </c>
+      <c r="P83">
+        <v>1.91991425496</v>
+      </c>
+      <c r="Q83">
+        <v>2.35991425496</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.5576101573041095</v>
+      </c>
+      <c r="T83">
+        <v>4.280011410629347</v>
+      </c>
+      <c r="U83">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V83">
+        <v>0.22</v>
+      </c>
+      <c r="W83">
+        <v>0.07129200000000001</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>2.104487142253945</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.1637534825115905</v>
+      </c>
+      <c r="C84">
+        <v>4.598295626744648</v>
+      </c>
+      <c r="D84">
+        <v>23.11193562674465</v>
+      </c>
+      <c r="E84">
+        <v>24.48164</v>
+      </c>
+      <c r="F84">
+        <v>24.68364</v>
+      </c>
+      <c r="G84">
+        <v>6.17</v>
+      </c>
+      <c r="H84">
+        <v>29.9</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>5.13</v>
+      </c>
+      <c r="K84">
+        <v>0.4399999999999995</v>
+      </c>
+      <c r="L84">
+        <v>4.69</v>
+      </c>
+      <c r="M84">
+        <v>2.256084696</v>
+      </c>
+      <c r="N84">
+        <v>2.433915304</v>
+      </c>
+      <c r="O84">
+        <v>0.53546136688</v>
+      </c>
+      <c r="P84">
+        <v>1.89845393712</v>
+      </c>
+      <c r="Q84">
+        <v>2.33845393712</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.5849669028421698</v>
+      </c>
+      <c r="T84">
+        <v>4.505695471382902</v>
+      </c>
+      <c r="U84">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V84">
+        <v>0.22</v>
+      </c>
+      <c r="W84">
+        <v>0.07129200000000001</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>2.078822664909385</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.1638145151354004</v>
+      </c>
+      <c r="C85">
+        <v>4.287542918476408</v>
+      </c>
+      <c r="D85">
+        <v>23.10220291847641</v>
+      </c>
+      <c r="E85">
+        <v>24.78266</v>
+      </c>
+      <c r="F85">
+        <v>24.98466</v>
+      </c>
+      <c r="G85">
+        <v>6.17</v>
+      </c>
+      <c r="H85">
+        <v>29.9</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>5.13</v>
+      </c>
+      <c r="K85">
+        <v>0.4399999999999995</v>
+      </c>
+      <c r="L85">
+        <v>4.69</v>
+      </c>
+      <c r="M85">
+        <v>2.283597924</v>
+      </c>
+      <c r="N85">
+        <v>2.406402076</v>
+      </c>
+      <c r="O85">
+        <v>0.5294084567199999</v>
+      </c>
+      <c r="P85">
+        <v>1.87699361928</v>
+      </c>
+      <c r="Q85">
+        <v>2.31699361928</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.6155420890317669</v>
+      </c>
+      <c r="T85">
+        <v>4.757930598107464</v>
+      </c>
+      <c r="U85">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V85">
+        <v>0.22</v>
+      </c>
+      <c r="W85">
+        <v>0.07129200000000001</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>2.053776608705657</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.1638755477592101</v>
+      </c>
+      <c r="C86">
+        <v>3.976798403873865</v>
+      </c>
+      <c r="D86">
+        <v>23.09247840387386</v>
+      </c>
+      <c r="E86">
+        <v>25.08368</v>
+      </c>
+      <c r="F86">
+        <v>25.28568</v>
+      </c>
+      <c r="G86">
+        <v>6.17</v>
+      </c>
+      <c r="H86">
+        <v>29.9</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>5.13</v>
+      </c>
+      <c r="K86">
+        <v>0.4399999999999995</v>
+      </c>
+      <c r="L86">
+        <v>4.69</v>
+      </c>
+      <c r="M86">
+        <v>2.311111152</v>
+      </c>
+      <c r="N86">
+        <v>2.378888848</v>
+      </c>
+      <c r="O86">
+        <v>0.5233555465600001</v>
+      </c>
+      <c r="P86">
+        <v>1.85553330144</v>
+      </c>
+      <c r="Q86">
+        <v>2.29553330144</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.6499391734950632</v>
+      </c>
+      <c r="T86">
+        <v>5.041695115672594</v>
+      </c>
+      <c r="U86">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V86">
+        <v>0.22</v>
+      </c>
+      <c r="W86">
+        <v>0.07129200000000001</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>2.029326887173448</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.1639365803830199</v>
+      </c>
+      <c r="C87">
+        <v>3.666062072594372</v>
+      </c>
+      <c r="D87">
+        <v>23.08276207259437</v>
+      </c>
+      <c r="E87">
+        <v>25.3847</v>
+      </c>
+      <c r="F87">
+        <v>25.5867</v>
+      </c>
+      <c r="G87">
+        <v>6.17</v>
+      </c>
+      <c r="H87">
+        <v>29.9</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>5.13</v>
+      </c>
+      <c r="K87">
+        <v>0.4399999999999995</v>
+      </c>
+      <c r="L87">
+        <v>4.69</v>
+      </c>
+      <c r="M87">
+        <v>2.33862438</v>
+      </c>
+      <c r="N87">
+        <v>2.35137562</v>
+      </c>
+      <c r="O87">
+        <v>0.5173026364</v>
+      </c>
+      <c r="P87">
+        <v>1.8340729836</v>
+      </c>
+      <c r="Q87">
+        <v>2.2740729836</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.6889225358867992</v>
+      </c>
+      <c r="T87">
+        <v>5.36329490224641</v>
+      </c>
+      <c r="U87">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V87">
+        <v>0.22</v>
+      </c>
+      <c r="W87">
+        <v>0.07129200000000001</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>2.005452453206701</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.1781514930068297</v>
+      </c>
+      <c r="C88">
+        <v>1.304884490111917</v>
+      </c>
+      <c r="D88">
+        <v>21.02260449011192</v>
+      </c>
+      <c r="E88">
+        <v>25.68572</v>
+      </c>
+      <c r="F88">
+        <v>25.88772</v>
+      </c>
+      <c r="G88">
+        <v>6.17</v>
+      </c>
+      <c r="H88">
+        <v>29.9</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>5.13</v>
+      </c>
+      <c r="K88">
+        <v>0.4399999999999995</v>
+      </c>
+      <c r="L88">
+        <v>4.69</v>
+      </c>
+      <c r="M88">
+        <v>2.9123685</v>
+      </c>
+      <c r="N88">
+        <v>1.7776315</v>
+      </c>
+      <c r="O88">
+        <v>0.3910789299999999</v>
+      </c>
+      <c r="P88">
+        <v>1.38655257</v>
+      </c>
+      <c r="Q88">
+        <v>1.82655257</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.7334749500487834</v>
+      </c>
+      <c r="T88">
+        <v>5.730837515473628</v>
+      </c>
+      <c r="U88">
+        <v>0.1125</v>
+      </c>
+      <c r="V88">
+        <v>0.22</v>
+      </c>
+      <c r="W88">
+        <v>0.08775000000000001</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>1.610373137877298</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.1783771056306395</v>
+      </c>
+      <c r="C89">
+        <v>0.9741270470829839</v>
+      </c>
+      <c r="D89">
+        <v>20.99286704708298</v>
+      </c>
+      <c r="E89">
+        <v>25.98674</v>
+      </c>
+      <c r="F89">
+        <v>26.18874</v>
+      </c>
+      <c r="G89">
+        <v>6.17</v>
+      </c>
+      <c r="H89">
+        <v>29.9</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>5.13</v>
+      </c>
+      <c r="K89">
+        <v>0.4399999999999995</v>
+      </c>
+      <c r="L89">
+        <v>4.69</v>
+      </c>
+      <c r="M89">
+        <v>2.94623325</v>
+      </c>
+      <c r="N89">
+        <v>1.74376675</v>
+      </c>
+      <c r="O89">
+        <v>0.383628685</v>
+      </c>
+      <c r="P89">
+        <v>1.360138065</v>
+      </c>
+      <c r="Q89">
+        <v>1.800138065</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.7848815817741497</v>
+      </c>
+      <c r="T89">
+        <v>6.154925146120418</v>
+      </c>
+      <c r="U89">
+        <v>0.1125</v>
+      </c>
+      <c r="V89">
+        <v>0.22</v>
+      </c>
+      <c r="W89">
+        <v>0.08775000000000001</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>1.591863101809743</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.1786027182544493</v>
+      </c>
+      <c r="C90">
+        <v>0.6434536151840753</v>
+      </c>
+      <c r="D90">
+        <v>20.96321361518408</v>
+      </c>
+      <c r="E90">
+        <v>26.28776</v>
+      </c>
+      <c r="F90">
+        <v>26.48976</v>
+      </c>
+      <c r="G90">
+        <v>6.17</v>
+      </c>
+      <c r="H90">
+        <v>29.9</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>5.13</v>
+      </c>
+      <c r="K90">
+        <v>0.4399999999999995</v>
+      </c>
+      <c r="L90">
+        <v>4.69</v>
+      </c>
+      <c r="M90">
+        <v>2.980098</v>
+      </c>
+      <c r="N90">
+        <v>1.709902</v>
+      </c>
+      <c r="O90">
+        <v>0.3761784400000001</v>
+      </c>
+      <c r="P90">
+        <v>1.33372356</v>
+      </c>
+      <c r="Q90">
+        <v>1.77372356</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.8448559854537439</v>
+      </c>
+      <c r="T90">
+        <v>6.649694048541675</v>
+      </c>
+      <c r="U90">
+        <v>0.1125</v>
+      </c>
+      <c r="V90">
+        <v>0.22</v>
+      </c>
+      <c r="W90">
+        <v>0.08775000000000001</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>1.573773748380087</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.1788283308782591</v>
+      </c>
+      <c r="C91">
+        <v>0.3128638389081395</v>
+      </c>
+      <c r="D91">
+        <v>20.93364383890814</v>
+      </c>
+      <c r="E91">
+        <v>26.58878</v>
+      </c>
+      <c r="F91">
+        <v>26.79078</v>
+      </c>
+      <c r="G91">
+        <v>6.17</v>
+      </c>
+      <c r="H91">
+        <v>29.9</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>5.13</v>
+      </c>
+      <c r="K91">
+        <v>0.4399999999999995</v>
+      </c>
+      <c r="L91">
+        <v>4.69</v>
+      </c>
+      <c r="M91">
+        <v>3.01396275</v>
+      </c>
+      <c r="N91">
+        <v>1.67603725</v>
+      </c>
+      <c r="O91">
+        <v>0.368728195</v>
+      </c>
+      <c r="P91">
+        <v>1.307309055</v>
+      </c>
+      <c r="Q91">
+        <v>1.747309055</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.9157348261659912</v>
+      </c>
+      <c r="T91">
+        <v>7.23442093322134</v>
+      </c>
+      <c r="U91">
+        <v>0.1125</v>
+      </c>
+      <c r="V91">
+        <v>0.22</v>
+      </c>
+      <c r="W91">
+        <v>0.08775000000000001</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>1.556090897274693</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.1790539435020688</v>
+      </c>
+      <c r="C92">
+        <v>-0.01764263524890453</v>
+      </c>
+      <c r="D92">
+        <v>20.9041573647511</v>
+      </c>
+      <c r="E92">
+        <v>26.8898</v>
+      </c>
+      <c r="F92">
+        <v>27.0918</v>
+      </c>
+      <c r="G92">
+        <v>6.17</v>
+      </c>
+      <c r="H92">
+        <v>29.9</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>5.13</v>
+      </c>
+      <c r="K92">
+        <v>0.4399999999999995</v>
+      </c>
+      <c r="L92">
+        <v>4.69</v>
+      </c>
+      <c r="M92">
+        <v>3.0478275</v>
+      </c>
+      <c r="N92">
+        <v>1.6421725</v>
+      </c>
+      <c r="O92">
+        <v>0.3612779500000001</v>
+      </c>
+      <c r="P92">
+        <v>1.28089455</v>
+      </c>
+      <c r="Q92">
+        <v>1.72089455</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>1.000789435020688</v>
+      </c>
+      <c r="T92">
+        <v>7.93609319483694</v>
+      </c>
+      <c r="U92">
+        <v>0.1125</v>
+      </c>
+      <c r="V92">
+        <v>0.22</v>
+      </c>
+      <c r="W92">
+        <v>0.08775000000000001</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>1.538800998416085</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.1792795561258786</v>
+      </c>
+      <c r="C93">
+        <v>-0.3480661588021761</v>
+      </c>
+      <c r="D93">
+        <v>20.87475384119783</v>
+      </c>
+      <c r="E93">
+        <v>27.19082</v>
+      </c>
+      <c r="F93">
+        <v>27.39282</v>
+      </c>
+      <c r="G93">
+        <v>6.17</v>
+      </c>
+      <c r="H93">
+        <v>29.9</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>5.13</v>
+      </c>
+      <c r="K93">
+        <v>0.4399999999999995</v>
+      </c>
+      <c r="L93">
+        <v>4.69</v>
+      </c>
+      <c r="M93">
+        <v>3.08169225</v>
+      </c>
+      <c r="N93">
+        <v>1.60830775</v>
+      </c>
+      <c r="O93">
+        <v>0.353827705</v>
+      </c>
+      <c r="P93">
+        <v>1.254480045</v>
+      </c>
+      <c r="Q93">
+        <v>1.694480045</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>1.104745068065318</v>
+      </c>
+      <c r="T93">
+        <v>8.793692625700452</v>
+      </c>
+      <c r="U93">
+        <v>0.1125</v>
+      </c>
+      <c r="V93">
+        <v>0.22</v>
+      </c>
+      <c r="W93">
+        <v>0.08775000000000001</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>1.521891097334589</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.1795051687496884</v>
+      </c>
+      <c r="C94">
+        <v>-0.6784070812918372</v>
+      </c>
+      <c r="D94">
+        <v>20.84543291870817</v>
+      </c>
+      <c r="E94">
+        <v>27.49184</v>
+      </c>
+      <c r="F94">
+        <v>27.69384</v>
+      </c>
+      <c r="G94">
+        <v>6.17</v>
+      </c>
+      <c r="H94">
+        <v>29.9</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>5.13</v>
+      </c>
+      <c r="K94">
+        <v>0.4399999999999995</v>
+      </c>
+      <c r="L94">
+        <v>4.69</v>
+      </c>
+      <c r="M94">
+        <v>3.115557</v>
+      </c>
+      <c r="N94">
+        <v>1.574443</v>
+      </c>
+      <c r="O94">
+        <v>0.34637746</v>
+      </c>
+      <c r="P94">
+        <v>1.22806554</v>
+      </c>
+      <c r="Q94">
+        <v>1.66806554</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>1.234689609371106</v>
+      </c>
+      <c r="T94">
+        <v>9.865691914279841</v>
+      </c>
+      <c r="U94">
+        <v>0.1125</v>
+      </c>
+      <c r="V94">
+        <v>0.22</v>
+      </c>
+      <c r="W94">
+        <v>0.08775000000000001</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>1.505348802798344</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.2503131954386311</v>
+      </c>
+      <c r="C95">
+        <v>-7.357246925838954</v>
+      </c>
+      <c r="D95">
+        <v>14.46761307416105</v>
+      </c>
+      <c r="E95">
+        <v>27.79286</v>
+      </c>
+      <c r="F95">
+        <v>27.99486</v>
+      </c>
+      <c r="G95">
+        <v>6.17</v>
+      </c>
+      <c r="H95">
+        <v>29.9</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>5.13</v>
+      </c>
+      <c r="K95">
+        <v>0.4399999999999995</v>
+      </c>
+      <c r="L95">
+        <v>4.69</v>
+      </c>
+      <c r="M95">
+        <v>5.503789476000001</v>
+      </c>
+      <c r="N95">
+        <v>-0.8137894760000002</v>
+      </c>
+      <c r="O95">
+        <v>-0.17903368472</v>
+      </c>
+      <c r="P95">
+        <v>-0.6347557912800001</v>
+      </c>
+      <c r="Q95">
+        <v>-0.1947557912800006</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>1.453599823976421</v>
+      </c>
+      <c r="T95">
+        <v>11.67162844659963</v>
+      </c>
+      <c r="U95">
+        <v>0.1966</v>
+      </c>
+      <c r="V95">
+        <v>0.1874708334138324</v>
+      </c>
+      <c r="W95">
+        <v>0.1597432341508405</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.8521401518810564</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.2518911954386311</v>
+      </c>
+      <c r="C96">
+        <v>-7.756245599175077</v>
+      </c>
+      <c r="D96">
+        <v>14.36963440082492</v>
+      </c>
+      <c r="E96">
+        <v>28.09388</v>
+      </c>
+      <c r="F96">
+        <v>28.29588</v>
+      </c>
+      <c r="G96">
+        <v>6.17</v>
+      </c>
+      <c r="H96">
+        <v>29.9</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>5.13</v>
+      </c>
+      <c r="K96">
+        <v>0.4399999999999995</v>
+      </c>
+      <c r="L96">
+        <v>4.69</v>
+      </c>
+      <c r="M96">
+        <v>5.562970008</v>
+      </c>
+      <c r="N96">
+        <v>-0.8729700079999994</v>
+      </c>
+      <c r="O96">
+        <v>-0.1920534017599998</v>
+      </c>
+      <c r="P96">
+        <v>-0.6809166062399995</v>
+      </c>
+      <c r="Q96">
+        <v>-0.24091660624</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>1.689399794639158</v>
+      </c>
+      <c r="T96">
+        <v>13.61689985436624</v>
+      </c>
+      <c r="U96">
+        <v>0.1966</v>
+      </c>
+      <c r="V96">
+        <v>0.1854764628456002</v>
+      </c>
+      <c r="W96">
+        <v>0.160135327404555</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.8430748311163645</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.2534691954386311</v>
+      </c>
+      <c r="C97">
+        <v>-8.15392612209272</v>
+      </c>
+      <c r="D97">
+        <v>14.27297387790728</v>
+      </c>
+      <c r="E97">
+        <v>28.3949</v>
+      </c>
+      <c r="F97">
+        <v>28.5969</v>
+      </c>
+      <c r="G97">
+        <v>6.17</v>
+      </c>
+      <c r="H97">
+        <v>29.9</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>5.13</v>
+      </c>
+      <c r="K97">
+        <v>0.4399999999999995</v>
+      </c>
+      <c r="L97">
+        <v>4.69</v>
+      </c>
+      <c r="M97">
+        <v>5.62215054</v>
+      </c>
+      <c r="N97">
+        <v>-0.9321505399999994</v>
+      </c>
+      <c r="O97">
+        <v>-0.2050731187999998</v>
+      </c>
+      <c r="P97">
+        <v>-0.7270774211999995</v>
+      </c>
+      <c r="Q97">
+        <v>-0.2870774212</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>2.019519753566991</v>
+      </c>
+      <c r="T97">
+        <v>16.3402798252395</v>
+      </c>
+      <c r="U97">
+        <v>0.1966</v>
+      </c>
+      <c r="V97">
+        <v>0.1835240790261728</v>
+      </c>
+      <c r="W97">
+        <v>0.1605191660634544</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.8342003592098763</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.2550471954386311</v>
+      </c>
+      <c r="C98">
+        <v>-8.550314917344096</v>
+      </c>
+      <c r="D98">
+        <v>14.17760508265591</v>
+      </c>
+      <c r="E98">
+        <v>28.69592</v>
+      </c>
+      <c r="F98">
+        <v>28.89792</v>
+      </c>
+      <c r="G98">
+        <v>6.17</v>
+      </c>
+      <c r="H98">
+        <v>29.9</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>5.13</v>
+      </c>
+      <c r="K98">
+        <v>0.4399999999999995</v>
+      </c>
+      <c r="L98">
+        <v>4.69</v>
+      </c>
+      <c r="M98">
+        <v>5.681331072</v>
+      </c>
+      <c r="N98">
+        <v>-0.9913310719999995</v>
+      </c>
+      <c r="O98">
+        <v>-0.2180928358399999</v>
+      </c>
+      <c r="P98">
+        <v>-0.7732382361599996</v>
+      </c>
+      <c r="Q98">
+        <v>-0.3332382361600001</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>2.514699691958733</v>
+      </c>
+      <c r="T98">
+        <v>20.42534978154933</v>
+      </c>
+      <c r="U98">
+        <v>0.1966</v>
+      </c>
+      <c r="V98">
+        <v>0.1816123698696502</v>
+      </c>
+      <c r="W98">
+        <v>0.1608950080836268</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.8255107721347735</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.2566251954386311</v>
+      </c>
+      <c r="C99">
+        <v>-8.945437706165279</v>
+      </c>
+      <c r="D99">
+        <v>14.08350229383472</v>
+      </c>
+      <c r="E99">
+        <v>28.99694</v>
+      </c>
+      <c r="F99">
+        <v>29.19894</v>
+      </c>
+      <c r="G99">
+        <v>6.17</v>
+      </c>
+      <c r="H99">
+        <v>29.9</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>5.13</v>
+      </c>
+      <c r="K99">
+        <v>0.4399999999999995</v>
+      </c>
+      <c r="L99">
+        <v>4.69</v>
+      </c>
+      <c r="M99">
+        <v>5.740511604</v>
+      </c>
+      <c r="N99">
+        <v>-1.050511604</v>
+      </c>
+      <c r="O99">
+        <v>-0.2311125528799999</v>
+      </c>
+      <c r="P99">
+        <v>-0.8193990511199997</v>
+      </c>
+      <c r="Q99">
+        <v>-0.3793990511200002</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>3.339999589278311</v>
+      </c>
+      <c r="T99">
+        <v>27.23379970873243</v>
+      </c>
+      <c r="U99">
+        <v>0.1966</v>
+      </c>
+      <c r="V99">
+        <v>0.1797400773967671</v>
+      </c>
+      <c r="W99">
+        <v>0.1612631007837956</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.8170003518034872</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.2582031954386311</v>
+      </c>
+      <c r="C100">
+        <v>-9.339319531404016</v>
+      </c>
+      <c r="D100">
+        <v>13.99064046859599</v>
+      </c>
+      <c r="E100">
+        <v>29.29796</v>
+      </c>
+      <c r="F100">
+        <v>29.49996</v>
+      </c>
+      <c r="G100">
+        <v>6.17</v>
+      </c>
+      <c r="H100">
+        <v>29.9</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>5.13</v>
+      </c>
+      <c r="K100">
+        <v>0.4399999999999995</v>
+      </c>
+      <c r="L100">
+        <v>4.69</v>
+      </c>
+      <c r="M100">
+        <v>5.799692136</v>
+      </c>
+      <c r="N100">
+        <v>-1.109692136</v>
+      </c>
+      <c r="O100">
+        <v>-0.2441322699199999</v>
+      </c>
+      <c r="P100">
+        <v>-0.8655598660799997</v>
+      </c>
+      <c r="Q100">
+        <v>-0.4255598660800002</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>4.990599383917466</v>
+      </c>
+      <c r="T100">
+        <v>40.85069956309865</v>
+      </c>
+      <c r="U100">
+        <v>0.1966</v>
+      </c>
+      <c r="V100">
+        <v>0.1779059949743512</v>
+      </c>
+      <c r="W100">
+        <v>0.1616236813880426</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.8086636135197781</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.2597811954386311</v>
+      </c>
+      <c r="C101">
+        <v>-9.731984779738511</v>
+      </c>
+      <c r="D101">
+        <v>13.89899522026149</v>
+      </c>
+      <c r="E101">
+        <v>29.59898</v>
+      </c>
+      <c r="F101">
+        <v>29.80098</v>
+      </c>
+      <c r="G101">
+        <v>6.17</v>
+      </c>
+      <c r="H101">
+        <v>29.9</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>5.13</v>
+      </c>
+      <c r="K101">
+        <v>0.4399999999999995</v>
+      </c>
+      <c r="L101">
+        <v>4.69</v>
+      </c>
+      <c r="M101">
+        <v>5.858872668</v>
+      </c>
+      <c r="N101">
+        <v>-1.168872668</v>
+      </c>
+      <c r="O101">
+        <v>-0.2571519869599999</v>
+      </c>
+      <c r="P101">
+        <v>-0.9117206810399998</v>
+      </c>
+      <c r="Q101">
+        <v>-0.4717206810400003</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>9.942398767834931</v>
+      </c>
+      <c r="T101">
+        <v>81.70139912619729</v>
+      </c>
+      <c r="U101">
+        <v>0.1966</v>
+      </c>
+      <c r="V101">
+        <v>0.176108964722085</v>
+      </c>
+      <c r="W101">
+        <v>0.1619769775356381</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.8004952941912955</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/greece/greece_recreation.xlsx
+++ b/research/traditional_assets/database/data/greece/greece_recreation.xlsx
@@ -1406,7 +1406,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1543,22 +1543,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1146192678745626</v>
+        <v>0.1144022054852385</v>
       </c>
       <c r="C2">
-        <v>38.1471658213783</v>
+        <v>37.82635033599116</v>
       </c>
       <c r="D2">
-        <v>31.4571658213783</v>
+        <v>31.51787033599116</v>
       </c>
       <c r="E2">
-        <v>-0.552</v>
+        <v>-0.17048</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.38152</v>
       </c>
       <c r="G2">
         <v>6.69</v>
@@ -1579,28 +1579,28 @@
         <v>4.98</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.019190456</v>
       </c>
       <c r="N2">
-        <v>4.98</v>
+        <v>4.960809544000001</v>
       </c>
       <c r="O2">
-        <v>1.0956</v>
+        <v>1.09137809968</v>
       </c>
       <c r="P2">
-        <v>3.8844</v>
+        <v>3.869431444320001</v>
       </c>
       <c r="Q2">
-        <v>4.2844</v>
+        <v>4.26943144432</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1146192678745626</v>
+        <v>0.1151614802881197</v>
       </c>
       <c r="T2">
-        <v>0.8969457633378592</v>
+        <v>0.9040126087459757</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1617,7 +1617,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>259.5039951109031</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1625,22 +1625,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1144022054852385</v>
+        <v>0.1141851430959145</v>
       </c>
       <c r="C3">
-        <v>37.82635033599116</v>
+        <v>37.50576959286101</v>
       </c>
       <c r="D3">
-        <v>31.51787033599116</v>
+        <v>31.578809592861</v>
       </c>
       <c r="E3">
-        <v>-0.17048</v>
+        <v>0.21104</v>
       </c>
       <c r="F3">
-        <v>0.38152</v>
+        <v>0.7630400000000001</v>
       </c>
       <c r="G3">
         <v>6.69</v>
@@ -1661,28 +1661,28 @@
         <v>4.98</v>
       </c>
       <c r="M3">
-        <v>0.019190456</v>
+        <v>0.038380912</v>
       </c>
       <c r="N3">
-        <v>4.960809544000001</v>
+        <v>4.941619088</v>
       </c>
       <c r="O3">
-        <v>1.09137809968</v>
+        <v>1.08715619936</v>
       </c>
       <c r="P3">
-        <v>3.869431444320001</v>
+        <v>3.854462888640001</v>
       </c>
       <c r="Q3">
-        <v>4.26943144432</v>
+        <v>4.25446288864</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1151614802881197</v>
+        <v>0.1157147582611373</v>
       </c>
       <c r="T3">
-        <v>0.9040126087459757</v>
+        <v>0.9112236754889517</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1699,7 +1699,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>259.5039951109031</v>
+        <v>129.7519975554515</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1707,22 +1707,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1141851430959145</v>
+        <v>0.1139680807065905</v>
       </c>
       <c r="C4">
-        <v>37.50576959286101</v>
+        <v>37.18542495623586</v>
       </c>
       <c r="D4">
-        <v>31.578809592861</v>
+        <v>31.63998495623586</v>
       </c>
       <c r="E4">
-        <v>0.21104</v>
+        <v>0.59256</v>
       </c>
       <c r="F4">
-        <v>0.7630400000000001</v>
+        <v>1.14456</v>
       </c>
       <c r="G4">
         <v>6.69</v>
@@ -1743,28 +1743,28 @@
         <v>4.98</v>
       </c>
       <c r="M4">
-        <v>0.038380912</v>
+        <v>0.057571368</v>
       </c>
       <c r="N4">
-        <v>4.941619088</v>
+        <v>4.922428632000001</v>
       </c>
       <c r="O4">
-        <v>1.08715619936</v>
+        <v>1.08293429904</v>
       </c>
       <c r="P4">
-        <v>3.854462888640001</v>
+        <v>3.839494332960001</v>
       </c>
       <c r="Q4">
-        <v>4.25446288864</v>
+        <v>4.23949433296</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1157147582611373</v>
+        <v>0.1162794440274129</v>
       </c>
       <c r="T4">
-        <v>0.9112236754889517</v>
+        <v>0.9185834240204427</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1781,7 +1781,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>129.7519975554515</v>
+        <v>86.50133170363436</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1789,22 +1789,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1139680807065905</v>
+        <v>0.1137510183172664</v>
       </c>
       <c r="C5">
-        <v>37.18542495623586</v>
+        <v>36.86531780095574</v>
       </c>
       <c r="D5">
-        <v>31.63998495623586</v>
+        <v>31.70139780095574</v>
       </c>
       <c r="E5">
-        <v>0.59256</v>
+        <v>0.9740800000000001</v>
       </c>
       <c r="F5">
-        <v>1.14456</v>
+        <v>1.52608</v>
       </c>
       <c r="G5">
         <v>6.69</v>
@@ -1825,28 +1825,28 @@
         <v>4.98</v>
       </c>
       <c r="M5">
-        <v>0.057571368</v>
+        <v>0.07676182400000001</v>
       </c>
       <c r="N5">
-        <v>4.922428632000001</v>
+        <v>4.903238176</v>
       </c>
       <c r="O5">
-        <v>1.08293429904</v>
+        <v>1.07871239872</v>
       </c>
       <c r="P5">
-        <v>3.839494332960001</v>
+        <v>3.82452577728</v>
       </c>
       <c r="Q5">
-        <v>4.23949433296</v>
+        <v>4.22452577728</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1162794440274129</v>
+        <v>0.1168558940804859</v>
       </c>
       <c r="T5">
-        <v>0.9185834240204427</v>
+        <v>0.9260965006463396</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1863,7 +1863,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>86.50133170363436</v>
+        <v>64.87599877772575</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1871,22 +1871,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1137510183172664</v>
+        <v>0.1135339559279424</v>
       </c>
       <c r="C6">
-        <v>36.86531780095574</v>
+        <v>36.54544951255554</v>
       </c>
       <c r="D6">
-        <v>31.70139780095574</v>
+        <v>31.76304951255554</v>
       </c>
       <c r="E6">
-        <v>0.9740800000000001</v>
+        <v>1.3556</v>
       </c>
       <c r="F6">
-        <v>1.52608</v>
+        <v>1.9076</v>
       </c>
       <c r="G6">
         <v>6.69</v>
@@ -1907,28 +1907,28 @@
         <v>4.98</v>
       </c>
       <c r="M6">
-        <v>0.07676182400000001</v>
+        <v>0.09595228</v>
       </c>
       <c r="N6">
-        <v>4.903238176</v>
+        <v>4.884047720000001</v>
       </c>
       <c r="O6">
-        <v>1.07871239872</v>
+        <v>1.0744904984</v>
       </c>
       <c r="P6">
-        <v>3.82452577728</v>
+        <v>3.8095572216</v>
       </c>
       <c r="Q6">
-        <v>4.22452577728</v>
+        <v>4.2095572216</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1168558940804859</v>
+        <v>0.1174444799241499</v>
       </c>
       <c r="T6">
-        <v>0.9260965006463396</v>
+        <v>0.9337677473064662</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1945,7 +1945,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>64.87599877772575</v>
+        <v>51.90079902218061</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1953,22 +1953,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1135339559279424</v>
+        <v>0.1133168935386183</v>
       </c>
       <c r="C7">
-        <v>36.54544951255554</v>
+        <v>36.22582148736937</v>
       </c>
       <c r="D7">
-        <v>31.76304951255554</v>
+        <v>31.82494148736937</v>
       </c>
       <c r="E7">
-        <v>1.3556</v>
+        <v>1.73712</v>
       </c>
       <c r="F7">
-        <v>1.9076</v>
+        <v>2.28912</v>
       </c>
       <c r="G7">
         <v>6.69</v>
@@ -1989,28 +1989,28 @@
         <v>4.98</v>
       </c>
       <c r="M7">
-        <v>0.09595228</v>
+        <v>0.115142736</v>
       </c>
       <c r="N7">
-        <v>4.884047720000001</v>
+        <v>4.864857264</v>
       </c>
       <c r="O7">
-        <v>1.0744904984</v>
+        <v>1.07026859808</v>
       </c>
       <c r="P7">
-        <v>3.8095572216</v>
+        <v>3.79458866592</v>
       </c>
       <c r="Q7">
-        <v>4.2095572216</v>
+        <v>4.19458866592</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1174444799241499</v>
+        <v>0.1180455888708706</v>
       </c>
       <c r="T7">
-        <v>0.9337677473064662</v>
+        <v>0.9416022119806378</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>51.90079902218061</v>
+        <v>43.25066585181718</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2035,22 +2035,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1133168935386183</v>
+        <v>0.1130998311492943</v>
       </c>
       <c r="C8">
-        <v>36.22582148736937</v>
+        <v>35.90643513263587</v>
       </c>
       <c r="D8">
-        <v>31.82494148736937</v>
+        <v>31.88707513263587</v>
       </c>
       <c r="E8">
-        <v>1.73712</v>
+        <v>2.11864</v>
       </c>
       <c r="F8">
-        <v>2.28912</v>
+        <v>2.67064</v>
       </c>
       <c r="G8">
         <v>6.69</v>
@@ -2071,28 +2071,28 @@
         <v>4.98</v>
       </c>
       <c r="M8">
-        <v>0.115142736</v>
+        <v>0.134333192</v>
       </c>
       <c r="N8">
-        <v>4.864857264</v>
+        <v>4.845666808000001</v>
       </c>
       <c r="O8">
-        <v>1.07026859808</v>
+        <v>1.06604669776</v>
       </c>
       <c r="P8">
-        <v>3.79458866592</v>
+        <v>3.779620110240001</v>
       </c>
       <c r="Q8">
-        <v>4.19458866592</v>
+        <v>4.17962011024</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1180455888708706</v>
+        <v>0.1186596248917143</v>
       </c>
       <c r="T8">
-        <v>0.9416022119806378</v>
+        <v>0.9496051597660818</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2109,7 +2109,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>43.25066585181718</v>
+        <v>37.07199930155758</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2117,22 +2117,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1130998311492943</v>
+        <v>0.1128827687599703</v>
       </c>
       <c r="C9">
-        <v>35.90643513263586</v>
+        <v>35.58729186660495</v>
       </c>
       <c r="D9">
-        <v>31.88707513263586</v>
+        <v>31.94945186660495</v>
       </c>
       <c r="E9">
-        <v>2.11864</v>
+        <v>2.50016</v>
       </c>
       <c r="F9">
-        <v>2.67064</v>
+        <v>3.05216</v>
       </c>
       <c r="G9">
         <v>6.69</v>
@@ -2153,28 +2153,28 @@
         <v>4.98</v>
       </c>
       <c r="M9">
-        <v>0.134333192</v>
+        <v>0.153523648</v>
       </c>
       <c r="N9">
-        <v>4.845666808000001</v>
+        <v>4.826476352</v>
       </c>
       <c r="O9">
-        <v>1.06604669776</v>
+        <v>1.06182479744</v>
       </c>
       <c r="P9">
-        <v>3.779620110240001</v>
+        <v>3.76465155456</v>
       </c>
       <c r="Q9">
-        <v>4.17962011024</v>
+        <v>4.16465155456</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1186596248917143</v>
+        <v>0.1192870095217068</v>
       </c>
       <c r="T9">
-        <v>0.9496051597660821</v>
+        <v>0.9577820846772966</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2191,7 +2191,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>37.07199930155758</v>
+        <v>32.43799938886288</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2199,22 +2199,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1128827687599703</v>
+        <v>0.1126657063706463</v>
       </c>
       <c r="C10">
-        <v>35.58729186660495</v>
+        <v>35.2683931186456</v>
       </c>
       <c r="D10">
-        <v>31.94945186660495</v>
+        <v>32.01207311864561</v>
       </c>
       <c r="E10">
-        <v>2.50016</v>
+        <v>2.88168</v>
       </c>
       <c r="F10">
-        <v>3.05216</v>
+        <v>3.43368</v>
       </c>
       <c r="G10">
         <v>6.69</v>
@@ -2235,28 +2235,28 @@
         <v>4.98</v>
       </c>
       <c r="M10">
-        <v>0.153523648</v>
+        <v>0.172714104</v>
       </c>
       <c r="N10">
-        <v>4.826476352</v>
+        <v>4.807285896000001</v>
       </c>
       <c r="O10">
-        <v>1.06182479744</v>
+        <v>1.05760289712</v>
       </c>
       <c r="P10">
-        <v>3.76465155456</v>
+        <v>3.74968299888</v>
       </c>
       <c r="Q10">
-        <v>4.16465155456</v>
+        <v>4.149682998879999</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1192870095217068</v>
+        <v>0.119928182824886</v>
       </c>
       <c r="T10">
-        <v>0.9577820846772966</v>
+        <v>0.9661387222239227</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2273,7 +2273,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>32.43799938886288</v>
+        <v>28.83377723454479</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2281,22 +2281,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1126657063706463</v>
+        <v>0.1124486439813222</v>
       </c>
       <c r="C11">
-        <v>35.2683931186456</v>
+        <v>34.94974032935521</v>
       </c>
       <c r="D11">
-        <v>32.01207311864561</v>
+        <v>32.07494032935521</v>
       </c>
       <c r="E11">
-        <v>2.88168</v>
+        <v>3.2632</v>
       </c>
       <c r="F11">
-        <v>3.43368</v>
+        <v>3.8152</v>
       </c>
       <c r="G11">
         <v>6.69</v>
@@ -2317,28 +2317,28 @@
         <v>4.98</v>
       </c>
       <c r="M11">
-        <v>0.172714104</v>
+        <v>0.19190456</v>
       </c>
       <c r="N11">
-        <v>4.807285896000001</v>
+        <v>4.78809544</v>
       </c>
       <c r="O11">
-        <v>1.05760289712</v>
+        <v>1.0533809968</v>
       </c>
       <c r="P11">
-        <v>3.74968299888</v>
+        <v>3.7347144432</v>
       </c>
       <c r="Q11">
-        <v>4.149682998879999</v>
+        <v>4.1347144432</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.119928182824886</v>
+        <v>0.1205836044236913</v>
       </c>
       <c r="T11">
-        <v>0.9661387222239227</v>
+        <v>0.9746810628271404</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2355,7 +2355,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>28.83377723454479</v>
+        <v>25.95039951109031</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2363,22 +2363,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1124486439813222</v>
+        <v>0.1122315815919982</v>
       </c>
       <c r="C12">
-        <v>34.94974032935521</v>
+        <v>34.63133495066985</v>
       </c>
       <c r="D12">
-        <v>32.07494032935521</v>
+        <v>32.13805495066985</v>
       </c>
       <c r="E12">
-        <v>3.2632</v>
+        <v>3.64472</v>
       </c>
       <c r="F12">
-        <v>3.8152</v>
+        <v>4.19672</v>
       </c>
       <c r="G12">
         <v>6.69</v>
@@ -2399,28 +2399,28 @@
         <v>4.98</v>
       </c>
       <c r="M12">
-        <v>0.19190456</v>
+        <v>0.211095016</v>
       </c>
       <c r="N12">
-        <v>4.78809544</v>
+        <v>4.768904984000001</v>
       </c>
       <c r="O12">
-        <v>1.0533809968</v>
+        <v>1.04915909648</v>
       </c>
       <c r="P12">
-        <v>3.7347144432</v>
+        <v>3.71974588752</v>
       </c>
       <c r="Q12">
-        <v>4.1347144432</v>
+        <v>4.11974588752</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1205836044236913</v>
+        <v>0.1212537545977508</v>
       </c>
       <c r="T12">
-        <v>0.9746810628271404</v>
+        <v>0.9834153661405428</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2437,7 +2437,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>25.95039951109031</v>
+        <v>23.59127228280937</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1122315815919982</v>
+        <v>0.1120145192026741</v>
       </c>
       <c r="C13">
-        <v>34.63133495066985</v>
+        <v>34.31317844597626</v>
       </c>
       <c r="D13">
-        <v>32.13805495066985</v>
+        <v>32.20141844597626</v>
       </c>
       <c r="E13">
-        <v>3.64472</v>
+        <v>4.02624</v>
       </c>
       <c r="F13">
-        <v>4.19672</v>
+        <v>4.57824</v>
       </c>
       <c r="G13">
         <v>6.69</v>
@@ -2481,28 +2481,28 @@
         <v>4.98</v>
       </c>
       <c r="M13">
-        <v>0.211095016</v>
+        <v>0.230285472</v>
       </c>
       <c r="N13">
-        <v>4.768904984000001</v>
+        <v>4.749714528</v>
       </c>
       <c r="O13">
-        <v>1.04915909648</v>
+        <v>1.04493719616</v>
       </c>
       <c r="P13">
-        <v>3.71974588752</v>
+        <v>3.70477733184</v>
       </c>
       <c r="Q13">
-        <v>4.11974588752</v>
+        <v>4.104777331839999</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1212537545977508</v>
+        <v>0.1219391354575843</v>
       </c>
       <c r="T13">
-        <v>0.9834153661405428</v>
+        <v>0.9923481763474317</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2519,7 +2519,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>23.59127228280937</v>
+        <v>21.62533292590859</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2527,22 +2527,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1120145192026741</v>
+        <v>0.1117974568133501</v>
       </c>
       <c r="C14">
-        <v>34.31317844597626</v>
+        <v>33.9952722902248</v>
       </c>
       <c r="D14">
-        <v>32.20141844597626</v>
+        <v>32.2650322902248</v>
       </c>
       <c r="E14">
-        <v>4.02624</v>
+        <v>4.40776</v>
       </c>
       <c r="F14">
-        <v>4.57824</v>
+        <v>4.95976</v>
       </c>
       <c r="G14">
         <v>6.69</v>
@@ -2563,28 +2563,28 @@
         <v>4.98</v>
       </c>
       <c r="M14">
-        <v>0.230285472</v>
+        <v>0.249475928</v>
       </c>
       <c r="N14">
-        <v>4.749714528</v>
+        <v>4.730524072000001</v>
       </c>
       <c r="O14">
-        <v>1.04493719616</v>
+        <v>1.04071529584</v>
       </c>
       <c r="P14">
-        <v>3.70477733184</v>
+        <v>3.68980877616</v>
       </c>
       <c r="Q14">
-        <v>4.104777331839999</v>
+        <v>4.08980877616</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1219391354575843</v>
+        <v>0.122640272199253</v>
       </c>
       <c r="T14">
-        <v>0.9923481763474317</v>
+        <v>1.001486338513099</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2601,7 +2601,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>21.62533292590859</v>
+        <v>19.96184577776178</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2609,22 +2609,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1117974568133501</v>
+        <v>0.111580394424026</v>
       </c>
       <c r="C15">
-        <v>33.9952722902248</v>
+        <v>33.67761797004395</v>
       </c>
       <c r="D15">
-        <v>32.2650322902248</v>
+        <v>32.32889797004395</v>
       </c>
       <c r="E15">
-        <v>4.40776</v>
+        <v>4.78928</v>
       </c>
       <c r="F15">
-        <v>4.95976</v>
+        <v>5.34128</v>
       </c>
       <c r="G15">
         <v>6.69</v>
@@ -2645,28 +2645,28 @@
         <v>4.98</v>
       </c>
       <c r="M15">
-        <v>0.249475928</v>
+        <v>0.268666384</v>
       </c>
       <c r="N15">
-        <v>4.730524072000001</v>
+        <v>4.711333616</v>
       </c>
       <c r="O15">
-        <v>1.04071529584</v>
+        <v>1.03649339552</v>
       </c>
       <c r="P15">
-        <v>3.68980877616</v>
+        <v>3.67484022048</v>
       </c>
       <c r="Q15">
-        <v>4.08980877616</v>
+        <v>4.07484022048</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.122640272199253</v>
+        <v>0.1233577144465419</v>
       </c>
       <c r="T15">
-        <v>1.001486338513099</v>
+        <v>1.010837016077969</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2683,7 +2683,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>19.96184577776178</v>
+        <v>18.53599965077879</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2691,22 +2691,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.111580394424026</v>
+        <v>0.111363332034702</v>
       </c>
       <c r="C16">
-        <v>33.67761797004395</v>
+        <v>33.36021698385613</v>
       </c>
       <c r="D16">
-        <v>32.32889797004395</v>
+        <v>32.39301698385613</v>
       </c>
       <c r="E16">
-        <v>4.78928</v>
+        <v>5.170800000000002</v>
       </c>
       <c r="F16">
-        <v>5.34128</v>
+        <v>5.722800000000001</v>
       </c>
       <c r="G16">
         <v>6.69</v>
@@ -2727,28 +2727,28 @@
         <v>4.98</v>
       </c>
       <c r="M16">
-        <v>0.268666384</v>
+        <v>0.2878568400000001</v>
       </c>
       <c r="N16">
-        <v>4.711333616</v>
+        <v>4.692143160000001</v>
       </c>
       <c r="O16">
-        <v>1.03649339552</v>
+        <v>1.0322714952</v>
       </c>
       <c r="P16">
-        <v>3.67484022048</v>
+        <v>3.659871664800001</v>
       </c>
       <c r="Q16">
-        <v>4.07484022048</v>
+        <v>4.0598716648</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1233577144465419</v>
+        <v>0.1240920376878847</v>
       </c>
       <c r="T16">
-        <v>1.010837016077969</v>
+        <v>1.020407709585541</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>18.53599965077879</v>
+        <v>17.30026634072687</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2773,22 +2773,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.111363332034702</v>
+        <v>0.111146269645378</v>
       </c>
       <c r="C17">
-        <v>33.36021698385613</v>
+        <v>33.04307084199485</v>
       </c>
       <c r="D17">
-        <v>32.39301698385613</v>
+        <v>32.45739084199485</v>
       </c>
       <c r="E17">
-        <v>5.1708</v>
+        <v>5.55232</v>
       </c>
       <c r="F17">
-        <v>5.7228</v>
+        <v>6.10432</v>
       </c>
       <c r="G17">
         <v>6.69</v>
@@ -2809,28 +2809,28 @@
         <v>4.98</v>
       </c>
       <c r="M17">
-        <v>0.28785684</v>
+        <v>0.307047296</v>
       </c>
       <c r="N17">
-        <v>4.692143160000001</v>
+        <v>4.672952704</v>
       </c>
       <c r="O17">
-        <v>1.0322714952</v>
+        <v>1.02804959488</v>
       </c>
       <c r="P17">
-        <v>3.659871664800001</v>
+        <v>3.64490310912</v>
       </c>
       <c r="Q17">
-        <v>4.0598716648</v>
+        <v>4.04490310912</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1240920376878847</v>
+        <v>0.1248438448159262</v>
       </c>
       <c r="T17">
-        <v>1.020407709585541</v>
+        <v>1.030206276748056</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2847,7 +2847,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>17.30026634072687</v>
+        <v>16.21899969443144</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2855,22 +2855,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.111146269645378</v>
+        <v>0.1109292072560539</v>
       </c>
       <c r="C18">
-        <v>33.04307084199485</v>
+        <v>32.72618106682335</v>
       </c>
       <c r="D18">
-        <v>32.45739084199485</v>
+        <v>32.52202106682336</v>
       </c>
       <c r="E18">
-        <v>5.55232</v>
+        <v>5.93384</v>
       </c>
       <c r="F18">
-        <v>6.10432</v>
+        <v>6.48584</v>
       </c>
       <c r="G18">
         <v>6.69</v>
@@ -2891,28 +2891,28 @@
         <v>4.98</v>
       </c>
       <c r="M18">
-        <v>0.307047296</v>
+        <v>0.326237752</v>
       </c>
       <c r="N18">
-        <v>4.672952704</v>
+        <v>4.653762248</v>
       </c>
       <c r="O18">
-        <v>1.02804959488</v>
+        <v>1.02382769456</v>
       </c>
       <c r="P18">
-        <v>3.64490310912</v>
+        <v>3.62993455344</v>
       </c>
       <c r="Q18">
-        <v>4.04490310912</v>
+        <v>4.02993455344</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1248438448159262</v>
+        <v>0.1256137677783782</v>
       </c>
       <c r="T18">
-        <v>1.030206276748056</v>
+        <v>1.040240953962679</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2929,7 +2929,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>16.21899969443144</v>
+        <v>15.26494088887665</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2937,22 +2937,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1109292072560539</v>
+        <v>0.1107121448667299</v>
       </c>
       <c r="C19">
-        <v>32.72618106682335</v>
+        <v>32.40954919285459</v>
       </c>
       <c r="D19">
-        <v>32.52202106682336</v>
+        <v>32.58690919285459</v>
       </c>
       <c r="E19">
-        <v>5.93384</v>
+        <v>6.31536</v>
       </c>
       <c r="F19">
-        <v>6.48584</v>
+        <v>6.867360000000001</v>
       </c>
       <c r="G19">
         <v>6.69</v>
@@ -2973,28 +2973,28 @@
         <v>4.98</v>
       </c>
       <c r="M19">
-        <v>0.326237752</v>
+        <v>0.345428208</v>
       </c>
       <c r="N19">
-        <v>4.653762248</v>
+        <v>4.634571792</v>
       </c>
       <c r="O19">
-        <v>1.02382769456</v>
+        <v>1.01960579424</v>
       </c>
       <c r="P19">
-        <v>3.62993455344</v>
+        <v>3.61496599776</v>
       </c>
       <c r="Q19">
-        <v>4.02993455344</v>
+        <v>4.014965997759999</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1256137677783782</v>
+        <v>0.1264024693496706</v>
       </c>
       <c r="T19">
-        <v>1.040240953962679</v>
+        <v>1.050520379402049</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -3011,7 +3011,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>15.26494088887665</v>
+        <v>14.41688861727239</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3019,22 +3019,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1107121448667299</v>
+        <v>0.1104950824774059</v>
       </c>
       <c r="C20">
-        <v>32.40954919285459</v>
+        <v>32.09317676687266</v>
       </c>
       <c r="D20">
-        <v>32.58690919285459</v>
+        <v>32.65205676687266</v>
       </c>
       <c r="E20">
-        <v>6.31536</v>
+        <v>6.69688</v>
       </c>
       <c r="F20">
-        <v>6.86736</v>
+        <v>7.248880000000001</v>
       </c>
       <c r="G20">
         <v>6.69</v>
@@ -3055,28 +3055,28 @@
         <v>4.98</v>
       </c>
       <c r="M20">
-        <v>0.345428208</v>
+        <v>0.364618664</v>
       </c>
       <c r="N20">
-        <v>4.634571792000001</v>
+        <v>4.615381336</v>
       </c>
       <c r="O20">
-        <v>1.01960579424</v>
+        <v>1.01538389392</v>
       </c>
       <c r="P20">
-        <v>3.614965997760001</v>
+        <v>3.59999744208</v>
       </c>
       <c r="Q20">
-        <v>4.01496599776</v>
+        <v>3.99999744208</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1264024693496706</v>
+        <v>0.1272106450338344</v>
       </c>
       <c r="T20">
-        <v>1.050520379402049</v>
+        <v>1.061053617815231</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -3093,7 +3093,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>14.4168886172724</v>
+        <v>13.658105005837</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3101,22 +3101,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1104950824774059</v>
+        <v>0.1102780200880818</v>
       </c>
       <c r="C21">
-        <v>32.09317676687266</v>
+        <v>31.77706534805571</v>
       </c>
       <c r="D21">
-        <v>32.65205676687266</v>
+        <v>32.71746534805572</v>
       </c>
       <c r="E21">
-        <v>6.69688</v>
+        <v>7.0784</v>
       </c>
       <c r="F21">
-        <v>7.248880000000001</v>
+        <v>7.630400000000001</v>
       </c>
       <c r="G21">
         <v>6.69</v>
@@ -3137,28 +3137,28 @@
         <v>4.98</v>
       </c>
       <c r="M21">
-        <v>0.364618664</v>
+        <v>0.38380912</v>
       </c>
       <c r="N21">
-        <v>4.615381336</v>
+        <v>4.59619088</v>
       </c>
       <c r="O21">
-        <v>1.01538389392</v>
+        <v>1.0111619936</v>
       </c>
       <c r="P21">
-        <v>3.59999744208</v>
+        <v>3.5850288864</v>
       </c>
       <c r="Q21">
-        <v>3.99999744208</v>
+        <v>3.985028886399999</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1272106450338344</v>
+        <v>0.1280390251101023</v>
       </c>
       <c r="T21">
-        <v>1.061053617815231</v>
+        <v>1.071850187188742</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3175,7 +3175,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>13.658105005837</v>
+        <v>12.97519975554515</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3183,22 +3183,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1102780200880818</v>
+        <v>0.1103066576987578</v>
       </c>
       <c r="C22">
-        <v>31.77706534805571</v>
+        <v>31.38690082026216</v>
       </c>
       <c r="D22">
-        <v>32.71746534805572</v>
+        <v>32.70882082026216</v>
       </c>
       <c r="E22">
-        <v>7.0784</v>
+        <v>7.459920000000002</v>
       </c>
       <c r="F22">
-        <v>7.630400000000001</v>
+        <v>8.011920000000002</v>
       </c>
       <c r="G22">
         <v>6.69</v>
@@ -3219,45 +3219,45 @@
         <v>4.98</v>
       </c>
       <c r="M22">
-        <v>0.38380912</v>
+        <v>0.4150174560000001</v>
       </c>
       <c r="N22">
-        <v>4.59619088</v>
+        <v>4.564982544</v>
       </c>
       <c r="O22">
-        <v>1.0111619936</v>
+        <v>1.00429615968</v>
       </c>
       <c r="P22">
-        <v>3.5850288864</v>
+        <v>3.56068638432</v>
       </c>
       <c r="Q22">
-        <v>3.985028886399999</v>
+        <v>3.96068638432</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1280390251101023</v>
+        <v>0.1288883768338706</v>
       </c>
       <c r="T22">
-        <v>1.071850187188742</v>
+        <v>1.082920087432469</v>
       </c>
       <c r="U22">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V22">
         <v>0.22</v>
       </c>
       <c r="W22">
-        <v>0.039234</v>
+        <v>0.040404</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y22">
-        <v>12.97519975554515</v>
+        <v>11.99949526942308</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3265,22 +3265,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1103066576987578</v>
+        <v>0.1101012953094338</v>
       </c>
       <c r="C23">
-        <v>31.38690082026217</v>
+        <v>31.06747262568485</v>
       </c>
       <c r="D23">
-        <v>32.70882082026218</v>
+        <v>32.77091262568485</v>
       </c>
       <c r="E23">
-        <v>7.45992</v>
+        <v>7.84144</v>
       </c>
       <c r="F23">
-        <v>8.01192</v>
+        <v>8.39344</v>
       </c>
       <c r="G23">
         <v>6.69</v>
@@ -3301,28 +3301,28 @@
         <v>4.98</v>
       </c>
       <c r="M23">
-        <v>0.415017456</v>
+        <v>0.434780192</v>
       </c>
       <c r="N23">
-        <v>4.564982544</v>
+        <v>4.545219808000001</v>
       </c>
       <c r="O23">
-        <v>1.00429615968</v>
+        <v>0.9999483577600001</v>
       </c>
       <c r="P23">
-        <v>3.56068638432</v>
+        <v>3.54527145024</v>
       </c>
       <c r="Q23">
-        <v>3.96068638432</v>
+        <v>3.94527145024</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1288883768338706</v>
+        <v>0.1297595068069664</v>
       </c>
       <c r="T23">
-        <v>1.082920087432468</v>
+        <v>1.094273831272188</v>
       </c>
       <c r="U23">
         <v>0.0518</v>
@@ -3339,7 +3339,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>11.99949526942308</v>
+        <v>11.45406366626748</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3347,22 +3347,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1101012953094338</v>
+        <v>0.1098959329201097</v>
       </c>
       <c r="C24">
-        <v>31.06747262568485</v>
+        <v>30.74828061968854</v>
       </c>
       <c r="D24">
-        <v>32.77091262568485</v>
+        <v>32.83324061968855</v>
       </c>
       <c r="E24">
-        <v>7.84144</v>
+        <v>8.22296</v>
       </c>
       <c r="F24">
-        <v>8.39344</v>
+        <v>8.77496</v>
       </c>
       <c r="G24">
         <v>6.69</v>
@@ -3383,28 +3383,28 @@
         <v>4.98</v>
       </c>
       <c r="M24">
-        <v>0.434780192</v>
+        <v>0.454542928</v>
       </c>
       <c r="N24">
-        <v>4.545219808000001</v>
+        <v>4.525457072</v>
       </c>
       <c r="O24">
-        <v>0.9999483577600001</v>
+        <v>0.99560055584</v>
       </c>
       <c r="P24">
-        <v>3.54527145024</v>
+        <v>3.52985651616</v>
       </c>
       <c r="Q24">
-        <v>3.94527145024</v>
+        <v>3.92985651616</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1297595068069664</v>
+        <v>0.13065326353261</v>
       </c>
       <c r="T24">
-        <v>1.094273831272188</v>
+        <v>1.105922477549304</v>
       </c>
       <c r="U24">
         <v>0.0518</v>
@@ -3421,7 +3421,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>11.45406366626748</v>
+        <v>10.9560608981689</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3429,22 +3429,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1098959329201097</v>
+        <v>0.1096905705307857</v>
       </c>
       <c r="C25">
-        <v>30.74828061968854</v>
+        <v>30.42932615248399</v>
       </c>
       <c r="D25">
-        <v>32.83324061968855</v>
+        <v>32.89580615248399</v>
       </c>
       <c r="E25">
-        <v>8.22296</v>
+        <v>8.604480000000001</v>
       </c>
       <c r="F25">
-        <v>8.77496</v>
+        <v>9.15648</v>
       </c>
       <c r="G25">
         <v>6.69</v>
@@ -3465,28 +3465,28 @@
         <v>4.98</v>
       </c>
       <c r="M25">
-        <v>0.454542928</v>
+        <v>0.474305664</v>
       </c>
       <c r="N25">
-        <v>4.525457072</v>
+        <v>4.505694336</v>
       </c>
       <c r="O25">
-        <v>0.99560055584</v>
+        <v>0.9912527539200001</v>
       </c>
       <c r="P25">
-        <v>3.52985651616</v>
+        <v>3.51444158208</v>
       </c>
       <c r="Q25">
-        <v>3.92985651616</v>
+        <v>3.91444158208</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.13065326353261</v>
+        <v>0.1315705401720864</v>
       </c>
       <c r="T25">
-        <v>1.105922477549304</v>
+        <v>1.1178776671495</v>
       </c>
       <c r="U25">
         <v>0.0518</v>
@@ -3503,7 +3503,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>10.9560608981689</v>
+        <v>10.49955836074519</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1096905705307857</v>
+        <v>0.1094852081414616</v>
       </c>
       <c r="C26">
-        <v>30.42932615248399</v>
+        <v>30.11061058459315</v>
       </c>
       <c r="D26">
-        <v>32.89580615248399</v>
+        <v>32.95861058459315</v>
       </c>
       <c r="E26">
-        <v>8.604480000000001</v>
+        <v>8.986000000000001</v>
       </c>
       <c r="F26">
-        <v>9.15648</v>
+        <v>9.538</v>
       </c>
       <c r="G26">
         <v>6.69</v>
@@ -3547,28 +3547,28 @@
         <v>4.98</v>
       </c>
       <c r="M26">
-        <v>0.474305664</v>
+        <v>0.4940684</v>
       </c>
       <c r="N26">
-        <v>4.505694336</v>
+        <v>4.485931600000001</v>
       </c>
       <c r="O26">
-        <v>0.9912527539200001</v>
+        <v>0.9869049520000002</v>
       </c>
       <c r="P26">
-        <v>3.51444158208</v>
+        <v>3.499026648000001</v>
       </c>
       <c r="Q26">
-        <v>3.91444158208</v>
+        <v>3.899026648</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1315705401720864</v>
+        <v>0.1325122775219488</v>
       </c>
       <c r="T26">
-        <v>1.1178776671495</v>
+        <v>1.130151661805703</v>
       </c>
       <c r="U26">
         <v>0.0518</v>
@@ -3585,7 +3585,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>10.49955836074519</v>
+        <v>10.07957602631538</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3593,22 +3593,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1094852081414616</v>
+        <v>0.1096246057521376</v>
       </c>
       <c r="C27">
-        <v>30.11061058459315</v>
+        <v>29.68643355390894</v>
       </c>
       <c r="D27">
-        <v>32.95861058459315</v>
+        <v>32.91595355390894</v>
       </c>
       <c r="E27">
-        <v>8.986000000000001</v>
+        <v>9.367520000000001</v>
       </c>
       <c r="F27">
-        <v>9.538</v>
+        <v>9.91952</v>
       </c>
       <c r="G27">
         <v>6.69</v>
@@ -3629,45 +3629,45 @@
         <v>4.98</v>
       </c>
       <c r="M27">
-        <v>0.4940684</v>
+        <v>0.5306943200000001</v>
       </c>
       <c r="N27">
-        <v>4.485931600000001</v>
+        <v>4.44930568</v>
       </c>
       <c r="O27">
-        <v>0.9869049520000002</v>
+        <v>0.9788472496</v>
       </c>
       <c r="P27">
-        <v>3.499026648000001</v>
+        <v>3.4704584304</v>
       </c>
       <c r="Q27">
-        <v>3.899026648</v>
+        <v>3.870458430399999</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1325122775219488</v>
+        <v>0.1334794672326184</v>
       </c>
       <c r="T27">
-        <v>1.130151661805703</v>
+        <v>1.142757386047208</v>
       </c>
       <c r="U27">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V27">
         <v>0.22</v>
       </c>
       <c r="W27">
-        <v>0.040404</v>
+        <v>0.04173</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y27">
-        <v>10.07957602631538</v>
+        <v>9.383933108611375</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3675,22 +3675,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1096246057521376</v>
+        <v>0.1094325033628136</v>
       </c>
       <c r="C28">
-        <v>29.68643355390894</v>
+        <v>29.36372757947719</v>
       </c>
       <c r="D28">
-        <v>32.91595355390894</v>
+        <v>32.97476757947719</v>
       </c>
       <c r="E28">
-        <v>9.367520000000001</v>
+        <v>9.749040000000001</v>
       </c>
       <c r="F28">
-        <v>9.91952</v>
+        <v>10.30104</v>
       </c>
       <c r="G28">
         <v>6.69</v>
@@ -3711,28 +3711,28 @@
         <v>4.98</v>
       </c>
       <c r="M28">
-        <v>0.5306943200000001</v>
+        <v>0.5511056400000001</v>
       </c>
       <c r="N28">
-        <v>4.44930568</v>
+        <v>4.42889436</v>
       </c>
       <c r="O28">
-        <v>0.9788472496</v>
+        <v>0.9743567592000001</v>
       </c>
       <c r="P28">
-        <v>3.4704584304</v>
+        <v>3.4545376008</v>
       </c>
       <c r="Q28">
-        <v>3.870458430399999</v>
+        <v>3.8545376008</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1334794672326184</v>
+        <v>0.1344731552915254</v>
       </c>
       <c r="T28">
-        <v>1.142757386047208</v>
+        <v>1.155708472596699</v>
       </c>
       <c r="U28">
         <v>0.0535</v>
@@ -3749,7 +3749,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>9.383933108611375</v>
+        <v>9.036380030514657</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3757,22 +3757,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1094325033628136</v>
+        <v>0.1092404009734895</v>
       </c>
       <c r="C29">
-        <v>29.36372757947719</v>
+        <v>29.04123215834696</v>
       </c>
       <c r="D29">
-        <v>32.97476757947719</v>
+        <v>33.03379215834696</v>
       </c>
       <c r="E29">
-        <v>9.749040000000001</v>
+        <v>10.13056</v>
       </c>
       <c r="F29">
-        <v>10.30104</v>
+        <v>10.68256</v>
       </c>
       <c r="G29">
         <v>6.69</v>
@@ -3793,28 +3793,28 @@
         <v>4.98</v>
       </c>
       <c r="M29">
-        <v>0.5511056400000001</v>
+        <v>0.57151696</v>
       </c>
       <c r="N29">
-        <v>4.42889436</v>
+        <v>4.40848304</v>
       </c>
       <c r="O29">
-        <v>0.9743567592000001</v>
+        <v>0.9698662688</v>
       </c>
       <c r="P29">
-        <v>3.4545376008</v>
+        <v>3.4386167712</v>
       </c>
       <c r="Q29">
-        <v>3.8545376008</v>
+        <v>3.838616771199999</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1344731552915254</v>
+        <v>0.1354944457965132</v>
       </c>
       <c r="T29">
-        <v>1.155708472596699</v>
+        <v>1.169019311550343</v>
       </c>
       <c r="U29">
         <v>0.0535</v>
@@ -3831,7 +3831,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>9.036380030514657</v>
+        <v>8.713652172281993</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3839,22 +3839,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1092404009734895</v>
+        <v>0.1090482985841655</v>
       </c>
       <c r="C30">
-        <v>29.04123215834696</v>
+        <v>28.71894842321214</v>
       </c>
       <c r="D30">
-        <v>33.03379215834696</v>
+        <v>33.09302842321215</v>
       </c>
       <c r="E30">
-        <v>10.13056</v>
+        <v>10.51208</v>
       </c>
       <c r="F30">
-        <v>10.68256</v>
+        <v>11.06408</v>
       </c>
       <c r="G30">
         <v>6.69</v>
@@ -3875,28 +3875,28 @@
         <v>4.98</v>
       </c>
       <c r="M30">
-        <v>0.57151696</v>
+        <v>0.5919282800000001</v>
       </c>
       <c r="N30">
-        <v>4.40848304</v>
+        <v>4.38807172</v>
       </c>
       <c r="O30">
-        <v>0.9698662688</v>
+        <v>0.9653757784</v>
       </c>
       <c r="P30">
-        <v>3.4386167712</v>
+        <v>3.4226959416</v>
       </c>
       <c r="Q30">
-        <v>3.838616771199999</v>
+        <v>3.8226959416</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1354944457965132</v>
+        <v>0.1365445050481204</v>
       </c>
       <c r="T30">
-        <v>1.169019311550343</v>
+        <v>1.182705103713949</v>
       </c>
       <c r="U30">
         <v>0.0535</v>
@@ -3913,7 +3913,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>8.713652172281993</v>
+        <v>8.413181407720543</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3921,22 +3921,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1090482985841655</v>
+        <v>0.1088561961948415</v>
       </c>
       <c r="C31">
-        <v>28.71894842321215</v>
+        <v>28.39687751490577</v>
       </c>
       <c r="D31">
-        <v>33.09302842321215</v>
+        <v>33.15247751490578</v>
       </c>
       <c r="E31">
-        <v>10.51208</v>
+        <v>10.8936</v>
       </c>
       <c r="F31">
-        <v>11.06408</v>
+        <v>11.4456</v>
       </c>
       <c r="G31">
         <v>6.69</v>
@@ -3957,28 +3957,28 @@
         <v>4.98</v>
       </c>
       <c r="M31">
-        <v>0.59192828</v>
+        <v>0.6123396</v>
       </c>
       <c r="N31">
-        <v>4.38807172</v>
+        <v>4.3676604</v>
       </c>
       <c r="O31">
-        <v>0.9653757784</v>
+        <v>0.9608852880000001</v>
       </c>
       <c r="P31">
-        <v>3.4226959416</v>
+        <v>3.406775112</v>
       </c>
       <c r="Q31">
-        <v>3.8226959416</v>
+        <v>3.806775112</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1365445050481204</v>
+        <v>0.1376245659926306</v>
       </c>
       <c r="T31">
-        <v>1.182705103713949</v>
+        <v>1.196781918510801</v>
       </c>
       <c r="U31">
         <v>0.0535</v>
@@ -3995,7 +3995,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>8.413181407720543</v>
+        <v>8.132742027463191</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4003,22 +4003,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1088561961948415</v>
+        <v>0.1086640938055174</v>
       </c>
       <c r="C32">
-        <v>28.39687751490577</v>
+        <v>28.07502058247334</v>
       </c>
       <c r="D32">
-        <v>33.15247751490578</v>
+        <v>33.21214058247335</v>
       </c>
       <c r="E32">
-        <v>10.8936</v>
+        <v>11.27512</v>
       </c>
       <c r="F32">
-        <v>11.4456</v>
+        <v>11.82712</v>
       </c>
       <c r="G32">
         <v>6.69</v>
@@ -4039,28 +4039,28 @@
         <v>4.98</v>
       </c>
       <c r="M32">
-        <v>0.6123396</v>
+        <v>0.63275092</v>
       </c>
       <c r="N32">
-        <v>4.3676604</v>
+        <v>4.34724908</v>
       </c>
       <c r="O32">
-        <v>0.9608852880000001</v>
+        <v>0.9563947976</v>
       </c>
       <c r="P32">
-        <v>3.406775112</v>
+        <v>3.3908542824</v>
       </c>
       <c r="Q32">
-        <v>3.806775112</v>
+        <v>3.7908542824</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1376245659926306</v>
+        <v>0.1387359330514745</v>
       </c>
       <c r="T32">
-        <v>1.196781918510801</v>
+        <v>1.211266756924953</v>
       </c>
       <c r="U32">
         <v>0.0535</v>
@@ -4077,7 +4077,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>8.132742027463191</v>
+        <v>7.87039551044825</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4085,22 +4085,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1086640938055174</v>
+        <v>0.1084719914161934</v>
       </c>
       <c r="C33">
-        <v>28.07502058247334</v>
+        <v>27.75337878324677</v>
       </c>
       <c r="D33">
-        <v>33.21214058247335</v>
+        <v>33.27201878324677</v>
       </c>
       <c r="E33">
-        <v>11.27512</v>
+        <v>11.65664</v>
       </c>
       <c r="F33">
-        <v>11.82712</v>
+        <v>12.20864</v>
       </c>
       <c r="G33">
         <v>6.69</v>
@@ -4121,28 +4121,28 @@
         <v>4.98</v>
       </c>
       <c r="M33">
-        <v>0.63275092</v>
+        <v>0.65316224</v>
       </c>
       <c r="N33">
-        <v>4.34724908</v>
+        <v>4.32683776</v>
       </c>
       <c r="O33">
-        <v>0.9563947976</v>
+        <v>0.9519043072000001</v>
       </c>
       <c r="P33">
-        <v>3.3908542824</v>
+        <v>3.3749334528</v>
       </c>
       <c r="Q33">
-        <v>3.7908542824</v>
+        <v>3.7749334528</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1387359330514745</v>
+        <v>0.139879987376755</v>
       </c>
       <c r="T33">
-        <v>1.211266756924953</v>
+        <v>1.226177619998344</v>
       </c>
       <c r="U33">
         <v>0.0535</v>
@@ -4159,7 +4159,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>7.87039551044825</v>
+        <v>7.624445650746742</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4167,22 +4167,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1084719914161934</v>
+        <v>0.1084858090268693</v>
       </c>
       <c r="C34">
-        <v>27.75337878324677</v>
+        <v>27.36754463666647</v>
       </c>
       <c r="D34">
-        <v>33.27201878324677</v>
+        <v>33.26770463666647</v>
       </c>
       <c r="E34">
-        <v>11.65664</v>
+        <v>12.03816</v>
       </c>
       <c r="F34">
-        <v>12.20864</v>
+        <v>12.59016</v>
       </c>
       <c r="G34">
         <v>6.69</v>
@@ -4203,45 +4203,45 @@
         <v>4.98</v>
       </c>
       <c r="M34">
-        <v>0.65316224</v>
+        <v>0.683645688</v>
       </c>
       <c r="N34">
-        <v>4.32683776</v>
+        <v>4.296354312</v>
       </c>
       <c r="O34">
-        <v>0.9519043072000001</v>
+        <v>0.9451979486400001</v>
       </c>
       <c r="P34">
-        <v>3.3749334528</v>
+        <v>3.35115636336</v>
       </c>
       <c r="Q34">
-        <v>3.7749334528</v>
+        <v>3.751156363359999</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.139879987376755</v>
+        <v>0.1410581925774169</v>
       </c>
       <c r="T34">
-        <v>1.226177619998344</v>
+        <v>1.241533583461986</v>
       </c>
       <c r="U34">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V34">
         <v>0.22</v>
       </c>
       <c r="W34">
-        <v>0.04173</v>
+        <v>0.042354</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y34">
-        <v>7.624445650746742</v>
+        <v>7.284475112494237</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4249,22 +4249,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1084858090268693</v>
+        <v>0.1082999466375453</v>
       </c>
       <c r="C35">
-        <v>27.36754463666647</v>
+        <v>27.04414860597355</v>
       </c>
       <c r="D35">
-        <v>33.26770463666647</v>
+        <v>33.32582860597355</v>
       </c>
       <c r="E35">
-        <v>12.03816</v>
+        <v>12.41968</v>
       </c>
       <c r="F35">
-        <v>12.59016</v>
+        <v>12.97168</v>
       </c>
       <c r="G35">
         <v>6.69</v>
@@ -4285,28 +4285,28 @@
         <v>4.98</v>
       </c>
       <c r="M35">
-        <v>0.683645688</v>
+        <v>0.704362224</v>
       </c>
       <c r="N35">
-        <v>4.296354312</v>
+        <v>4.275637776</v>
       </c>
       <c r="O35">
-        <v>0.9451979486400001</v>
+        <v>0.94064031072</v>
       </c>
       <c r="P35">
-        <v>3.35115636336</v>
+        <v>3.33499746528</v>
       </c>
       <c r="Q35">
-        <v>3.751156363359999</v>
+        <v>3.734997465279999</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1410581925774169</v>
+        <v>0.1422721009659777</v>
       </c>
       <c r="T35">
-        <v>1.241533583461986</v>
+        <v>1.257354879151799</v>
       </c>
       <c r="U35">
         <v>0.0543</v>
@@ -4323,7 +4323,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>7.284475112494237</v>
+        <v>7.0702258444797</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4331,22 +4331,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1082999466375453</v>
+        <v>0.1081140842482212</v>
       </c>
       <c r="C36">
-        <v>27.04414860597355</v>
+        <v>26.72095603438732</v>
       </c>
       <c r="D36">
-        <v>33.32582860597355</v>
+        <v>33.38415603438732</v>
       </c>
       <c r="E36">
-        <v>12.41968</v>
+        <v>12.8012</v>
       </c>
       <c r="F36">
-        <v>12.97168</v>
+        <v>13.3532</v>
       </c>
       <c r="G36">
         <v>6.69</v>
@@ -4367,28 +4367,28 @@
         <v>4.98</v>
       </c>
       <c r="M36">
-        <v>0.704362224</v>
+        <v>0.72507876</v>
       </c>
       <c r="N36">
-        <v>4.275637776</v>
+        <v>4.254921240000001</v>
       </c>
       <c r="O36">
-        <v>0.94064031072</v>
+        <v>0.9360826728000001</v>
       </c>
       <c r="P36">
-        <v>3.33499746528</v>
+        <v>3.318838567200001</v>
       </c>
       <c r="Q36">
-        <v>3.734997465279999</v>
+        <v>3.7188385672</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1422721009659777</v>
+        <v>0.1435233603818789</v>
       </c>
       <c r="T36">
-        <v>1.257354879151799</v>
+        <v>1.27366298393976</v>
       </c>
       <c r="U36">
         <v>0.0543</v>
@@ -4405,7 +4405,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>7.0702258444797</v>
+        <v>6.868219391780281</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4413,22 +4413,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1081140842482212</v>
+        <v>0.1079282218588972</v>
       </c>
       <c r="C37">
-        <v>26.72095603438732</v>
+        <v>26.3979679920735</v>
       </c>
       <c r="D37">
-        <v>33.38415603438732</v>
+        <v>33.4426879920735</v>
       </c>
       <c r="E37">
-        <v>12.8012</v>
+        <v>13.18272</v>
       </c>
       <c r="F37">
-        <v>13.3532</v>
+        <v>13.73472</v>
       </c>
       <c r="G37">
         <v>6.69</v>
@@ -4449,28 +4449,28 @@
         <v>4.98</v>
       </c>
       <c r="M37">
-        <v>0.72507876</v>
+        <v>0.7457952960000001</v>
       </c>
       <c r="N37">
-        <v>4.254921240000001</v>
+        <v>4.234204704000001</v>
       </c>
       <c r="O37">
-        <v>0.9360826728000001</v>
+        <v>0.9315250348800002</v>
       </c>
       <c r="P37">
-        <v>3.318838567200001</v>
+        <v>3.302679669120001</v>
       </c>
       <c r="Q37">
-        <v>3.7188385672</v>
+        <v>3.70267966912</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1435233603818789</v>
+        <v>0.1448137216545269</v>
       </c>
       <c r="T37">
-        <v>1.27366298393976</v>
+        <v>1.290480717002345</v>
       </c>
       <c r="U37">
         <v>0.0543</v>
@@ -4487,7 +4487,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>6.868219391780281</v>
+        <v>6.677435519786385</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4495,22 +4495,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1079282218588972</v>
+        <v>0.1077423594695732</v>
       </c>
       <c r="C38">
-        <v>26.39796799207349</v>
+        <v>26.07518555671621</v>
       </c>
       <c r="D38">
-        <v>33.44268799207349</v>
+        <v>33.50142555671621</v>
       </c>
       <c r="E38">
-        <v>13.18272</v>
+        <v>13.56424</v>
       </c>
       <c r="F38">
-        <v>13.73472</v>
+        <v>14.11624</v>
       </c>
       <c r="G38">
         <v>6.69</v>
@@ -4531,28 +4531,28 @@
         <v>4.98</v>
       </c>
       <c r="M38">
-        <v>0.7457952959999999</v>
+        <v>0.7665118319999999</v>
       </c>
       <c r="N38">
-        <v>4.234204704000001</v>
+        <v>4.213488168</v>
       </c>
       <c r="O38">
-        <v>0.9315250348800002</v>
+        <v>0.9269673969600001</v>
       </c>
       <c r="P38">
-        <v>3.302679669120001</v>
+        <v>3.28652077104</v>
       </c>
       <c r="Q38">
-        <v>3.70267966912</v>
+        <v>3.68652077104</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1448137216545269</v>
+        <v>0.1461450467771003</v>
       </c>
       <c r="T38">
-        <v>1.290480717002345</v>
+        <v>1.307832346352631</v>
       </c>
       <c r="U38">
         <v>0.0543</v>
@@ -4569,7 +4569,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>6.677435519786385</v>
+        <v>6.496964289521888</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1077423594695732</v>
+        <v>0.1075564970802491</v>
       </c>
       <c r="C39">
-        <v>26.07518555671621</v>
+        <v>25.75260981358414</v>
       </c>
       <c r="D39">
-        <v>33.50142555671621</v>
+        <v>33.56036981358415</v>
       </c>
       <c r="E39">
-        <v>13.56424</v>
+        <v>13.94576</v>
       </c>
       <c r="F39">
-        <v>14.11624</v>
+        <v>14.49776</v>
       </c>
       <c r="G39">
         <v>6.69</v>
@@ -4613,28 +4613,28 @@
         <v>4.98</v>
       </c>
       <c r="M39">
-        <v>0.7665118319999999</v>
+        <v>0.7872283680000001</v>
       </c>
       <c r="N39">
-        <v>4.213488168</v>
+        <v>4.192771632</v>
       </c>
       <c r="O39">
-        <v>0.9269673969600001</v>
+        <v>0.9224097590400001</v>
       </c>
       <c r="P39">
-        <v>3.28652077104</v>
+        <v>3.27036187296</v>
       </c>
       <c r="Q39">
-        <v>3.68652077104</v>
+        <v>3.67036187296</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1461450467771003</v>
+        <v>0.1475193178713696</v>
       </c>
       <c r="T39">
-        <v>1.307832346352631</v>
+        <v>1.325743705681958</v>
       </c>
       <c r="U39">
         <v>0.0543</v>
@@ -4651,7 +4651,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>6.496964289521888</v>
+        <v>6.325991545060785</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4659,22 +4659,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1075564970802491</v>
+        <v>0.1073706346909251</v>
       </c>
       <c r="C40">
-        <v>25.75260981358414</v>
+        <v>25.43024185559734</v>
       </c>
       <c r="D40">
-        <v>33.56036981358415</v>
+        <v>33.61952185559735</v>
       </c>
       <c r="E40">
-        <v>13.94576</v>
+        <v>14.32728</v>
       </c>
       <c r="F40">
-        <v>14.49776</v>
+        <v>14.87928</v>
       </c>
       <c r="G40">
         <v>6.69</v>
@@ -4695,28 +4695,28 @@
         <v>4.98</v>
       </c>
       <c r="M40">
-        <v>0.7872283680000001</v>
+        <v>0.8079449040000001</v>
       </c>
       <c r="N40">
-        <v>4.192771632</v>
+        <v>4.172055096</v>
       </c>
       <c r="O40">
-        <v>0.9224097590400001</v>
+        <v>0.91785212112</v>
       </c>
       <c r="P40">
-        <v>3.27036187296</v>
+        <v>3.25420297488</v>
       </c>
       <c r="Q40">
-        <v>3.67036187296</v>
+        <v>3.65420297488</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1475193178713696</v>
+        <v>0.1489386470343035</v>
       </c>
       <c r="T40">
-        <v>1.325743705681958</v>
+        <v>1.344242322694215</v>
       </c>
       <c r="U40">
         <v>0.0543</v>
@@ -4733,7 +4733,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>6.325991545060785</v>
+        <v>6.16378663364897</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4741,22 +4741,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1073706346909251</v>
+        <v>0.1074967723016011</v>
       </c>
       <c r="C41">
-        <v>25.43024185559734</v>
+        <v>25.00855494428349</v>
       </c>
       <c r="D41">
-        <v>33.61952185559735</v>
+        <v>33.57935494428349</v>
       </c>
       <c r="E41">
-        <v>14.32728</v>
+        <v>14.7088</v>
       </c>
       <c r="F41">
-        <v>14.87928</v>
+        <v>15.2608</v>
       </c>
       <c r="G41">
         <v>6.69</v>
@@ -4777,45 +4777,45 @@
         <v>4.98</v>
       </c>
       <c r="M41">
-        <v>0.8079449040000001</v>
+        <v>0.8439222400000002</v>
       </c>
       <c r="N41">
-        <v>4.172055096</v>
+        <v>4.13607776</v>
       </c>
       <c r="O41">
-        <v>0.91785212112</v>
+        <v>0.9099371072</v>
       </c>
       <c r="P41">
-        <v>3.25420297488</v>
+        <v>3.2261406528</v>
       </c>
       <c r="Q41">
-        <v>3.65420297488</v>
+        <v>3.626140652799999</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1489386470343035</v>
+        <v>0.1504052871693351</v>
       </c>
       <c r="T41">
-        <v>1.344242322694215</v>
+        <v>1.363357560273546</v>
       </c>
       <c r="U41">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V41">
         <v>0.22</v>
       </c>
       <c r="W41">
-        <v>0.042354</v>
+        <v>0.04313400000000001</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y41">
-        <v>6.16378663364897</v>
+        <v>5.901017610342866</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4823,22 +4823,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1074967723016011</v>
+        <v>0.107318709912277</v>
       </c>
       <c r="C42">
-        <v>25.00855494428349</v>
+        <v>24.68376457245637</v>
       </c>
       <c r="D42">
-        <v>33.57935494428349</v>
+        <v>33.63608457245638</v>
       </c>
       <c r="E42">
-        <v>14.7088</v>
+        <v>15.09032</v>
       </c>
       <c r="F42">
-        <v>15.2608</v>
+        <v>15.64232</v>
       </c>
       <c r="G42">
         <v>6.69</v>
@@ -4859,28 +4859,28 @@
         <v>4.98</v>
       </c>
       <c r="M42">
-        <v>0.8439222400000002</v>
+        <v>0.8650202960000001</v>
       </c>
       <c r="N42">
-        <v>4.13607776</v>
+        <v>4.114979704</v>
       </c>
       <c r="O42">
-        <v>0.9099371072</v>
+        <v>0.9052955348800001</v>
       </c>
       <c r="P42">
-        <v>3.2261406528</v>
+        <v>3.20968416912</v>
       </c>
       <c r="Q42">
-        <v>3.626140652799999</v>
+        <v>3.60968416912</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1504052871693351</v>
+        <v>0.1519216439191136</v>
       </c>
       <c r="T42">
-        <v>1.363357560273546</v>
+        <v>1.383120772008109</v>
       </c>
       <c r="U42">
         <v>0.0553</v>
@@ -4897,7 +4897,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>5.901017610342866</v>
+        <v>5.757090351554018</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4905,22 +4905,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.107318709912277</v>
+        <v>0.107140647522953</v>
       </c>
       <c r="C43">
-        <v>24.68376457245637</v>
+        <v>24.35916620532354</v>
       </c>
       <c r="D43">
-        <v>33.63608457245638</v>
+        <v>33.69300620532355</v>
       </c>
       <c r="E43">
-        <v>15.09032</v>
+        <v>15.47184</v>
       </c>
       <c r="F43">
-        <v>15.64232</v>
+        <v>16.02384</v>
       </c>
       <c r="G43">
         <v>6.69</v>
@@ -4941,28 +4941,28 @@
         <v>4.98</v>
       </c>
       <c r="M43">
-        <v>0.8650202960000001</v>
+        <v>0.8861183520000002</v>
       </c>
       <c r="N43">
-        <v>4.114979704</v>
+        <v>4.093881648</v>
       </c>
       <c r="O43">
-        <v>0.9052955348800001</v>
+        <v>0.90065396256</v>
       </c>
       <c r="P43">
-        <v>3.20968416912</v>
+        <v>3.19322768544</v>
       </c>
       <c r="Q43">
-        <v>3.60968416912</v>
+        <v>3.59322768544</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1519216439191136</v>
+        <v>0.1534902888326776</v>
       </c>
       <c r="T43">
-        <v>1.383120772008109</v>
+        <v>1.403565473802485</v>
       </c>
       <c r="U43">
         <v>0.0553</v>
@@ -4979,7 +4979,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>5.757090351554018</v>
+        <v>5.620016771755111</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4987,22 +4987,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.107140647522953</v>
+        <v>0.106962585133629</v>
       </c>
       <c r="C44">
-        <v>24.35916620532354</v>
+        <v>24.0347608193138</v>
       </c>
       <c r="D44">
-        <v>33.69300620532354</v>
+        <v>33.7501208193138</v>
       </c>
       <c r="E44">
-        <v>15.47184</v>
+        <v>15.85336</v>
       </c>
       <c r="F44">
-        <v>16.02384</v>
+        <v>16.40536</v>
       </c>
       <c r="G44">
         <v>6.69</v>
@@ -5023,28 +5023,28 @@
         <v>4.98</v>
       </c>
       <c r="M44">
-        <v>0.886118352</v>
+        <v>0.9072164080000001</v>
       </c>
       <c r="N44">
-        <v>4.093881648</v>
+        <v>4.072783592</v>
       </c>
       <c r="O44">
-        <v>0.90065396256</v>
+        <v>0.8960123902400001</v>
       </c>
       <c r="P44">
-        <v>3.19322768544</v>
+        <v>3.17677120176</v>
       </c>
       <c r="Q44">
-        <v>3.59322768544</v>
+        <v>3.57677120176</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1534902888326776</v>
+        <v>0.1551139739186473</v>
       </c>
       <c r="T44">
-        <v>1.403565473802485</v>
+        <v>1.424727533554558</v>
       </c>
       <c r="U44">
         <v>0.0553</v>
@@ -5061,7 +5061,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>5.620016771755112</v>
+        <v>5.48931870729569</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5069,22 +5069,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.106962585133629</v>
+        <v>0.1067845227443049</v>
       </c>
       <c r="C45">
-        <v>24.0347608193138</v>
+        <v>23.71054939748796</v>
       </c>
       <c r="D45">
-        <v>33.7501208193138</v>
+        <v>33.80742939748796</v>
       </c>
       <c r="E45">
-        <v>15.85336</v>
+        <v>16.23488</v>
       </c>
       <c r="F45">
-        <v>16.40536</v>
+        <v>16.78688</v>
       </c>
       <c r="G45">
         <v>6.69</v>
@@ -5105,28 +5105,28 @@
         <v>4.98</v>
       </c>
       <c r="M45">
-        <v>0.9072164080000001</v>
+        <v>0.9283144640000001</v>
       </c>
       <c r="N45">
-        <v>4.072783592</v>
+        <v>4.051685536000001</v>
       </c>
       <c r="O45">
-        <v>0.8960123902400001</v>
+        <v>0.8913708179200002</v>
       </c>
       <c r="P45">
-        <v>3.17677120176</v>
+        <v>3.16031471808</v>
       </c>
       <c r="Q45">
-        <v>3.57677120176</v>
+        <v>3.56031471808</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1551139739186473</v>
+        <v>0.1567956477576874</v>
       </c>
       <c r="T45">
-        <v>1.424727533554558</v>
+        <v>1.446645381154919</v>
       </c>
       <c r="U45">
         <v>0.0553</v>
@@ -5143,7 +5143,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>5.48931870729569</v>
+        <v>5.364561463948062</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5151,22 +5151,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1067845227443049</v>
+        <v>0.1066064603549809</v>
       </c>
       <c r="C46">
-        <v>23.71054939748796</v>
+        <v>23.38653292959526</v>
       </c>
       <c r="D46">
-        <v>33.80742939748796</v>
+        <v>33.86493292959526</v>
       </c>
       <c r="E46">
-        <v>16.23488</v>
+        <v>16.6164</v>
       </c>
       <c r="F46">
-        <v>16.78688</v>
+        <v>17.1684</v>
       </c>
       <c r="G46">
         <v>6.69</v>
@@ -5187,28 +5187,28 @@
         <v>4.98</v>
       </c>
       <c r="M46">
-        <v>0.9283144640000001</v>
+        <v>0.9494125200000001</v>
       </c>
       <c r="N46">
-        <v>4.051685536000001</v>
+        <v>4.03058748</v>
       </c>
       <c r="O46">
-        <v>0.8913708179200002</v>
+        <v>0.8867292456000001</v>
       </c>
       <c r="P46">
-        <v>3.16031471808</v>
+        <v>3.1438582344</v>
       </c>
       <c r="Q46">
-        <v>3.56031471808</v>
+        <v>3.5438582344</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1567956477576874</v>
+        <v>0.1585384733726925</v>
       </c>
       <c r="T46">
-        <v>1.446645381154919</v>
+        <v>1.469360241395293</v>
       </c>
       <c r="U46">
         <v>0.0553</v>
@@ -5225,7 +5225,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>5.364561463948062</v>
+        <v>5.245348986971438</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5233,22 +5233,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1066064603549809</v>
+        <v>0.1064283979656569</v>
       </c>
       <c r="C47">
-        <v>23.38653292959526</v>
+        <v>23.0627124121303</v>
       </c>
       <c r="D47">
-        <v>33.86493292959526</v>
+        <v>33.92263241213031</v>
       </c>
       <c r="E47">
-        <v>16.6164</v>
+        <v>16.99792</v>
       </c>
       <c r="F47">
-        <v>17.1684</v>
+        <v>17.54992</v>
       </c>
       <c r="G47">
         <v>6.69</v>
@@ -5269,28 +5269,28 @@
         <v>4.98</v>
       </c>
       <c r="M47">
-        <v>0.9494125200000001</v>
+        <v>0.970510576</v>
       </c>
       <c r="N47">
-        <v>4.03058748</v>
+        <v>4.009489424000001</v>
       </c>
       <c r="O47">
-        <v>0.8867292456000001</v>
+        <v>0.8820876732800002</v>
       </c>
       <c r="P47">
-        <v>3.1438582344</v>
+        <v>3.127401750720001</v>
       </c>
       <c r="Q47">
-        <v>3.5438582344</v>
+        <v>3.52740175072</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1585384733726925</v>
+        <v>0.1603458480845497</v>
       </c>
       <c r="T47">
-        <v>1.469360241395293</v>
+        <v>1.492916392755681</v>
       </c>
       <c r="U47">
         <v>0.0553</v>
@@ -5307,7 +5307,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>5.245348986971438</v>
+        <v>5.131319661167712</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5315,22 +5315,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1064283979656569</v>
+        <v>0.1062503355763328</v>
       </c>
       <c r="C48">
-        <v>23.0627124121303</v>
+        <v>22.73908884839064</v>
       </c>
       <c r="D48">
-        <v>33.92263241213031</v>
+        <v>33.98052884839065</v>
       </c>
       <c r="E48">
-        <v>16.99792</v>
+        <v>17.37944</v>
       </c>
       <c r="F48">
-        <v>17.54992</v>
+        <v>17.93144</v>
       </c>
       <c r="G48">
         <v>6.69</v>
@@ -5351,28 +5351,28 @@
         <v>4.98</v>
       </c>
       <c r="M48">
-        <v>0.970510576</v>
+        <v>0.9916086320000002</v>
       </c>
       <c r="N48">
-        <v>4.009489424000001</v>
+        <v>3.988391368</v>
       </c>
       <c r="O48">
-        <v>0.8820876732800002</v>
+        <v>0.8774461009600001</v>
       </c>
       <c r="P48">
-        <v>3.127401750720001</v>
+        <v>3.11094526704</v>
       </c>
       <c r="Q48">
-        <v>3.52740175072</v>
+        <v>3.510945267039999</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1603458480845497</v>
+        <v>0.1622214256157223</v>
       </c>
       <c r="T48">
-        <v>1.492916392755681</v>
+        <v>1.51736145548816</v>
       </c>
       <c r="U48">
         <v>0.0553</v>
@@ -5389,7 +5389,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>5.131319661167712</v>
+        <v>5.022142647100313</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5397,22 +5397,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1062503355763328</v>
+        <v>0.1060722731870088</v>
       </c>
       <c r="C49">
-        <v>22.73908884839064</v>
+        <v>22.41566324853496</v>
       </c>
       <c r="D49">
-        <v>33.98052884839065</v>
+        <v>34.03862324853496</v>
       </c>
       <c r="E49">
-        <v>17.37944</v>
+        <v>17.76096</v>
       </c>
       <c r="F49">
-        <v>17.93144</v>
+        <v>18.31296</v>
       </c>
       <c r="G49">
         <v>6.69</v>
@@ -5433,28 +5433,28 @@
         <v>4.98</v>
       </c>
       <c r="M49">
-        <v>0.9916086320000002</v>
+        <v>1.012706688</v>
       </c>
       <c r="N49">
-        <v>3.988391368</v>
+        <v>3.967293312000001</v>
       </c>
       <c r="O49">
-        <v>0.8774461009600001</v>
+        <v>0.8728045286400001</v>
       </c>
       <c r="P49">
-        <v>3.11094526704</v>
+        <v>3.094488783360001</v>
       </c>
       <c r="Q49">
-        <v>3.510945267039999</v>
+        <v>3.49448878336</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1622214256157223</v>
+        <v>0.1641691407442477</v>
       </c>
       <c r="T49">
-        <v>1.51736145548816</v>
+        <v>1.542746712941118</v>
       </c>
       <c r="U49">
         <v>0.0553</v>
@@ -5471,7 +5471,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>5.022142647100313</v>
+        <v>4.917514675285724</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5479,22 +5479,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1060722731870088</v>
+        <v>0.1058942107976847</v>
       </c>
       <c r="C50">
-        <v>22.41566324853497</v>
+        <v>22.09243662964175</v>
       </c>
       <c r="D50">
-        <v>34.03862324853497</v>
+        <v>34.09691662964175</v>
       </c>
       <c r="E50">
-        <v>17.76096</v>
+        <v>18.14248</v>
       </c>
       <c r="F50">
-        <v>18.31296</v>
+        <v>18.69448</v>
       </c>
       <c r="G50">
         <v>6.69</v>
@@ -5515,28 +5515,28 @@
         <v>4.98</v>
       </c>
       <c r="M50">
-        <v>1.012706688</v>
+        <v>1.033804744</v>
       </c>
       <c r="N50">
-        <v>3.967293312000001</v>
+        <v>3.946195256</v>
       </c>
       <c r="O50">
-        <v>0.8728045286400001</v>
+        <v>0.8681629563200001</v>
       </c>
       <c r="P50">
-        <v>3.094488783360001</v>
+        <v>3.07803229968</v>
       </c>
       <c r="Q50">
-        <v>3.49448878336</v>
+        <v>3.47803229968</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1641691407442476</v>
+        <v>0.1661932368582054</v>
       </c>
       <c r="T50">
-        <v>1.542746712941118</v>
+        <v>1.569127470686349</v>
       </c>
       <c r="U50">
         <v>0.0553</v>
@@ -5553,7 +5553,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>4.917514675285724</v>
+        <v>4.817157232932953</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5561,22 +5561,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1058942107976847</v>
+        <v>0.1057161484083607</v>
       </c>
       <c r="C51">
-        <v>22.09243662964175</v>
+        <v>21.76941001576875</v>
       </c>
       <c r="D51">
-        <v>34.09691662964175</v>
+        <v>34.15541001576875</v>
       </c>
       <c r="E51">
-        <v>18.14248</v>
+        <v>18.524</v>
       </c>
       <c r="F51">
-        <v>18.69448</v>
+        <v>19.076</v>
       </c>
       <c r="G51">
         <v>6.69</v>
@@ -5597,28 +5597,28 @@
         <v>4.98</v>
       </c>
       <c r="M51">
-        <v>1.033804744</v>
+        <v>1.0549028</v>
       </c>
       <c r="N51">
-        <v>3.946195256</v>
+        <v>3.925097200000001</v>
       </c>
       <c r="O51">
-        <v>0.8681629563200001</v>
+        <v>0.8635213840000001</v>
       </c>
       <c r="P51">
-        <v>3.07803229968</v>
+        <v>3.061575816</v>
       </c>
       <c r="Q51">
-        <v>3.47803229968</v>
+        <v>3.461575816</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1661932368582054</v>
+        <v>0.1682982968167214</v>
       </c>
       <c r="T51">
-        <v>1.569127470686349</v>
+        <v>1.596563458741389</v>
       </c>
       <c r="U51">
         <v>0.0553</v>
@@ -5635,7 +5635,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>4.817157232932953</v>
+        <v>4.720814088274294</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1057161484083607</v>
+        <v>0.1055380860190367</v>
       </c>
       <c r="C52">
-        <v>21.76941001576875</v>
+        <v>21.44658443801286</v>
       </c>
       <c r="D52">
-        <v>34.15541001576875</v>
+        <v>34.21410443801286</v>
       </c>
       <c r="E52">
-        <v>18.524</v>
+        <v>18.90552</v>
       </c>
       <c r="F52">
-        <v>19.076</v>
+        <v>19.45752</v>
       </c>
       <c r="G52">
         <v>6.69</v>
@@ -5679,28 +5679,28 @@
         <v>4.98</v>
       </c>
       <c r="M52">
-        <v>1.0549028</v>
+        <v>1.076000856</v>
       </c>
       <c r="N52">
-        <v>3.925097200000001</v>
+        <v>3.903999144</v>
       </c>
       <c r="O52">
-        <v>0.8635213840000001</v>
+        <v>0.85887981168</v>
       </c>
       <c r="P52">
-        <v>3.061575816</v>
+        <v>3.04511933232</v>
       </c>
       <c r="Q52">
-        <v>3.461575816</v>
+        <v>3.44511933232</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1682982968167214</v>
+        <v>0.1704892775898707</v>
       </c>
       <c r="T52">
-        <v>1.596563458741389</v>
+        <v>1.625119283043575</v>
       </c>
       <c r="U52">
         <v>0.0553</v>
@@ -5717,7 +5717,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>4.720814088274294</v>
+        <v>4.628249106151268</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5725,22 +5725,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1055380860190367</v>
+        <v>0.1053600236297126</v>
       </c>
       <c r="C53">
-        <v>21.44658443801286</v>
+        <v>21.12396093457071</v>
       </c>
       <c r="D53">
-        <v>34.21410443801286</v>
+        <v>34.27300093457072</v>
       </c>
       <c r="E53">
-        <v>18.90552</v>
+        <v>19.28704</v>
       </c>
       <c r="F53">
-        <v>19.45752</v>
+        <v>19.83904</v>
       </c>
       <c r="G53">
         <v>6.69</v>
@@ -5761,28 +5761,28 @@
         <v>4.98</v>
       </c>
       <c r="M53">
-        <v>1.076000856</v>
+        <v>1.097098912</v>
       </c>
       <c r="N53">
-        <v>3.903999144</v>
+        <v>3.882901088000001</v>
       </c>
       <c r="O53">
-        <v>0.85887981168</v>
+        <v>0.8542382393600001</v>
       </c>
       <c r="P53">
-        <v>3.04511933232</v>
+        <v>3.028662848640001</v>
       </c>
       <c r="Q53">
-        <v>3.44511933232</v>
+        <v>3.42866284864</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1704892775898707</v>
+        <v>0.172771549228568</v>
       </c>
       <c r="T53">
-        <v>1.625119283043575</v>
+        <v>1.65486493335835</v>
       </c>
       <c r="U53">
         <v>0.0553</v>
@@ -5799,7 +5799,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>4.628249106151268</v>
+        <v>4.53924431564836</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5807,22 +5807,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1053600236297126</v>
+        <v>0.1062154612403886</v>
       </c>
       <c r="C54">
-        <v>21.12396093457071</v>
+        <v>20.46133128216536</v>
       </c>
       <c r="D54">
-        <v>34.27300093457072</v>
+        <v>33.99189128216537</v>
       </c>
       <c r="E54">
-        <v>19.28704</v>
+        <v>19.66856</v>
       </c>
       <c r="F54">
-        <v>19.83904</v>
+        <v>20.22056</v>
       </c>
       <c r="G54">
         <v>6.69</v>
@@ -5843,45 +5843,45 @@
         <v>4.98</v>
       </c>
       <c r="M54">
-        <v>1.097098912</v>
+        <v>1.168748368</v>
       </c>
       <c r="N54">
-        <v>3.882901088000001</v>
+        <v>3.811251632</v>
       </c>
       <c r="O54">
-        <v>0.8542382393600001</v>
+        <v>0.83847535904</v>
       </c>
       <c r="P54">
-        <v>3.028662848640001</v>
+        <v>2.97277627296</v>
       </c>
       <c r="Q54">
-        <v>3.42866284864</v>
+        <v>3.372776272959999</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.172771549228568</v>
+        <v>0.1751509388093374</v>
       </c>
       <c r="T54">
-        <v>1.65486493335835</v>
+        <v>1.685876356026947</v>
       </c>
       <c r="U54">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V54">
         <v>0.22</v>
       </c>
       <c r="W54">
-        <v>0.04313400000000001</v>
+        <v>0.04508400000000001</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y54">
-        <v>4.53924431564836</v>
+        <v>4.260968516706412</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5889,22 +5889,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1062154612403886</v>
+        <v>0.1060568988510645</v>
       </c>
       <c r="C55">
-        <v>20.46133128216536</v>
+        <v>20.13156857646178</v>
       </c>
       <c r="D55">
-        <v>33.99189128216537</v>
+        <v>34.04364857646178</v>
       </c>
       <c r="E55">
-        <v>19.66856</v>
+        <v>20.05008</v>
       </c>
       <c r="F55">
-        <v>20.22056</v>
+        <v>20.60208</v>
       </c>
       <c r="G55">
         <v>6.69</v>
@@ -5925,28 +5925,28 @@
         <v>4.98</v>
       </c>
       <c r="M55">
-        <v>1.168748368</v>
+        <v>1.190800224</v>
       </c>
       <c r="N55">
-        <v>3.811251632</v>
+        <v>3.789199776</v>
       </c>
       <c r="O55">
-        <v>0.83847535904</v>
+        <v>0.8336239507200001</v>
       </c>
       <c r="P55">
-        <v>2.97277627296</v>
+        <v>2.95557582528</v>
       </c>
       <c r="Q55">
-        <v>3.372776272959999</v>
+        <v>3.35557582528</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1751509388093374</v>
+        <v>0.1776337801110099</v>
       </c>
       <c r="T55">
-        <v>1.685876356026947</v>
+        <v>1.718236101420265</v>
       </c>
       <c r="U55">
         <v>0.0578</v>
@@ -5963,7 +5963,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>4.260968516706412</v>
+        <v>4.18206169232296</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5971,22 +5971,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1060568988510645</v>
+        <v>0.1058983364617405</v>
       </c>
       <c r="C56">
-        <v>20.13156857646178</v>
+        <v>19.8019637262053</v>
       </c>
       <c r="D56">
-        <v>34.04364857646178</v>
+        <v>34.09556372620531</v>
       </c>
       <c r="E56">
-        <v>20.05008</v>
+        <v>20.4316</v>
       </c>
       <c r="F56">
-        <v>20.60208</v>
+        <v>20.9836</v>
       </c>
       <c r="G56">
         <v>6.69</v>
@@ -6007,28 +6007,28 @@
         <v>4.98</v>
       </c>
       <c r="M56">
-        <v>1.190800224</v>
+        <v>1.21285208</v>
       </c>
       <c r="N56">
-        <v>3.789199776</v>
+        <v>3.76714792</v>
       </c>
       <c r="O56">
-        <v>0.8336239507200001</v>
+        <v>0.8287725424000001</v>
       </c>
       <c r="P56">
-        <v>2.95557582528</v>
+        <v>2.9383753776</v>
       </c>
       <c r="Q56">
-        <v>3.35557582528</v>
+        <v>3.338375377599999</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1776337801110099</v>
+        <v>0.1802269699149789</v>
       </c>
       <c r="T56">
-        <v>1.718236101420265</v>
+        <v>1.752034057719952</v>
       </c>
       <c r="U56">
         <v>0.0578</v>
@@ -6045,7 +6045,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>4.18206169232296</v>
+        <v>4.106024207007996</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6053,22 +6053,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1058983364617405</v>
+        <v>0.1057397740724165</v>
       </c>
       <c r="C57">
-        <v>19.8019637262053</v>
+        <v>19.4725174546679</v>
       </c>
       <c r="D57">
-        <v>34.09556372620531</v>
+        <v>34.1476374546679</v>
       </c>
       <c r="E57">
-        <v>20.4316</v>
+        <v>20.81312</v>
       </c>
       <c r="F57">
-        <v>20.9836</v>
+        <v>21.36512</v>
       </c>
       <c r="G57">
         <v>6.69</v>
@@ -6089,28 +6089,28 @@
         <v>4.98</v>
       </c>
       <c r="M57">
-        <v>1.21285208</v>
+        <v>1.234903936</v>
       </c>
       <c r="N57">
-        <v>3.76714792</v>
+        <v>3.745096064</v>
       </c>
       <c r="O57">
-        <v>0.8287725424000001</v>
+        <v>0.82392113408</v>
       </c>
       <c r="P57">
-        <v>2.9383753776</v>
+        <v>2.92117492992</v>
       </c>
       <c r="Q57">
-        <v>3.338375377599999</v>
+        <v>3.32117492992</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1802269699149789</v>
+        <v>0.1829380319827647</v>
       </c>
       <c r="T57">
-        <v>1.752034057719952</v>
+        <v>1.787368284760534</v>
       </c>
       <c r="U57">
         <v>0.0578</v>
@@ -6127,7 +6127,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>4.106024207007996</v>
+        <v>4.032702346168568</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6135,22 +6135,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1057397740724165</v>
+        <v>0.1071373116830924</v>
       </c>
       <c r="C58">
-        <v>19.4725174546679</v>
+        <v>18.63743441975769</v>
       </c>
       <c r="D58">
-        <v>34.1476374546679</v>
+        <v>33.6940744197577</v>
       </c>
       <c r="E58">
-        <v>20.81312</v>
+        <v>21.19464</v>
       </c>
       <c r="F58">
-        <v>21.36512</v>
+        <v>21.74664</v>
       </c>
       <c r="G58">
         <v>6.69</v>
@@ -6171,45 +6171,45 @@
         <v>4.98</v>
       </c>
       <c r="M58">
-        <v>1.234903936</v>
+        <v>1.333069032</v>
       </c>
       <c r="N58">
-        <v>3.745096064</v>
+        <v>3.646930968</v>
       </c>
       <c r="O58">
-        <v>0.82392113408</v>
+        <v>0.8023248129600001</v>
       </c>
       <c r="P58">
-        <v>2.92117492992</v>
+        <v>2.84460615504</v>
       </c>
       <c r="Q58">
-        <v>3.32117492992</v>
+        <v>3.24460615504</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1829380319827647</v>
+        <v>0.1857751899606801</v>
       </c>
       <c r="T58">
-        <v>1.787368284760534</v>
+        <v>1.824345964221609</v>
       </c>
       <c r="U58">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V58">
         <v>0.22</v>
       </c>
       <c r="W58">
-        <v>0.04508400000000001</v>
+        <v>0.047814</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y58">
-        <v>4.032702346168568</v>
+        <v>3.735740520900496</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6217,22 +6217,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1071373116830924</v>
+        <v>0.1070060492937684</v>
       </c>
       <c r="C59">
-        <v>18.63743441975769</v>
+        <v>18.29800156410177</v>
       </c>
       <c r="D59">
-        <v>33.6940744197577</v>
+        <v>33.73616156410178</v>
       </c>
       <c r="E59">
-        <v>21.19464</v>
+        <v>21.57616000000001</v>
       </c>
       <c r="F59">
-        <v>21.74664</v>
+        <v>22.12816</v>
       </c>
       <c r="G59">
         <v>6.69</v>
@@ -6253,28 +6253,28 @@
         <v>4.98</v>
       </c>
       <c r="M59">
-        <v>1.333069032</v>
+        <v>1.356456208</v>
       </c>
       <c r="N59">
-        <v>3.646930968</v>
+        <v>3.623543792</v>
       </c>
       <c r="O59">
-        <v>0.8023248129600001</v>
+        <v>0.79717963424</v>
       </c>
       <c r="P59">
-        <v>2.84460615504</v>
+        <v>2.82636415776</v>
       </c>
       <c r="Q59">
-        <v>3.24460615504</v>
+        <v>3.22636415776</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1857751899606801</v>
+        <v>0.1887474506994486</v>
       </c>
       <c r="T59">
-        <v>1.824345964221609</v>
+        <v>1.863084485561782</v>
       </c>
       <c r="U59">
         <v>0.0613</v>
@@ -6291,7 +6291,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>3.735740520900496</v>
+        <v>3.671331201574625</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6299,22 +6299,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1070060492937684</v>
+        <v>0.1068747869044444</v>
       </c>
       <c r="C60">
-        <v>18.29800156410178</v>
+        <v>17.95867398173652</v>
       </c>
       <c r="D60">
-        <v>33.73616156410178</v>
+        <v>33.77835398173652</v>
       </c>
       <c r="E60">
-        <v>21.57616</v>
+        <v>21.95768</v>
       </c>
       <c r="F60">
-        <v>22.12816</v>
+        <v>22.50968</v>
       </c>
       <c r="G60">
         <v>6.69</v>
@@ -6335,28 +6335,28 @@
         <v>4.98</v>
       </c>
       <c r="M60">
-        <v>1.356456208</v>
+        <v>1.379843384</v>
       </c>
       <c r="N60">
-        <v>3.623543792</v>
+        <v>3.600156616</v>
       </c>
       <c r="O60">
-        <v>0.79717963424</v>
+        <v>0.7920344555200001</v>
       </c>
       <c r="P60">
-        <v>2.82636415776</v>
+        <v>2.80812216048</v>
       </c>
       <c r="Q60">
-        <v>3.22636415776</v>
+        <v>3.20812216048</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1887474506994486</v>
+        <v>0.1918646997669374</v>
       </c>
       <c r="T60">
-        <v>1.863084485561782</v>
+        <v>1.903712690869768</v>
       </c>
       <c r="U60">
         <v>0.0613</v>
@@ -6373,7 +6373,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>3.671331201574626</v>
+        <v>3.609105249005564</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6381,22 +6381,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1068747869044444</v>
+        <v>0.1067435245151203</v>
       </c>
       <c r="C61">
-        <v>17.95867398173652</v>
+        <v>17.61945206813936</v>
       </c>
       <c r="D61">
-        <v>33.77835398173652</v>
+        <v>33.82065206813936</v>
       </c>
       <c r="E61">
-        <v>21.95768</v>
+        <v>22.3392</v>
       </c>
       <c r="F61">
-        <v>22.50968</v>
+        <v>22.8912</v>
       </c>
       <c r="G61">
         <v>6.69</v>
@@ -6417,28 +6417,28 @@
         <v>4.98</v>
       </c>
       <c r="M61">
-        <v>1.379843384</v>
+        <v>1.40323056</v>
       </c>
       <c r="N61">
-        <v>3.600156616</v>
+        <v>3.576769440000001</v>
       </c>
       <c r="O61">
-        <v>0.7920344555200001</v>
+        <v>0.7868892768000001</v>
       </c>
       <c r="P61">
-        <v>2.80812216048</v>
+        <v>2.7898801632</v>
       </c>
       <c r="Q61">
-        <v>3.20812216048</v>
+        <v>3.1898801632</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1918646997669374</v>
+        <v>0.1951378112878008</v>
       </c>
       <c r="T61">
-        <v>1.903712690869768</v>
+        <v>1.946372306443154</v>
       </c>
       <c r="U61">
         <v>0.0613</v>
@@ -6455,7 +6455,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>3.609105249005564</v>
+        <v>3.548953494855471</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6463,22 +6463,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1067435245151203</v>
+        <v>0.1079445021257963</v>
       </c>
       <c r="C62">
-        <v>17.61945206813936</v>
+        <v>16.85483279472924</v>
       </c>
       <c r="D62">
-        <v>33.82065206813936</v>
+        <v>33.43755279472924</v>
       </c>
       <c r="E62">
-        <v>22.3392</v>
+        <v>22.72072</v>
       </c>
       <c r="F62">
-        <v>22.8912</v>
+        <v>23.27272</v>
       </c>
       <c r="G62">
         <v>6.69</v>
@@ -6499,45 +6499,45 @@
         <v>4.98</v>
       </c>
       <c r="M62">
-        <v>1.40323056</v>
+        <v>1.491781352</v>
       </c>
       <c r="N62">
-        <v>3.576769440000001</v>
+        <v>3.488218648</v>
       </c>
       <c r="O62">
-        <v>0.7868892768000001</v>
+        <v>0.76740810256</v>
       </c>
       <c r="P62">
-        <v>2.7898801632</v>
+        <v>2.72081054544</v>
       </c>
       <c r="Q62">
-        <v>3.1898801632</v>
+        <v>3.120810545439999</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1951378112878008</v>
+        <v>0.1985787746815289</v>
       </c>
       <c r="T62">
-        <v>1.946372306443154</v>
+        <v>1.991219594610047</v>
       </c>
       <c r="U62">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V62">
         <v>0.22</v>
       </c>
       <c r="W62">
-        <v>0.047814</v>
+        <v>0.04999800000000001</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y62">
-        <v>3.548953494855471</v>
+        <v>3.338290824807146</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6545,22 +6545,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1079445021257963</v>
+        <v>0.1078350797364722</v>
       </c>
       <c r="C63">
-        <v>16.85483279472924</v>
+        <v>16.50785766485966</v>
       </c>
       <c r="D63">
-        <v>33.43755279472924</v>
+        <v>33.47209766485967</v>
       </c>
       <c r="E63">
-        <v>22.72072</v>
+        <v>23.10224</v>
       </c>
       <c r="F63">
-        <v>23.27272</v>
+        <v>23.65424</v>
       </c>
       <c r="G63">
         <v>6.69</v>
@@ -6581,28 +6581,28 @@
         <v>4.98</v>
       </c>
       <c r="M63">
-        <v>1.491781352</v>
+        <v>1.516236784</v>
       </c>
       <c r="N63">
-        <v>3.488218648</v>
+        <v>3.463763216</v>
       </c>
       <c r="O63">
-        <v>0.76740810256</v>
+        <v>0.76202790752</v>
       </c>
       <c r="P63">
-        <v>2.72081054544</v>
+        <v>2.70173530848</v>
       </c>
       <c r="Q63">
-        <v>3.120810545439999</v>
+        <v>3.101735308479999</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1985787746815289</v>
+        <v>0.2022008414117691</v>
       </c>
       <c r="T63">
-        <v>1.991219594610047</v>
+        <v>2.038427266364672</v>
       </c>
       <c r="U63">
         <v>0.0641</v>
@@ -6619,7 +6619,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>3.338290824807146</v>
+        <v>3.284447424407031</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6627,22 +6627,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1078350797364722</v>
+        <v>0.1077256573471482</v>
       </c>
       <c r="C64">
-        <v>16.50785766485966</v>
+        <v>16.16095398652255</v>
       </c>
       <c r="D64">
-        <v>33.47209766485967</v>
+        <v>33.50671398652255</v>
       </c>
       <c r="E64">
-        <v>23.10224</v>
+        <v>23.48376</v>
       </c>
       <c r="F64">
-        <v>23.65424</v>
+        <v>24.03576</v>
       </c>
       <c r="G64">
         <v>6.69</v>
@@ -6663,28 +6663,28 @@
         <v>4.98</v>
       </c>
       <c r="M64">
-        <v>1.516236784</v>
+        <v>1.540692216</v>
       </c>
       <c r="N64">
-        <v>3.463763216</v>
+        <v>3.439307784</v>
       </c>
       <c r="O64">
-        <v>0.76202790752</v>
+        <v>0.7566477124800001</v>
       </c>
       <c r="P64">
-        <v>2.70173530848</v>
+        <v>2.68266007152</v>
       </c>
       <c r="Q64">
-        <v>3.101735308479999</v>
+        <v>3.08266007152</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2022008414117691</v>
+        <v>0.206018695532833</v>
       </c>
       <c r="T64">
-        <v>2.038427266364672</v>
+        <v>2.088186704160087</v>
       </c>
       <c r="U64">
         <v>0.0641</v>
@@ -6701,7 +6701,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>3.284447424407031</v>
+        <v>3.232313338305332</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6709,22 +6709,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1077256573471482</v>
+        <v>0.1076162349578242</v>
       </c>
       <c r="C65">
-        <v>16.16095398652255</v>
+        <v>15.81412198162954</v>
       </c>
       <c r="D65">
-        <v>33.50671398652255</v>
+        <v>33.54140198162955</v>
       </c>
       <c r="E65">
-        <v>23.48376</v>
+        <v>23.86528</v>
       </c>
       <c r="F65">
-        <v>24.03576</v>
+        <v>24.41728</v>
       </c>
       <c r="G65">
         <v>6.69</v>
@@ -6745,28 +6745,28 @@
         <v>4.98</v>
       </c>
       <c r="M65">
-        <v>1.540692216</v>
+        <v>1.565147648</v>
       </c>
       <c r="N65">
-        <v>3.439307784</v>
+        <v>3.414852352</v>
       </c>
       <c r="O65">
-        <v>0.7566477124800001</v>
+        <v>0.7512675174400001</v>
       </c>
       <c r="P65">
-        <v>2.68266007152</v>
+        <v>2.66358483456</v>
       </c>
       <c r="Q65">
-        <v>3.08266007152</v>
+        <v>3.06358483456</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.206018695532833</v>
+        <v>0.2100486526606227</v>
       </c>
       <c r="T65">
-        <v>2.088186704160087</v>
+        <v>2.140710555166358</v>
       </c>
       <c r="U65">
         <v>0.0641</v>
@@ -6783,7 +6783,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>3.232313338305332</v>
+        <v>3.181808442394312</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6791,22 +6791,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1076162349578242</v>
+        <v>0.1075068125685001</v>
       </c>
       <c r="C66">
-        <v>15.81412198162954</v>
+        <v>15.46736187301226</v>
       </c>
       <c r="D66">
-        <v>33.54140198162955</v>
+        <v>33.57616187301226</v>
       </c>
       <c r="E66">
-        <v>23.86528</v>
+        <v>24.2468</v>
       </c>
       <c r="F66">
-        <v>24.41728</v>
+        <v>24.7988</v>
       </c>
       <c r="G66">
         <v>6.69</v>
@@ -6827,28 +6827,28 @@
         <v>4.98</v>
       </c>
       <c r="M66">
-        <v>1.565147648</v>
+        <v>1.58960308</v>
       </c>
       <c r="N66">
-        <v>3.414852352</v>
+        <v>3.390396920000001</v>
       </c>
       <c r="O66">
-        <v>0.7512675174400001</v>
+        <v>0.7458873224000001</v>
       </c>
       <c r="P66">
-        <v>2.66358483456</v>
+        <v>2.6445095976</v>
       </c>
       <c r="Q66">
-        <v>3.06358483456</v>
+        <v>3.0445095976</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2100486526606227</v>
+        <v>0.2143088930528575</v>
       </c>
       <c r="T66">
-        <v>2.140710555166358</v>
+        <v>2.196235769087273</v>
       </c>
       <c r="U66">
         <v>0.0641</v>
@@ -6865,7 +6865,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>3.181808442394312</v>
+        <v>3.132857543280553</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6873,22 +6873,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1075068125685001</v>
+        <v>0.1073973901791761</v>
       </c>
       <c r="C67">
-        <v>15.46736187301226</v>
+        <v>15.12067388442691</v>
       </c>
       <c r="D67">
-        <v>33.57616187301226</v>
+        <v>33.61099388442692</v>
       </c>
       <c r="E67">
-        <v>24.2468</v>
+        <v>24.62832</v>
       </c>
       <c r="F67">
-        <v>24.7988</v>
+        <v>25.18032</v>
       </c>
       <c r="G67">
         <v>6.69</v>
@@ -6909,28 +6909,28 @@
         <v>4.98</v>
       </c>
       <c r="M67">
-        <v>1.58960308</v>
+        <v>1.614058512</v>
       </c>
       <c r="N67">
-        <v>3.390396920000001</v>
+        <v>3.365941488</v>
       </c>
       <c r="O67">
-        <v>0.7458873224000001</v>
+        <v>0.74050712736</v>
       </c>
       <c r="P67">
-        <v>2.6445095976</v>
+        <v>2.62543436064</v>
       </c>
       <c r="Q67">
-        <v>3.0445095976</v>
+        <v>3.02543436064</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2143088930528575</v>
+        <v>0.2188197358211062</v>
       </c>
       <c r="T67">
-        <v>2.196235769087273</v>
+        <v>2.25502717206236</v>
       </c>
       <c r="U67">
         <v>0.0641</v>
@@ -6947,7 +6947,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>3.132857543280553</v>
+        <v>3.085390004745999</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6955,22 +6955,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1073973901791761</v>
+        <v>0.1072879677898521</v>
       </c>
       <c r="C68">
-        <v>15.12067388442691</v>
+        <v>14.77405824055922</v>
       </c>
       <c r="D68">
-        <v>33.61099388442692</v>
+        <v>33.64589824055923</v>
       </c>
       <c r="E68">
-        <v>24.62832</v>
+        <v>25.00984</v>
       </c>
       <c r="F68">
-        <v>25.18032</v>
+        <v>25.56184</v>
       </c>
       <c r="G68">
         <v>6.69</v>
@@ -6991,28 +6991,28 @@
         <v>4.98</v>
       </c>
       <c r="M68">
-        <v>1.614058512</v>
+        <v>1.638513944</v>
       </c>
       <c r="N68">
-        <v>3.365941488</v>
+        <v>3.341486056</v>
       </c>
       <c r="O68">
-        <v>0.74050712736</v>
+        <v>0.73512693232</v>
       </c>
       <c r="P68">
-        <v>2.62543436064</v>
+        <v>2.60635912368</v>
       </c>
       <c r="Q68">
-        <v>3.02543436064</v>
+        <v>3.006359123679999</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2188197358211062</v>
+        <v>0.2236039629995517</v>
       </c>
       <c r="T68">
-        <v>2.25502717206236</v>
+        <v>2.317381690369269</v>
       </c>
       <c r="U68">
         <v>0.0641</v>
@@ -7029,7 +7029,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>3.085390004745999</v>
+        <v>3.039339407660238</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7037,22 +7037,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1072879677898521</v>
+        <v>0.111315665400528</v>
       </c>
       <c r="C69">
-        <v>14.77405824055922</v>
+        <v>13.15377151422506</v>
       </c>
       <c r="D69">
-        <v>33.64589824055923</v>
+        <v>32.40713151422506</v>
       </c>
       <c r="E69">
-        <v>25.00984</v>
+        <v>25.39136</v>
       </c>
       <c r="F69">
-        <v>25.56184</v>
+        <v>25.94336</v>
       </c>
       <c r="G69">
         <v>6.69</v>
@@ -7073,45 +7073,45 @@
         <v>4.98</v>
       </c>
       <c r="M69">
-        <v>1.638513944</v>
+        <v>1.865327584</v>
       </c>
       <c r="N69">
-        <v>3.341486056</v>
+        <v>3.114672416</v>
       </c>
       <c r="O69">
-        <v>0.73512693232</v>
+        <v>0.6852279315200001</v>
       </c>
       <c r="P69">
-        <v>2.60635912368</v>
+        <v>2.42944448448</v>
       </c>
       <c r="Q69">
-        <v>3.006359123679999</v>
+        <v>2.82944448448</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2236039629995517</v>
+        <v>0.2286872043766501</v>
       </c>
       <c r="T69">
-        <v>2.317381690369269</v>
+        <v>2.383633366070362</v>
       </c>
       <c r="U69">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V69">
         <v>0.22</v>
       </c>
       <c r="W69">
-        <v>0.04999800000000001</v>
+        <v>0.05608200000000001</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y69">
-        <v>3.039339407660238</v>
+        <v>2.669772346003113</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7119,22 +7119,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.111315665400528</v>
+        <v>0.111267083011204</v>
       </c>
       <c r="C70">
-        <v>13.15377151422506</v>
+        <v>12.78664987068035</v>
       </c>
       <c r="D70">
-        <v>32.40713151422506</v>
+        <v>32.42152987068036</v>
       </c>
       <c r="E70">
-        <v>25.39136</v>
+        <v>25.77288</v>
       </c>
       <c r="F70">
-        <v>25.94336</v>
+        <v>26.32488</v>
       </c>
       <c r="G70">
         <v>6.69</v>
@@ -7155,28 +7155,28 @@
         <v>4.98</v>
       </c>
       <c r="M70">
-        <v>1.865327584</v>
+        <v>1.892758872</v>
       </c>
       <c r="N70">
-        <v>3.114672416</v>
+        <v>3.087241128</v>
       </c>
       <c r="O70">
-        <v>0.6852279315200001</v>
+        <v>0.67919304816</v>
       </c>
       <c r="P70">
-        <v>2.42944448448</v>
+        <v>2.40804807984</v>
       </c>
       <c r="Q70">
-        <v>2.82944448448</v>
+        <v>2.808048079839999</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2286872043766501</v>
+        <v>0.2340983968103355</v>
       </c>
       <c r="T70">
-        <v>2.383633366070362</v>
+        <v>2.454159343429589</v>
       </c>
       <c r="U70">
         <v>0.07190000000000001</v>
@@ -7193,7 +7193,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>2.669772346003113</v>
+        <v>2.631079993162488</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7201,22 +7201,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.111267083011204</v>
+        <v>0.1112185006218799</v>
       </c>
       <c r="C71">
-        <v>12.78664987068035</v>
+        <v>12.41954102708482</v>
       </c>
       <c r="D71">
-        <v>32.42152987068036</v>
+        <v>32.43594102708482</v>
       </c>
       <c r="E71">
-        <v>25.77288</v>
+        <v>26.1544</v>
       </c>
       <c r="F71">
-        <v>26.32488</v>
+        <v>26.7064</v>
       </c>
       <c r="G71">
         <v>6.69</v>
@@ -7237,28 +7237,28 @@
         <v>4.98</v>
       </c>
       <c r="M71">
-        <v>1.892758872</v>
+        <v>1.92019016</v>
       </c>
       <c r="N71">
-        <v>3.087241128</v>
+        <v>3.05980984</v>
       </c>
       <c r="O71">
-        <v>0.67919304816</v>
+        <v>0.6731581648</v>
       </c>
       <c r="P71">
-        <v>2.40804807984</v>
+        <v>2.3866516752</v>
       </c>
       <c r="Q71">
-        <v>2.808048079839999</v>
+        <v>2.7866516752</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2340983968103355</v>
+        <v>0.2398703354062665</v>
       </c>
       <c r="T71">
-        <v>2.454159343429589</v>
+        <v>2.529387052612763</v>
       </c>
       <c r="U71">
         <v>0.07190000000000001</v>
@@ -7275,7 +7275,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>2.631079993162488</v>
+        <v>2.59349313611731</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7283,22 +7283,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1112185006218799</v>
+        <v>0.1111699182325559</v>
       </c>
       <c r="C72">
-        <v>12.41954102708482</v>
+        <v>12.0524450005145</v>
       </c>
       <c r="D72">
-        <v>32.43594102708482</v>
+        <v>32.4503650005145</v>
       </c>
       <c r="E72">
-        <v>26.1544</v>
+        <v>26.53592</v>
       </c>
       <c r="F72">
-        <v>26.7064</v>
+        <v>27.08792</v>
       </c>
       <c r="G72">
         <v>6.69</v>
@@ -7319,28 +7319,28 @@
         <v>4.98</v>
       </c>
       <c r="M72">
-        <v>1.92019016</v>
+        <v>1.947621448</v>
       </c>
       <c r="N72">
-        <v>3.05980984</v>
+        <v>3.032378552</v>
       </c>
       <c r="O72">
-        <v>0.6731581648</v>
+        <v>0.66712328144</v>
       </c>
       <c r="P72">
-        <v>2.3866516752</v>
+        <v>2.36525527056</v>
       </c>
       <c r="Q72">
-        <v>2.7866516752</v>
+        <v>2.76525527056</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2398703354062665</v>
+        <v>0.2460403387329514</v>
       </c>
       <c r="T72">
-        <v>2.529387052612763</v>
+        <v>2.609802879670641</v>
       </c>
       <c r="U72">
         <v>0.07190000000000001</v>
@@ -7357,7 +7357,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>2.59349313611731</v>
+        <v>2.556965063777629</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7365,22 +7365,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1111699182325559</v>
+        <v>0.1111213358432319</v>
       </c>
       <c r="C73">
-        <v>12.05244500051449</v>
+        <v>11.68536180807585</v>
       </c>
       <c r="D73">
-        <v>32.45036500051449</v>
+        <v>32.46480180807585</v>
       </c>
       <c r="E73">
-        <v>26.53592</v>
+        <v>26.91744</v>
       </c>
       <c r="F73">
-        <v>27.08792</v>
+        <v>27.46944</v>
       </c>
       <c r="G73">
         <v>6.69</v>
@@ -7401,28 +7401,28 @@
         <v>4.98</v>
       </c>
       <c r="M73">
-        <v>1.947621448</v>
+        <v>1.975052736</v>
       </c>
       <c r="N73">
-        <v>3.032378552</v>
+        <v>3.004947264</v>
       </c>
       <c r="O73">
-        <v>0.66712328144</v>
+        <v>0.6610883980800001</v>
       </c>
       <c r="P73">
-        <v>2.36525527056</v>
+        <v>2.34385886592</v>
       </c>
       <c r="Q73">
-        <v>2.76525527056</v>
+        <v>2.74385886592</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2460403387329514</v>
+        <v>0.2526510565829709</v>
       </c>
       <c r="T73">
-        <v>2.60980287967064</v>
+        <v>2.695962694375508</v>
       </c>
       <c r="U73">
         <v>0.07190000000000001</v>
@@ -7439,7 +7439,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>2.55696506377763</v>
+        <v>2.521451660114052</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7447,22 +7447,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1111213358432319</v>
+        <v>0.1132934134539078</v>
       </c>
       <c r="C74">
-        <v>11.68536180807585</v>
+        <v>10.67069092920561</v>
       </c>
       <c r="D74">
-        <v>32.46480180807585</v>
+        <v>31.83165092920561</v>
       </c>
       <c r="E74">
-        <v>26.91744</v>
+        <v>27.29896</v>
       </c>
       <c r="F74">
-        <v>27.46944</v>
+        <v>27.85096</v>
       </c>
       <c r="G74">
         <v>6.69</v>
@@ -7483,45 +7483,45 @@
         <v>4.98</v>
       </c>
       <c r="M74">
-        <v>1.975052736</v>
+        <v>2.111102768</v>
       </c>
       <c r="N74">
-        <v>3.004947264</v>
+        <v>2.868897232</v>
       </c>
       <c r="O74">
-        <v>0.6610883980800001</v>
+        <v>0.63115739104</v>
       </c>
       <c r="P74">
-        <v>2.34385886592</v>
+        <v>2.23773984096</v>
       </c>
       <c r="Q74">
-        <v>2.74385886592</v>
+        <v>2.63773984096</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2526510565829709</v>
+        <v>0.2597514572366956</v>
       </c>
       <c r="T74">
-        <v>2.695962694375508</v>
+        <v>2.788504717577033</v>
       </c>
       <c r="U74">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V74">
         <v>0.22</v>
       </c>
       <c r="W74">
-        <v>0.05608200000000001</v>
+        <v>0.05912400000000001</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y74">
-        <v>2.521451660114052</v>
+        <v>2.358956691017895</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7529,22 +7529,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1132934134539078</v>
+        <v>0.1132752510645838</v>
       </c>
       <c r="C75">
-        <v>10.67069092920561</v>
+        <v>10.29436277868125</v>
       </c>
       <c r="D75">
-        <v>31.83165092920561</v>
+        <v>31.83684277868125</v>
       </c>
       <c r="E75">
-        <v>27.29896</v>
+        <v>27.68048</v>
       </c>
       <c r="F75">
-        <v>27.85096</v>
+        <v>28.23248</v>
       </c>
       <c r="G75">
         <v>6.69</v>
@@ -7565,28 +7565,28 @@
         <v>4.98</v>
       </c>
       <c r="M75">
-        <v>2.111102768</v>
+        <v>2.140021984</v>
       </c>
       <c r="N75">
-        <v>2.868897232</v>
+        <v>2.839978016</v>
       </c>
       <c r="O75">
-        <v>0.63115739104</v>
+        <v>0.6247951635200001</v>
       </c>
       <c r="P75">
-        <v>2.23773984096</v>
+        <v>2.21518285248</v>
       </c>
       <c r="Q75">
-        <v>2.63773984096</v>
+        <v>2.61518285248</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2597514572366956</v>
+        <v>0.2673980425560915</v>
       </c>
       <c r="T75">
-        <v>2.788504717577033</v>
+        <v>2.888165357947907</v>
       </c>
       <c r="U75">
         <v>0.07580000000000001</v>
@@ -7603,7 +7603,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>2.358956691017895</v>
+        <v>2.327078897896032</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7611,22 +7611,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1132752510645838</v>
+        <v>0.1132570886752598</v>
       </c>
       <c r="C76">
-        <v>10.29436277868125</v>
+        <v>9.918036322049435</v>
       </c>
       <c r="D76">
-        <v>31.83684277868125</v>
+        <v>31.84203632204943</v>
       </c>
       <c r="E76">
-        <v>27.68048</v>
+        <v>28.062</v>
       </c>
       <c r="F76">
-        <v>28.23248</v>
+        <v>28.614</v>
       </c>
       <c r="G76">
         <v>6.69</v>
@@ -7647,28 +7647,28 @@
         <v>4.98</v>
       </c>
       <c r="M76">
-        <v>2.140021984</v>
+        <v>2.1689412</v>
       </c>
       <c r="N76">
-        <v>2.839978016</v>
+        <v>2.8110588</v>
       </c>
       <c r="O76">
-        <v>0.6247951635200001</v>
+        <v>0.618432936</v>
       </c>
       <c r="P76">
-        <v>2.21518285248</v>
+        <v>2.192625864</v>
       </c>
       <c r="Q76">
-        <v>2.61518285248</v>
+        <v>2.592625864</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2673980425560915</v>
+        <v>0.275656354701039</v>
       </c>
       <c r="T76">
-        <v>2.888165357947907</v>
+        <v>2.99579884954845</v>
       </c>
       <c r="U76">
         <v>0.07580000000000001</v>
@@ -7685,7 +7685,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>2.327078897896032</v>
+        <v>2.296051179257418</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7693,22 +7693,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1132570886752598</v>
+        <v>0.1132389262859357</v>
       </c>
       <c r="C77">
-        <v>9.918036322049435</v>
+        <v>9.54171156013928</v>
       </c>
       <c r="D77">
-        <v>31.84203632204943</v>
+        <v>31.84723156013928</v>
       </c>
       <c r="E77">
-        <v>28.062</v>
+        <v>28.44352</v>
       </c>
       <c r="F77">
-        <v>28.614</v>
+        <v>28.99552</v>
       </c>
       <c r="G77">
         <v>6.69</v>
@@ -7729,28 +7729,28 @@
         <v>4.98</v>
       </c>
       <c r="M77">
-        <v>2.1689412</v>
+        <v>2.197860416000001</v>
       </c>
       <c r="N77">
-        <v>2.8110588</v>
+        <v>2.782139584</v>
       </c>
       <c r="O77">
-        <v>0.618432936</v>
+        <v>0.61207070848</v>
       </c>
       <c r="P77">
-        <v>2.192625864</v>
+        <v>2.17006887552</v>
       </c>
       <c r="Q77">
-        <v>2.592625864</v>
+        <v>2.570068875519999</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.275656354701039</v>
+        <v>0.2846028595247321</v>
       </c>
       <c r="T77">
-        <v>2.99579884954845</v>
+        <v>3.112401798782372</v>
       </c>
       <c r="U77">
         <v>0.07580000000000001</v>
@@ -7767,7 +7767,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>2.296051179257418</v>
+        <v>2.265839979530346</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7775,22 +7775,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1132389262859357</v>
+        <v>0.1132207638966117</v>
       </c>
       <c r="C78">
-        <v>9.54171156013928</v>
+        <v>9.165388493780441</v>
       </c>
       <c r="D78">
-        <v>31.84723156013928</v>
+        <v>31.85242849378044</v>
       </c>
       <c r="E78">
-        <v>28.44352</v>
+        <v>28.82504</v>
       </c>
       <c r="F78">
-        <v>28.99552</v>
+        <v>29.37704</v>
       </c>
       <c r="G78">
         <v>6.69</v>
@@ -7811,28 +7811,28 @@
         <v>4.98</v>
       </c>
       <c r="M78">
-        <v>2.197860416000001</v>
+        <v>2.226779632</v>
       </c>
       <c r="N78">
-        <v>2.782139584</v>
+        <v>2.753220368</v>
       </c>
       <c r="O78">
-        <v>0.61207070848</v>
+        <v>0.60570848096</v>
       </c>
       <c r="P78">
-        <v>2.17006887552</v>
+        <v>2.14751188704</v>
       </c>
       <c r="Q78">
-        <v>2.570068875519999</v>
+        <v>2.54751188704</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2846028595247321</v>
+        <v>0.294327321289616</v>
       </c>
       <c r="T78">
-        <v>3.112401798782372</v>
+        <v>3.2391441349062</v>
       </c>
       <c r="U78">
         <v>0.07580000000000001</v>
@@ -7849,7 +7849,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>2.265839979530346</v>
+        <v>2.236413486289693</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7857,22 +7857,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1132207638966117</v>
+        <v>0.1132026015072876</v>
       </c>
       <c r="C79">
-        <v>9.165388493780441</v>
+        <v>8.7890671238031</v>
       </c>
       <c r="D79">
-        <v>31.85242849378044</v>
+        <v>31.8576271238031</v>
       </c>
       <c r="E79">
-        <v>28.82504</v>
+        <v>29.20656</v>
       </c>
       <c r="F79">
-        <v>29.37704</v>
+        <v>29.75856</v>
       </c>
       <c r="G79">
         <v>6.69</v>
@@ -7893,28 +7893,28 @@
         <v>4.98</v>
       </c>
       <c r="M79">
-        <v>2.226779632</v>
+        <v>2.255698848</v>
       </c>
       <c r="N79">
-        <v>2.753220368</v>
+        <v>2.724301152</v>
       </c>
       <c r="O79">
-        <v>0.60570848096</v>
+        <v>0.59934625344</v>
       </c>
       <c r="P79">
-        <v>2.14751188704</v>
+        <v>2.12495489856</v>
       </c>
       <c r="Q79">
-        <v>2.54751188704</v>
+        <v>2.52495489856</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.294327321289616</v>
+        <v>0.3049358250331257</v>
       </c>
       <c r="T79">
-        <v>3.2391441349062</v>
+        <v>3.37740850158674</v>
       </c>
       <c r="U79">
         <v>0.07580000000000001</v>
@@ -7931,7 +7931,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>2.236413486289693</v>
+        <v>2.207741518516748</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7939,22 +7939,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1132026015072876</v>
+        <v>0.1131844391179636</v>
       </c>
       <c r="C80">
-        <v>8.7890671238031</v>
+        <v>8.412747451037998</v>
       </c>
       <c r="D80">
-        <v>31.8576271238031</v>
+        <v>31.862827451038</v>
       </c>
       <c r="E80">
-        <v>29.20656</v>
+        <v>29.58808</v>
       </c>
       <c r="F80">
-        <v>29.75856</v>
+        <v>30.14008</v>
       </c>
       <c r="G80">
         <v>6.69</v>
@@ -7975,28 +7975,28 @@
         <v>4.98</v>
       </c>
       <c r="M80">
-        <v>2.255698848</v>
+        <v>2.284618064</v>
       </c>
       <c r="N80">
-        <v>2.724301152</v>
+        <v>2.695381936</v>
       </c>
       <c r="O80">
-        <v>0.59934625344</v>
+        <v>0.59298402592</v>
       </c>
       <c r="P80">
-        <v>2.12495489856</v>
+        <v>2.10239791008</v>
       </c>
       <c r="Q80">
-        <v>2.52495489856</v>
+        <v>2.50239791008</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3049358250331257</v>
+        <v>0.3165546624664934</v>
       </c>
       <c r="T80">
-        <v>3.37740850158674</v>
+        <v>3.528840903189236</v>
       </c>
       <c r="U80">
         <v>0.07580000000000001</v>
@@ -8013,7 +8013,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>2.207741518516748</v>
+        <v>2.17979542334565</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8021,22 +8021,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1131844391179636</v>
+        <v>0.1131662767286396</v>
       </c>
       <c r="C81">
-        <v>8.412747451037998</v>
+        <v>8.036429476316396</v>
       </c>
       <c r="D81">
-        <v>31.862827451038</v>
+        <v>31.8680294763164</v>
       </c>
       <c r="E81">
-        <v>29.58808</v>
+        <v>29.9696</v>
       </c>
       <c r="F81">
-        <v>30.14008</v>
+        <v>30.5216</v>
       </c>
       <c r="G81">
         <v>6.69</v>
@@ -8057,28 +8057,28 @@
         <v>4.98</v>
       </c>
       <c r="M81">
-        <v>2.284618064</v>
+        <v>2.31353728</v>
       </c>
       <c r="N81">
-        <v>2.695381936</v>
+        <v>2.66646272</v>
       </c>
       <c r="O81">
-        <v>0.59298402592</v>
+        <v>0.5866217984000001</v>
       </c>
       <c r="P81">
-        <v>2.10239791008</v>
+        <v>2.0798409216</v>
       </c>
       <c r="Q81">
-        <v>2.50239791008</v>
+        <v>2.4798409216</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3165546624664934</v>
+        <v>0.3293353836431979</v>
       </c>
       <c r="T81">
-        <v>3.528840903189236</v>
+        <v>3.695416544951981</v>
       </c>
       <c r="U81">
         <v>0.07580000000000001</v>
@@ -8095,7 +8095,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>2.17979542334565</v>
+        <v>2.152547980553829</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8103,22 +8103,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1131662767286396</v>
+        <v>0.1131481143393155</v>
       </c>
       <c r="C82">
-        <v>8.036429476316396</v>
+        <v>7.660113200470143</v>
       </c>
       <c r="D82">
-        <v>31.8680294763164</v>
+        <v>31.87323320047015</v>
       </c>
       <c r="E82">
-        <v>29.9696</v>
+        <v>30.35112</v>
       </c>
       <c r="F82">
-        <v>30.5216</v>
+        <v>30.90312</v>
       </c>
       <c r="G82">
         <v>6.69</v>
@@ -8139,28 +8139,28 @@
         <v>4.98</v>
       </c>
       <c r="M82">
-        <v>2.31353728</v>
+        <v>2.342456496</v>
       </c>
       <c r="N82">
-        <v>2.66646272</v>
+        <v>2.637543504</v>
       </c>
       <c r="O82">
-        <v>0.5866217984000001</v>
+        <v>0.58025957088</v>
       </c>
       <c r="P82">
-        <v>2.0798409216</v>
+        <v>2.05728393312</v>
       </c>
       <c r="Q82">
-        <v>2.4798409216</v>
+        <v>2.457283933119999</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3293353836431979</v>
+        <v>0.3434614438911344</v>
       </c>
       <c r="T82">
-        <v>3.695416544951981</v>
+        <v>3.879526464795015</v>
       </c>
       <c r="U82">
         <v>0.07580000000000001</v>
@@ -8177,7 +8177,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>2.152547980553829</v>
+        <v>2.125973314127239</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8185,22 +8185,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1131481143393155</v>
+        <v>0.1131299519499915</v>
       </c>
       <c r="C83">
-        <v>7.660113200470143</v>
+        <v>7.283798624331588</v>
       </c>
       <c r="D83">
-        <v>31.87323320047015</v>
+        <v>31.87843862433159</v>
       </c>
       <c r="E83">
-        <v>30.35112</v>
+        <v>30.73264</v>
       </c>
       <c r="F83">
-        <v>30.90312</v>
+        <v>31.28464</v>
       </c>
       <c r="G83">
         <v>6.69</v>
@@ -8221,28 +8221,28 @@
         <v>4.98</v>
       </c>
       <c r="M83">
-        <v>2.342456496</v>
+        <v>2.371375712</v>
       </c>
       <c r="N83">
-        <v>2.637543504</v>
+        <v>2.608624288</v>
       </c>
       <c r="O83">
-        <v>0.58025957088</v>
+        <v>0.57389734336</v>
       </c>
       <c r="P83">
-        <v>2.05728393312</v>
+        <v>2.03472694464</v>
       </c>
       <c r="Q83">
-        <v>2.457283933119999</v>
+        <v>2.43472694464</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3434614438911344</v>
+        <v>0.3591570663888417</v>
       </c>
       <c r="T83">
-        <v>3.879526464795015</v>
+        <v>4.084093042398387</v>
       </c>
       <c r="U83">
         <v>0.07580000000000001</v>
@@ -8259,7 +8259,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>2.125973314127239</v>
+        <v>2.100046810296419</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8267,22 +8267,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1131299519499915</v>
+        <v>0.1131117895606675</v>
       </c>
       <c r="C84">
-        <v>7.283798624331588</v>
+        <v>6.90748574873362</v>
       </c>
       <c r="D84">
-        <v>31.87843862433159</v>
+        <v>31.88364574873363</v>
       </c>
       <c r="E84">
-        <v>30.73264</v>
+        <v>31.11416000000001</v>
       </c>
       <c r="F84">
-        <v>31.28464</v>
+        <v>31.66616</v>
       </c>
       <c r="G84">
         <v>6.69</v>
@@ -8303,28 +8303,28 @@
         <v>4.98</v>
       </c>
       <c r="M84">
-        <v>2.371375712</v>
+        <v>2.400294928000001</v>
       </c>
       <c r="N84">
-        <v>2.608624288</v>
+        <v>2.579705072</v>
       </c>
       <c r="O84">
-        <v>0.57389734336</v>
+        <v>0.5675351158399999</v>
       </c>
       <c r="P84">
-        <v>2.03472694464</v>
+        <v>2.01216995616</v>
       </c>
       <c r="Q84">
-        <v>2.43472694464</v>
+        <v>2.41216995616</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3591570663888417</v>
+        <v>0.3766992327098087</v>
       </c>
       <c r="T84">
-        <v>4.084093042398387</v>
+        <v>4.312726276190391</v>
       </c>
       <c r="U84">
         <v>0.07580000000000001</v>
@@ -8341,7 +8341,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>2.100046810296419</v>
+        <v>2.074745041497667</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8349,22 +8349,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1131117895606675</v>
+        <v>0.1130936271713434</v>
       </c>
       <c r="C85">
-        <v>6.90748574873362</v>
+        <v>6.531174574509713</v>
       </c>
       <c r="D85">
-        <v>31.88364574873363</v>
+        <v>31.88885457450972</v>
       </c>
       <c r="E85">
-        <v>31.11416000000001</v>
+        <v>31.49568000000001</v>
       </c>
       <c r="F85">
-        <v>31.66616</v>
+        <v>32.04768000000001</v>
       </c>
       <c r="G85">
         <v>6.69</v>
@@ -8385,28 +8385,28 @@
         <v>4.98</v>
       </c>
       <c r="M85">
-        <v>2.400294928000001</v>
+        <v>2.429214144000001</v>
       </c>
       <c r="N85">
-        <v>2.579705072</v>
+        <v>2.550785856</v>
       </c>
       <c r="O85">
-        <v>0.5675351158399999</v>
+        <v>0.5611728883199999</v>
       </c>
       <c r="P85">
-        <v>2.01216995616</v>
+        <v>1.98961296768</v>
       </c>
       <c r="Q85">
-        <v>2.41216995616</v>
+        <v>2.389612967679999</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3766992327098087</v>
+        <v>0.3964341698208966</v>
       </c>
       <c r="T85">
-        <v>4.312726276190391</v>
+        <v>4.569938664206396</v>
       </c>
       <c r="U85">
         <v>0.07580000000000001</v>
@@ -8423,7 +8423,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>2.074745041497667</v>
+        <v>2.050045695765552</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8431,22 +8431,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1130936271713434</v>
+        <v>0.1130754647820194</v>
       </c>
       <c r="C86">
-        <v>6.53117457450972</v>
+        <v>6.154865102493858</v>
       </c>
       <c r="D86">
-        <v>31.88885457450972</v>
+        <v>31.89406510249386</v>
       </c>
       <c r="E86">
-        <v>31.49568</v>
+        <v>31.8772</v>
       </c>
       <c r="F86">
-        <v>32.04768</v>
+        <v>32.4292</v>
       </c>
       <c r="G86">
         <v>6.69</v>
@@ -8467,28 +8467,28 @@
         <v>4.98</v>
       </c>
       <c r="M86">
-        <v>2.429214144</v>
+        <v>2.45813336</v>
       </c>
       <c r="N86">
-        <v>2.550785856</v>
+        <v>2.52186664</v>
       </c>
       <c r="O86">
-        <v>0.56117288832</v>
+        <v>0.5548106608000001</v>
       </c>
       <c r="P86">
-        <v>1.98961296768</v>
+        <v>1.9670559792</v>
       </c>
       <c r="Q86">
-        <v>2.38961296768</v>
+        <v>2.3670559792</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3964341698208963</v>
+        <v>0.4188004318801292</v>
       </c>
       <c r="T86">
-        <v>4.569938664206393</v>
+        <v>4.861446037291197</v>
       </c>
       <c r="U86">
         <v>0.07580000000000001</v>
@@ -8505,7 +8505,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>2.050045695765552</v>
+        <v>2.025927511109487</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8513,22 +8513,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1130754647820194</v>
+        <v>0.1130573023926953</v>
       </c>
       <c r="C87">
-        <v>6.154865102493858</v>
+        <v>5.778557333520595</v>
       </c>
       <c r="D87">
-        <v>31.89406510249386</v>
+        <v>31.8992773335206</v>
       </c>
       <c r="E87">
-        <v>31.8772</v>
+        <v>32.25872</v>
       </c>
       <c r="F87">
-        <v>32.4292</v>
+        <v>32.81072</v>
       </c>
       <c r="G87">
         <v>6.69</v>
@@ -8549,28 +8549,28 @@
         <v>4.98</v>
       </c>
       <c r="M87">
-        <v>2.45813336</v>
+        <v>2.487052576</v>
       </c>
       <c r="N87">
-        <v>2.52186664</v>
+        <v>2.492947424</v>
       </c>
       <c r="O87">
-        <v>0.5548106608000001</v>
+        <v>0.54844843328</v>
       </c>
       <c r="P87">
-        <v>1.9670559792</v>
+        <v>1.94449899072</v>
       </c>
       <c r="Q87">
-        <v>2.3670559792</v>
+        <v>2.34449899072</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.4188004318801292</v>
+        <v>0.4443618742335381</v>
       </c>
       <c r="T87">
-        <v>4.861446037291197</v>
+        <v>5.194597320816687</v>
       </c>
       <c r="U87">
         <v>0.07580000000000001</v>
@@ -8587,7 +8587,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>2.025927511109487</v>
+        <v>2.002370214468678</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8595,22 +8595,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1130573023926953</v>
+        <v>0.1226752600033713</v>
       </c>
       <c r="C88">
-        <v>5.778557333520595</v>
+        <v>2.856308917839797</v>
       </c>
       <c r="D88">
-        <v>31.8992773335206</v>
+        <v>29.3585489178398</v>
       </c>
       <c r="E88">
-        <v>32.25872</v>
+        <v>32.64024</v>
       </c>
       <c r="F88">
-        <v>32.81072</v>
+        <v>33.19224</v>
       </c>
       <c r="G88">
         <v>6.69</v>
@@ -8631,45 +8631,45 @@
         <v>4.98</v>
       </c>
       <c r="M88">
-        <v>2.487052576</v>
+        <v>2.9873016</v>
       </c>
       <c r="N88">
-        <v>2.492947424</v>
+        <v>1.992698400000001</v>
       </c>
       <c r="O88">
-        <v>0.54844843328</v>
+        <v>0.4383936480000001</v>
       </c>
       <c r="P88">
-        <v>1.94449899072</v>
+        <v>1.554304752</v>
       </c>
       <c r="Q88">
-        <v>2.34449899072</v>
+        <v>1.954304752</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4443618742335381</v>
+        <v>0.4738558461797792</v>
       </c>
       <c r="T88">
-        <v>5.194597320816687</v>
+        <v>5.579002647961484</v>
       </c>
       <c r="U88">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V88">
         <v>0.22</v>
       </c>
       <c r="W88">
-        <v>0.05912400000000001</v>
+        <v>0.0702</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y88">
-        <v>2.002370214468678</v>
+        <v>1.667056315974256</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8677,22 +8677,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1226752600033713</v>
+        <v>0.1227678576140473</v>
       </c>
       <c r="C89">
-        <v>2.856308917839797</v>
+        <v>2.452293399229632</v>
       </c>
       <c r="D89">
-        <v>29.3585489178398</v>
+        <v>29.33605339922963</v>
       </c>
       <c r="E89">
-        <v>32.64024</v>
+        <v>33.02176</v>
       </c>
       <c r="F89">
-        <v>33.19224</v>
+        <v>33.57376</v>
       </c>
       <c r="G89">
         <v>6.69</v>
@@ -8713,28 +8713,28 @@
         <v>4.98</v>
       </c>
       <c r="M89">
-        <v>2.9873016</v>
+        <v>3.0216384</v>
       </c>
       <c r="N89">
-        <v>1.992698400000001</v>
+        <v>1.9583616</v>
       </c>
       <c r="O89">
-        <v>0.4383936480000001</v>
+        <v>0.4308395520000001</v>
       </c>
       <c r="P89">
-        <v>1.554304752</v>
+        <v>1.527522048</v>
       </c>
       <c r="Q89">
-        <v>1.954304752</v>
+        <v>1.927522048</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4738558461797792</v>
+        <v>0.5082654801170605</v>
       </c>
       <c r="T89">
-        <v>5.579002647961484</v>
+        <v>6.027475529630415</v>
       </c>
       <c r="U89">
         <v>0.09</v>
@@ -8751,7 +8751,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>1.667056315974256</v>
+        <v>1.648112494201821</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8759,22 +8759,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1227678576140473</v>
+        <v>0.1228604552247232</v>
       </c>
       <c r="C90">
-        <v>2.452293399229632</v>
+        <v>2.048312327887579</v>
       </c>
       <c r="D90">
-        <v>29.33605339922963</v>
+        <v>29.31359232788758</v>
       </c>
       <c r="E90">
-        <v>33.02176</v>
+        <v>33.40328</v>
       </c>
       <c r="F90">
-        <v>33.57376</v>
+        <v>33.95528</v>
       </c>
       <c r="G90">
         <v>6.69</v>
@@ -8795,28 +8795,28 @@
         <v>4.98</v>
       </c>
       <c r="M90">
-        <v>3.0216384</v>
+        <v>3.0559752</v>
       </c>
       <c r="N90">
-        <v>1.9583616</v>
+        <v>1.9240248</v>
       </c>
       <c r="O90">
-        <v>0.4308395520000001</v>
+        <v>0.4232854560000001</v>
       </c>
       <c r="P90">
-        <v>1.527522048</v>
+        <v>1.500739344</v>
       </c>
       <c r="Q90">
-        <v>1.927522048</v>
+        <v>1.900739344</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.5082654801170605</v>
+        <v>0.5489314111338475</v>
       </c>
       <c r="T90">
-        <v>6.027475529630415</v>
+        <v>6.557488935239149</v>
       </c>
       <c r="U90">
         <v>0.09</v>
@@ -8833,7 +8833,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>1.648112494201821</v>
+        <v>1.629594376289441</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8841,22 +8841,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1228604552247232</v>
+        <v>0.1229530528353992</v>
       </c>
       <c r="C91">
-        <v>2.048312327887579</v>
+        <v>1.644365624750797</v>
       </c>
       <c r="D91">
-        <v>29.31359232788758</v>
+        <v>29.2911656247508</v>
       </c>
       <c r="E91">
-        <v>33.40328</v>
+        <v>33.7848</v>
       </c>
       <c r="F91">
-        <v>33.95528</v>
+        <v>34.3368</v>
       </c>
       <c r="G91">
         <v>6.69</v>
@@ -8877,28 +8877,28 @@
         <v>4.98</v>
       </c>
       <c r="M91">
-        <v>3.0559752</v>
+        <v>3.090312</v>
       </c>
       <c r="N91">
-        <v>1.9240248</v>
+        <v>1.889688</v>
       </c>
       <c r="O91">
-        <v>0.4232854560000001</v>
+        <v>0.41573136</v>
       </c>
       <c r="P91">
-        <v>1.500739344</v>
+        <v>1.47395664</v>
       </c>
       <c r="Q91">
-        <v>1.900739344</v>
+        <v>1.873956639999999</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.5489314111338475</v>
+        <v>0.5977305283539919</v>
       </c>
       <c r="T91">
-        <v>6.557488935239149</v>
+        <v>7.193505021969632</v>
       </c>
       <c r="U91">
         <v>0.09</v>
@@ -8915,7 +8915,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>1.629594376289441</v>
+        <v>1.611487772108447</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8923,22 +8923,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1229530528353992</v>
+        <v>0.1230456504460751</v>
       </c>
       <c r="C92">
-        <v>1.644365624750797</v>
+        <v>1.240453210998197</v>
       </c>
       <c r="D92">
-        <v>29.2911656247508</v>
+        <v>29.2687732109982</v>
       </c>
       <c r="E92">
-        <v>33.7848</v>
+        <v>34.16632000000001</v>
       </c>
       <c r="F92">
-        <v>34.3368</v>
+        <v>34.71832000000001</v>
       </c>
       <c r="G92">
         <v>6.69</v>
@@ -8959,28 +8959,28 @@
         <v>4.98</v>
       </c>
       <c r="M92">
-        <v>3.090312</v>
+        <v>3.124648800000001</v>
       </c>
       <c r="N92">
-        <v>1.889688</v>
+        <v>1.8553512</v>
       </c>
       <c r="O92">
-        <v>0.41573136</v>
+        <v>0.408177264</v>
       </c>
       <c r="P92">
-        <v>1.47395664</v>
+        <v>1.447173936</v>
       </c>
       <c r="Q92">
-        <v>1.873956639999999</v>
+        <v>1.847173935999999</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.5977305283539919</v>
+        <v>0.6573738938452797</v>
       </c>
       <c r="T92">
-        <v>7.193505021969632</v>
+        <v>7.970858016862445</v>
       </c>
       <c r="U92">
         <v>0.09</v>
@@ -8997,7 +8997,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>1.611487772108447</v>
+        <v>1.593779115272091</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9005,22 +9005,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1230456504460751</v>
+        <v>0.1231382480567511</v>
       </c>
       <c r="C93">
-        <v>1.240453210998197</v>
+        <v>0.8365750080495573</v>
       </c>
       <c r="D93">
-        <v>29.2687732109982</v>
+        <v>29.24641500804956</v>
       </c>
       <c r="E93">
-        <v>34.16632000000001</v>
+        <v>34.54784</v>
       </c>
       <c r="F93">
-        <v>34.71832000000001</v>
+        <v>35.09984</v>
       </c>
       <c r="G93">
         <v>6.69</v>
@@ -9041,28 +9041,28 @@
         <v>4.98</v>
       </c>
       <c r="M93">
-        <v>3.124648800000001</v>
+        <v>3.1589856</v>
       </c>
       <c r="N93">
-        <v>1.8553512</v>
+        <v>1.821014400000001</v>
       </c>
       <c r="O93">
-        <v>0.408177264</v>
+        <v>0.4006231680000001</v>
       </c>
       <c r="P93">
-        <v>1.447173936</v>
+        <v>1.420391232000001</v>
       </c>
       <c r="Q93">
-        <v>1.847173935999999</v>
+        <v>1.820391232</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.6573738938452797</v>
+        <v>0.7319281007093892</v>
       </c>
       <c r="T93">
-        <v>7.970858016862445</v>
+        <v>8.942549260478462</v>
       </c>
       <c r="U93">
         <v>0.09</v>
@@ -9079,7 +9079,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>1.593779115272091</v>
+        <v>1.576455429236525</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9087,22 +9087,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1231382480567511</v>
+        <v>0.1232308456674271</v>
       </c>
       <c r="C94">
-        <v>0.8365750080495573</v>
+        <v>0.4327309375645711</v>
       </c>
       <c r="D94">
-        <v>29.24641500804956</v>
+        <v>29.22409093756457</v>
       </c>
       <c r="E94">
-        <v>34.54784</v>
+        <v>34.92936</v>
       </c>
       <c r="F94">
-        <v>35.09984</v>
+        <v>35.48136</v>
       </c>
       <c r="G94">
         <v>6.69</v>
@@ -9123,28 +9123,28 @@
         <v>4.98</v>
       </c>
       <c r="M94">
-        <v>3.1589856</v>
+        <v>3.1933224</v>
       </c>
       <c r="N94">
-        <v>1.821014400000001</v>
+        <v>1.7866776</v>
       </c>
       <c r="O94">
-        <v>0.4006231680000001</v>
+        <v>0.3930690720000001</v>
       </c>
       <c r="P94">
-        <v>1.420391232000001</v>
+        <v>1.393608528</v>
       </c>
       <c r="Q94">
-        <v>1.820391232</v>
+        <v>1.793608528</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.7319281007093892</v>
+        <v>0.8277835095346729</v>
       </c>
       <c r="T94">
-        <v>8.942549260478462</v>
+        <v>10.19186657369905</v>
       </c>
       <c r="U94">
         <v>0.09</v>
@@ -9161,7 +9161,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>1.576455429236525</v>
+        <v>1.55950429558882</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9169,22 +9169,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1232308456674271</v>
+        <v>0.123323443278103</v>
       </c>
       <c r="C95">
-        <v>0.4327309375645711</v>
+        <v>0.02892092144192304</v>
       </c>
       <c r="D95">
-        <v>29.22409093756457</v>
+        <v>29.20180092144193</v>
       </c>
       <c r="E95">
-        <v>34.92936</v>
+        <v>35.31088</v>
       </c>
       <c r="F95">
-        <v>35.48136</v>
+        <v>35.86288</v>
       </c>
       <c r="G95">
         <v>6.69</v>
@@ -9205,28 +9205,28 @@
         <v>4.98</v>
       </c>
       <c r="M95">
-        <v>3.1933224</v>
+        <v>3.2276592</v>
       </c>
       <c r="N95">
-        <v>1.7866776</v>
+        <v>1.7523408</v>
       </c>
       <c r="O95">
-        <v>0.3930690720000001</v>
+        <v>0.3855149760000001</v>
       </c>
       <c r="P95">
-        <v>1.393608528</v>
+        <v>1.366825824</v>
       </c>
       <c r="Q95">
-        <v>1.793608528</v>
+        <v>1.766825824</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.8277835095346729</v>
+        <v>0.9555907213017182</v>
       </c>
       <c r="T95">
-        <v>10.19186657369905</v>
+        <v>11.85762299132651</v>
       </c>
       <c r="U95">
         <v>0.09</v>
@@ -9243,7 +9243,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>1.55950429558882</v>
+        <v>1.542913824359152</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9251,22 +9251,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.123323443278103</v>
+        <v>0.123416040888779</v>
       </c>
       <c r="C96">
-        <v>0.02892092144192304</v>
+        <v>-0.3748551181815785</v>
       </c>
       <c r="D96">
-        <v>29.20180092144193</v>
+        <v>29.17954488181843</v>
       </c>
       <c r="E96">
-        <v>35.31088</v>
+        <v>35.69240000000001</v>
       </c>
       <c r="F96">
-        <v>35.86288</v>
+        <v>36.24440000000001</v>
       </c>
       <c r="G96">
         <v>6.69</v>
@@ -9287,28 +9287,28 @@
         <v>4.98</v>
       </c>
       <c r="M96">
-        <v>3.2276592</v>
+        <v>3.261996</v>
       </c>
       <c r="N96">
-        <v>1.7523408</v>
+        <v>1.718004</v>
       </c>
       <c r="O96">
-        <v>0.3855149760000001</v>
+        <v>0.37796088</v>
       </c>
       <c r="P96">
-        <v>1.366825824</v>
+        <v>1.34004312</v>
       </c>
       <c r="Q96">
-        <v>1.766825824</v>
+        <v>1.740043119999999</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.9555907213017182</v>
+        <v>1.134520817775582</v>
       </c>
       <c r="T96">
-        <v>11.85762299132651</v>
+        <v>14.18968197600495</v>
       </c>
       <c r="U96">
         <v>0.09</v>
@@ -9325,7 +9325,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>1.542913824359152</v>
+        <v>1.526672626208003</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9333,22 +9333,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.123416040888779</v>
+        <v>0.123508638499455</v>
       </c>
       <c r="C97">
-        <v>-0.3748551181815785</v>
+        <v>-0.7785972589319385</v>
       </c>
       <c r="D97">
-        <v>29.17954488181843</v>
+        <v>29.15732274106806</v>
       </c>
       <c r="E97">
-        <v>35.69240000000001</v>
+        <v>36.07392</v>
       </c>
       <c r="F97">
-        <v>36.24440000000001</v>
+        <v>36.62592</v>
       </c>
       <c r="G97">
         <v>6.69</v>
@@ -9369,28 +9369,28 @@
         <v>4.98</v>
       </c>
       <c r="M97">
-        <v>3.261996</v>
+        <v>3.2963328</v>
       </c>
       <c r="N97">
-        <v>1.718004</v>
+        <v>1.6836672</v>
       </c>
       <c r="O97">
-        <v>0.37796088</v>
+        <v>0.3704067840000001</v>
       </c>
       <c r="P97">
-        <v>1.34004312</v>
+        <v>1.313260416</v>
       </c>
       <c r="Q97">
-        <v>1.740043119999999</v>
+        <v>1.713260416</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.134520817775582</v>
+        <v>1.402915962486377</v>
       </c>
       <c r="T97">
-        <v>14.18968197600495</v>
+        <v>17.68777045302262</v>
       </c>
       <c r="U97">
         <v>0.09</v>
@@ -9407,7 +9407,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>1.526672626208003</v>
+        <v>1.510769786351669</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9415,22 +9415,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.123508638499455</v>
+        <v>0.1704102730615854</v>
       </c>
       <c r="C98">
-        <v>-0.7785972589319314</v>
+        <v>-9.276475688213413</v>
       </c>
       <c r="D98">
-        <v>29.15732274106807</v>
+        <v>21.04096431178659</v>
       </c>
       <c r="E98">
-        <v>36.07392</v>
+        <v>36.45544</v>
       </c>
       <c r="F98">
-        <v>36.62592</v>
+        <v>37.00744</v>
       </c>
       <c r="G98">
         <v>6.69</v>
@@ -9451,45 +9451,45 @@
         <v>4.98</v>
       </c>
       <c r="M98">
-        <v>3.2963328</v>
+        <v>5.432692192000001</v>
       </c>
       <c r="N98">
-        <v>1.6836672</v>
+        <v>-0.4526921920000007</v>
       </c>
       <c r="O98">
-        <v>0.3704067840000001</v>
+        <v>-0.09959228224000015</v>
       </c>
       <c r="P98">
-        <v>1.313260416</v>
+        <v>-0.3530999097600005</v>
       </c>
       <c r="Q98">
-        <v>1.713260416</v>
+        <v>0.04690009023999897</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.402915962486373</v>
+        <v>1.891032838685263</v>
       </c>
       <c r="T98">
-        <v>17.68777045302257</v>
+        <v>24.04956966481181</v>
       </c>
       <c r="U98">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V98">
-        <v>0.22</v>
+        <v>0.2016679688964053</v>
       </c>
       <c r="W98">
-        <v>0.0702</v>
+        <v>0.1171951421660077</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y98">
-        <v>1.510769786351669</v>
+        <v>0.9166725858927514</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9497,22 +9497,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1704102730615854</v>
+        <v>0.1714202730615854</v>
       </c>
       <c r="C99">
-        <v>-9.276475688213413</v>
+        <v>-9.783372446940778</v>
       </c>
       <c r="D99">
-        <v>21.04096431178659</v>
+        <v>20.91558755305922</v>
       </c>
       <c r="E99">
-        <v>36.45544</v>
+        <v>36.83696</v>
       </c>
       <c r="F99">
-        <v>37.00744</v>
+        <v>37.38896</v>
       </c>
       <c r="G99">
         <v>6.69</v>
@@ -9533,37 +9533,37 @@
         <v>4.98</v>
       </c>
       <c r="M99">
-        <v>5.432692192000001</v>
+        <v>5.488699328</v>
       </c>
       <c r="N99">
-        <v>-0.4526921920000007</v>
+        <v>-0.5086993279999996</v>
       </c>
       <c r="O99">
-        <v>-0.09959228224000015</v>
+        <v>-0.1119138521599999</v>
       </c>
       <c r="P99">
-        <v>-0.3530999097600005</v>
+        <v>-0.3967854758399997</v>
       </c>
       <c r="Q99">
-        <v>0.04690009023999897</v>
+        <v>0.003214524159999788</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.891032838685263</v>
+        <v>2.813649258027894</v>
       </c>
       <c r="T99">
-        <v>24.04956966481181</v>
+        <v>36.0743544972177</v>
       </c>
       <c r="U99">
         <v>0.1468</v>
       </c>
       <c r="V99">
-        <v>0.2016679688964053</v>
+        <v>0.1996101324790951</v>
       </c>
       <c r="W99">
-        <v>0.1171951421660077</v>
+        <v>0.1174972325520689</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9571,7 +9571,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.9166725858927514</v>
+        <v>0.9073187839958867</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9579,22 +9579,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1714202730615854</v>
+        <v>0.1724302730615854</v>
       </c>
       <c r="C100">
-        <v>-9.783372446940778</v>
+        <v>-10.28878389164278</v>
       </c>
       <c r="D100">
-        <v>20.91558755305922</v>
+        <v>20.79169610835722</v>
       </c>
       <c r="E100">
-        <v>36.83696</v>
+        <v>37.21848</v>
       </c>
       <c r="F100">
-        <v>37.38896</v>
+        <v>37.77048</v>
       </c>
       <c r="G100">
         <v>6.69</v>
@@ -9615,37 +9615,37 @@
         <v>4.98</v>
       </c>
       <c r="M100">
-        <v>5.488699328</v>
+        <v>5.544706464000001</v>
       </c>
       <c r="N100">
-        <v>-0.5086993279999996</v>
+        <v>-0.5647064640000004</v>
       </c>
       <c r="O100">
-        <v>-0.1119138521599999</v>
+        <v>-0.1242354220800001</v>
       </c>
       <c r="P100">
-        <v>-0.3967854758399997</v>
+        <v>-0.4404710419200003</v>
       </c>
       <c r="Q100">
-        <v>0.003214524159999788</v>
+        <v>-0.04047104192000084</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.813649258027894</v>
+        <v>5.581498516055787</v>
       </c>
       <c r="T100">
-        <v>36.0743544972177</v>
+        <v>72.14870899443541</v>
       </c>
       <c r="U100">
         <v>0.1468</v>
       </c>
       <c r="V100">
-        <v>0.1996101324790951</v>
+        <v>0.1975938685146597</v>
       </c>
       <c r="W100">
-        <v>0.1174972325520689</v>
+        <v>0.117793220102048</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9653,91 +9653,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.9073187839958867</v>
+        <v>0.8981539477939079</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1724302730615854</v>
-      </c>
-      <c r="C101">
-        <v>-10.28878389164278</v>
-      </c>
-      <c r="D101">
-        <v>20.79169610835722</v>
-      </c>
-      <c r="E101">
-        <v>37.21848</v>
-      </c>
-      <c r="F101">
-        <v>37.77048</v>
-      </c>
-      <c r="G101">
-        <v>6.69</v>
-      </c>
-      <c r="H101">
-        <v>37.6</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>5.38</v>
-      </c>
-      <c r="K101">
-        <v>0.3999999999999995</v>
-      </c>
-      <c r="L101">
-        <v>4.98</v>
-      </c>
-      <c r="M101">
-        <v>5.544706464000001</v>
-      </c>
-      <c r="N101">
-        <v>-0.5647064640000004</v>
-      </c>
-      <c r="O101">
-        <v>-0.1242354220800001</v>
-      </c>
-      <c r="P101">
-        <v>-0.4404710419200003</v>
-      </c>
-      <c r="Q101">
-        <v>-0.04047104192000084</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>5.581498516055787</v>
-      </c>
-      <c r="T101">
-        <v>72.14870899443541</v>
-      </c>
-      <c r="U101">
-        <v>0.1468</v>
-      </c>
-      <c r="V101">
-        <v>0.1975938685146597</v>
-      </c>
-      <c r="W101">
-        <v>0.117793220102048</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Ca2/CC</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.8981539477939079</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
